--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E705AD42-CB9C-4471-9148-59829DDA0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB375B0-967B-4EDD-97AD-B071DCDB46C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4943,10 +4943,52 @@
       <c r="A31">
         <v>29</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:36">
       <c r="A32">
         <v>30</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB375B0-967B-4EDD-97AD-B071DCDB46C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD612116-B862-4F74-BDDB-99F90D30F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="375">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1570,6 +1570,46 @@
     <rPh sb="15" eb="17">
       <t>ジョウホウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="びび"&gt;微美&lt;/r&gt;しき&lt;r="びぼう"&gt;魅忘&lt;/r&gt;の&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>娇美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>嬌美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>Errante Bello del Olvido</t>
+  </si>
+  <si>
+    <t>Errante Belo do Esquecimento</t>
+  </si>
+  <si>
+    <t>微美しき魅忘の彷徨う者の情報</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="うた"&gt;唄&lt;/r&gt;&lt;r="うた"&gt;歌&lt;/r&gt;う&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sing-Song Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>咏永的彷徨者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canto-Llanto, el Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唄歌う彷徨う者の情報</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1955,7 +1995,7 @@
     <col min="13" max="13" width="26.25" customWidth="1"/>
     <col min="14" max="14" width="9.625" customWidth="1"/>
     <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
     <col min="17" max="17" width="20.375" customWidth="1"/>
     <col min="18" max="18" width="20.625" customWidth="1"/>
     <col min="19" max="19" width="23.875" customWidth="1"/>
@@ -4939,7 +4979,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="31" spans="1:36">
+    <row r="31" spans="1:36" ht="75">
       <c r="A31">
         <v>29</v>
       </c>
@@ -4964,8 +5004,71 @@
       <c r="I31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:36">
+      <c r="J31" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="K31" s="1">
+        <v>10</v>
+      </c>
+      <c r="M31" s="1">
+        <v>10</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>10</v>
+      </c>
+      <c r="S31" s="1">
+        <v>10</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="U31" s="1">
+        <v>10</v>
+      </c>
+      <c r="W31" s="1">
+        <v>10</v>
+      </c>
+      <c r="X31" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>367</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>368</v>
+      </c>
+      <c r="AG31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AI31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AJ31" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" ht="56.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -4989,6 +5092,69 @@
       </c>
       <c r="I32">
         <v>1</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K32" s="1">
+        <v>10</v>
+      </c>
+      <c r="M32" s="1">
+        <v>10</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>10</v>
+      </c>
+      <c r="S32" s="1">
+        <v>10</v>
+      </c>
+      <c r="T32" t="s">
+        <v>372</v>
+      </c>
+      <c r="U32" s="1">
+        <v>10</v>
+      </c>
+      <c r="W32" s="1">
+        <v>10</v>
+      </c>
+      <c r="X32" t="s">
+        <v>372</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AI32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AJ32" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD612116-B862-4F74-BDDB-99F90D30F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86D2458-68BF-4736-B1BA-1A51B5FD2504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="387">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1612,12 +1612,84 @@
     <t>唄歌う彷徨う者の情報</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
+俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
+姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It happened the moment I heard a woman's voice from somewhere and peered out from cover to check what was going on. The moment the earless, brown-haired woman noticed me, she screamed and lunged at me with wild ferocity.
+I got lucky and dove into cover to escape her, but someone nearby ended up being targeted instead. The fact that it ran off into the distance with that thing is the only reason I survived — but there's a good chance that person only got attacked because of me.
+Getting seen isn't the only trigger — if it's exposed to light, it loses itself entirely and charges. Bottom line: never use a light source around it, no matter what.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不知从哪里传来了女人的声音，我正想从暗处窥探情况，就在那一瞬间，一个没有耳朵、留着棕色头发的女人注意到了我，尖叫着朝我猛扑过来。
+我运气好滚进了暗处才逃过一劫，但附近的一个人却因此被盯上了。多亏它带着那家伙一起跑远了，我才捡回一条命——但那人很可能是因为我才被袭击的。
+不仅仅是被看到会引发攻击，只要被灯光照到，它就会彻底失控冲过来。总之，对付它绝对不能用灯光。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不知從哪裡傳來了女人的聲音，我正想從暗處窺探情況，就在那一瞬間，一個沒有耳朵、留著棕色頭髮的女人注意到了我，尖叫著朝我猛撲過來。
+我運氣好滾進了暗處才逃過一劫，但附近的一個人卻因此被盯上了。多虧牠帶著那傢伙一起跑遠了，我才撿回一條命——但那人很可能是因為我才被襲擊的。
+不僅僅是被看到會引發攻擊，只要被燈光照到，牠就會徹底失控衝過來。總之，對付牠絕對不能用燈光。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fue en el instante en que oí la voz de una mujer surgir de algún lugar y me asomé desde donde me escondía para ver qué pasaba. En cuanto esa mujer sin orejas y de cabello castaño me notó, se lanzó hacia mí gritando con una ferocidad desquiciada.
+Tuve la suerte de arrojarme a un escondite y escapar, pero alguien que estaba cerca terminó siendo el blanco. El hecho de que esa cosa se alejara corriendo junto con esa persona es la única razón por la que sobreviví, pero es muy probable que a esa persona la atacaran por mi culpa.
+No basta con que la vean para que ataque: si la ilumina una luz, pierde completamente el control y embiste. En resumen, bajo ninguna circunstancia hay que usar luz cerca de ella.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Foi no instante em que ouvi a voz de uma mulher vindo de algum lugar e espiei do meu esconderijo para ver o que estava acontecendo. Assim que aquela mulher sem orelhas e de cabelo castanho me percebeu, ela avançou gritando com uma fúria descontrolada.
+Tive a sorte de me jogar num esconderijo e escapar, mas alguém que estava por perto acabou sendo o alvo. O fato de aquela coisa ter corrido para longe junto com essa pessoa foi a única razão pela qual sobrevivi — mas é bem provável que essa pessoa só tenha sido atacada por minha causa.
+Não é só ser vista que desencadeia o ataque: se for exposta à luz, ela perde completamente o controle e avança. Resumindo, nunca se deve usar luz perto dela, de jeito nenhum.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠くから子供の鼻歌が聞こえてきたが、歌が全て終わった瞬間、いきなりこちらに向かって走り始めてきた。
+何度も奴を足止めしながら逃げ切ったつもりだが、常に俺を追跡してくる。なんで俺の居場所が常にバレているんだ…。
+他の化け物の時は運よく逃げ切れたが、今度こそ俺は終わりかもしれない…。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I heard a child humming a tune from somewhere far off, and the instant the humming finished, it suddenly started running straight at me.
+I've been stalling it over and over and thought I'd gotten away clean, but it keeps tracking me no matter what. Why does it always know exactly where I am...
+I got lucky and escaped the other monsters, but this time... this might really be it for me.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>远处传来了孩子哼歌的声音，可就在那首歌唱完的瞬间，它突然朝我猛冲了过来。
+我一次又一次地拖住它、试图甩掉它，本以为已经逃脱了，可它却始终紧追不舍。为什么我的位置总是被它发现……
+之前遇到别的怪物时运气好逃过了一劫，可这一次……我可能真的要完了……</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠處傳來了孩子哼歌的聲音，可就在那首歌唱完的瞬間，牠突然朝我猛衝了過來。
+我一次又一次地拖住牠、試圖甩掉牠，本以為已經逃脫了，可牠卻始終緊追不捨。為什麼我的位置總是被牠發現……
+之前遇到其他怪物時運氣好逃過了一劫，可這一次……我可能真的要完了……</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Oí a lo lejos el tarareo de un niño, y en el instante mismo en que la melodía terminó, se lanzó a correr directo hacia mí.
+Lo he ido frenando una y otra vez y pensé que había logrado escapar limpiamente, pero no importa lo que haga, siempre me sigue el rastro. ¿Por qué siempre sabe exactamente dónde estoy...?
+Con los otros monstruos tuve la suerte de escapar, pero esta vez... puede que de verdad sea mi fin.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ouvi ao longe um zumbido de criança, uma cantarolada, e no exato instante em que a melodia terminou, aquilo saiu correndo direto na minha direção.
+Fiquei atrasando-o várias vezes e achei que tinha conseguido escapar de vez, mas não importa o que eu faça, ele sempre me rastreia. Por que ele sempre sabe exatamente onde eu estou...
+Com os outros monstros tive a sorte de escapar, mas dessa vez... pode ser que esse seja realmente o meu fim.</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1657,6 +1729,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1678,7 +1757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1696,6 +1775,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4979,7 +5061,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="75">
+    <row r="31" spans="1:36" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5010,6 +5092,9 @@
       <c r="K31" s="1">
         <v>10</v>
       </c>
+      <c r="L31" s="1" t="s">
+        <v>375</v>
+      </c>
       <c r="M31" s="1">
         <v>10</v>
       </c>
@@ -5025,6 +5110,9 @@
       <c r="Q31" s="1">
         <v>10</v>
       </c>
+      <c r="R31" s="1" t="s">
+        <v>376</v>
+      </c>
       <c r="S31" s="1">
         <v>10</v>
       </c>
@@ -5034,6 +5122,9 @@
       <c r="U31" s="1">
         <v>10</v>
       </c>
+      <c r="V31" s="8" t="s">
+        <v>377</v>
+      </c>
       <c r="W31" s="1">
         <v>10</v>
       </c>
@@ -5043,6 +5134,9 @@
       <c r="Y31" s="1">
         <v>10</v>
       </c>
+      <c r="Z31" s="9" t="s">
+        <v>378</v>
+      </c>
       <c r="AA31" s="1">
         <v>10</v>
       </c>
@@ -5052,6 +5146,9 @@
       <c r="AC31" s="1">
         <v>10</v>
       </c>
+      <c r="AD31" s="1" t="s">
+        <v>379</v>
+      </c>
       <c r="AE31" s="1">
         <v>10</v>
       </c>
@@ -5061,6 +5158,9 @@
       <c r="AG31" s="1">
         <v>10</v>
       </c>
+      <c r="AH31" s="1" t="s">
+        <v>380</v>
+      </c>
       <c r="AI31" s="1">
         <v>10</v>
       </c>
@@ -5068,7 +5168,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="56.25">
+    <row r="32" spans="1:36" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5099,6 +5199,9 @@
       <c r="K32" s="1">
         <v>10</v>
       </c>
+      <c r="L32" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="M32" s="1">
         <v>10</v>
       </c>
@@ -5114,6 +5217,9 @@
       <c r="Q32" s="1">
         <v>10</v>
       </c>
+      <c r="R32" s="1" t="s">
+        <v>382</v>
+      </c>
       <c r="S32" s="1">
         <v>10</v>
       </c>
@@ -5123,6 +5229,9 @@
       <c r="U32" s="1">
         <v>10</v>
       </c>
+      <c r="V32" s="8" t="s">
+        <v>383</v>
+      </c>
       <c r="W32" s="1">
         <v>10</v>
       </c>
@@ -5132,6 +5241,9 @@
       <c r="Y32" s="1">
         <v>10</v>
       </c>
+      <c r="Z32" s="1" t="s">
+        <v>384</v>
+      </c>
       <c r="AA32" s="1">
         <v>10</v>
       </c>
@@ -5141,6 +5253,9 @@
       <c r="AC32" s="1">
         <v>10</v>
       </c>
+      <c r="AD32" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="AE32" s="1">
         <v>10</v>
       </c>
@@ -5149,6 +5264,9 @@
       </c>
       <c r="AG32" s="1">
         <v>10</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="AI32" s="1">
         <v>10</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86D2458-68BF-4736-B1BA-1A51B5FD2504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF19439-1955-4784-83CD-641D32181F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="388">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1682,6 +1682,10 @@
     <t>Ouvi ao longe um zumbido de criança, uma cantarolada, e no exato instante em que a melodia terminou, aquilo saiu correndo direto na minha direção.
 Fiquei atrasando-o várias vezes e achei que tinha conseguido escapar de vez, mas não importa o que eu faça, ele sempre me rastreia. Por que ele sempre sabe exatamente onde eu estou...
 Com os outros monstros tive a sorte de escapar, mas dessa vez... pode ser que esse seja realmente o meu fim.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Beauteous-Bewilder Wanderer</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2077,7 +2081,7 @@
     <col min="13" max="13" width="26.25" customWidth="1"/>
     <col min="14" max="14" width="9.625" customWidth="1"/>
     <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="16" max="16" width="31.25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" customWidth="1"/>
     <col min="18" max="18" width="20.625" customWidth="1"/>
     <col min="19" max="19" width="23.875" customWidth="1"/>
@@ -5105,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="Q31" s="1">
         <v>10</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF19439-1955-4784-83CD-641D32181F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CFAC64-4662-4402-95E0-99B5871654E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>350</v>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>364</v>
@@ -5195,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>370</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CFAC64-4662-4402-95E0-99B5871654E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A1995F-BF9F-4E60-9297-D42B291A2B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1613,12 +1613,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
-俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
-姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>It happened the moment I heard a woman's voice from somewhere and peered out from cover to check what was going on. The moment the earless, brown-haired woman noticed me, she screamed and lunged at me with wild ferocity.
 I got lucky and dove into cover to escape her, but someone nearby ended up being targeted instead. The fact that it ran off into the distance with that thing is the only reason I survived — but there's a good chance that person only got attacked because of me.
 Getting seen isn't the only trigger — if it's exposed to light, it loses itself entirely and charges. Bottom line: never use a light source around it, no matter what.</t>
@@ -1686,6 +1680,15 @@
   </si>
   <si>
     <t>Beauteous-Bewilder Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せないんだ。
+このメモを読んでいる君と同じ状況だろう。この迷宮で起こった出来事をここにメモする。
+俺の他に何人か迷宮を探索している人がいたが、そのうちの1人が長身でスーツ姿の肌が赤い化け物に捕まっちまった。
+俺はいち早く逃げたが、そいつがその後どうなったかは分からない。
+今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
+まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。化け物に見つかった原因は恐らくそれだろう。また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4880,7 +4883,7 @@
         <v>350</v>
       </c>
       <c r="K29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>351</v>
@@ -4898,7 +4901,7 @@
         <v>352</v>
       </c>
       <c r="Q29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>353</v>
@@ -4910,7 +4913,7 @@
         <v>355</v>
       </c>
       <c r="U29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V29" s="8" t="s">
         <v>354</v>
@@ -4922,7 +4925,7 @@
         <v>356</v>
       </c>
       <c r="Y29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z29" s="8" t="s">
         <v>357</v>
@@ -4934,7 +4937,7 @@
         <v>358</v>
       </c>
       <c r="AC29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD29" s="1" t="s">
         <v>359</v>
@@ -4946,7 +4949,7 @@
         <v>360</v>
       </c>
       <c r="AG29" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>361</v>
@@ -4987,10 +4990,10 @@
         <v>350</v>
       </c>
       <c r="K30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="M30" s="1">
         <v>10</v>
@@ -5005,7 +5008,7 @@
         <v>352</v>
       </c>
       <c r="Q30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>353</v>
@@ -5017,7 +5020,7 @@
         <v>355</v>
       </c>
       <c r="U30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V30" s="8" t="s">
         <v>354</v>
@@ -5029,7 +5032,7 @@
         <v>356</v>
       </c>
       <c r="Y30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z30" s="8" t="s">
         <v>357</v>
@@ -5041,7 +5044,7 @@
         <v>358</v>
       </c>
       <c r="AC30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD30" s="1" t="s">
         <v>359</v>
@@ -5053,7 +5056,7 @@
         <v>360</v>
       </c>
       <c r="AG30" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH30" s="1" t="s">
         <v>361</v>
@@ -5094,10 +5097,10 @@
         <v>364</v>
       </c>
       <c r="K31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="M31" s="1">
         <v>10</v>
@@ -5109,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S31" s="1">
         <v>10</v>
@@ -5124,10 +5127,10 @@
         <v>365</v>
       </c>
       <c r="U31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="W31" s="1">
         <v>10</v>
@@ -5136,10 +5139,10 @@
         <v>366</v>
       </c>
       <c r="Y31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z31" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA31" s="1">
         <v>10</v>
@@ -5148,10 +5151,10 @@
         <v>367</v>
       </c>
       <c r="AC31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AE31" s="1">
         <v>10</v>
@@ -5160,10 +5163,10 @@
         <v>368</v>
       </c>
       <c r="AG31" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI31" s="1">
         <v>10</v>
@@ -5201,10 +5204,10 @@
         <v>370</v>
       </c>
       <c r="K32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M32" s="1">
         <v>10</v>
@@ -5219,10 +5222,10 @@
         <v>371</v>
       </c>
       <c r="Q32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="S32" s="1">
         <v>10</v>
@@ -5231,10 +5234,10 @@
         <v>372</v>
       </c>
       <c r="U32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="W32" s="1">
         <v>10</v>
@@ -5243,10 +5246,10 @@
         <v>372</v>
       </c>
       <c r="Y32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA32" s="1">
         <v>10</v>
@@ -5255,10 +5258,10 @@
         <v>373</v>
       </c>
       <c r="AC32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AE32" s="1">
         <v>10</v>
@@ -5267,10 +5270,10 @@
         <v>360</v>
       </c>
       <c r="AG32" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AH32" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AI32" s="1">
         <v>10</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A1995F-BF9F-4E60-9297-D42B291A2B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04296982-097B-4F91-AEDD-F126B9B57688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1461,46 +1461,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せないんだ。
-このメモを読んでいる君と同じ状況だろう。
-この迷宮で起こった出来事をここにメモする。
-俺の他に何人か迷宮を探索している人がいたが、そのうちの1人が長身でスーツ姿の肌が赤い化け物に捕まっちまった。
-俺はいち早く逃げたが、そいつがその後どうなったかは分からない。
-今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
-まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。
-化け物に見つかった原因は恐らくそれだろう。
-また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Vein-Vain Wanderer</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>I'd love to tell you my name... but having had it discarded, I can no longer remember it.
-You, reading this note, are likely in the exact same situation.
-I will write down what happened in this labyrinth right here.
-There were a few others exploring the labyrinth besides me, but one of them was caught by a tall monster in a suit with red skin.
-I was the first to run, so I don't know what happened to them after that.
-Now I'm hiding and taking stock of the situation, analyzing the characteristics of that monster in my own way.
-First, regarding the person who was caught—they couldn't handle the fear, panicked, ran, and made a lot of noise.
-That was likely the reason they were spotted by the monster.
-Also, I once accidentally turned on my light near the creature, but because it couldn't detect the bright glare, my location wasn't exposed.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>我想说出我的名字……但因为名字被毁弃了，我已经想不起来了。
-读着这张纸条的你，大概也是同样的境遇吧。
-在此，我将这迷宫里发生的事记录下来。
-除了我之外，还有几个人也在探索这座迷宫，但其中一人被一个身穿西装、皮肤发红的高大怪物给抓住了。
-我第一时间逃跑了，所以不知道那个人之后怎么样了。
-现在我正躲着整理当下的状况，试着用我自己的方式分析一下那个怪物的特征。
-首先是关于那个被抓的人，他无法承受恐惧，陷入恐慌并疯狂逃跑、发出很大的噪音。
-被怪物发现的原因恐怕就是这个。
-另外，有一次我在怪物附近不小心点亮了手电筒，但也许是因为它无法感知强烈的光线，我的位置并没有暴露。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>沉溺寂声之徘徊者</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1509,47 +1473,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>我想說出我的名字……但因為名字被毀棄了，我已经想不起來了。
-讀著這張紙條的你，大概也是同樣的境遇吧。
-在此，我將這迷宮裡發生的事記錄下來。
-除了我之外，還有幾個人也在探索這座迷宮，但其中一人被一個身穿西裝、皮膚發紅的高大怪物給抓住了。
-我第一時間逃跑了，所以不知道那個人之後怎麼樣了。
-現在我正躲著整理當下的狀況，試著用我自己方式分析一下那個怪物的特徵。
-首先是關於那個被抓的人，他無法承受恐懼，陷入恐慌並瘋狂逃跑、發出很大的噪音。
-被怪物發現的原因恐怕就是這個。
-另外，有一次我在怪物附近不小心點亮了手電筒，但也許是因為它無法感知強烈的光線，我的位置並沒有暴露。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Errante que Arde en Silencio</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Me gustaría decirte mi nombre... pero como me lo destruyeron, ya no puedo recordarlo.
-Tú, que estás leyendo esta nota, probablemente te encuentres en la misma situación.
-Voy a anotar aquí lo que ha sucedido en este laberinto.
-Había otras personas explorando el laberinto conmigo, pero una de ellas fue atrapada por un monstruo alto, con traje y de piel roja.
-Huí lo antes posible, así que no sé qué fue de esa persona después de eso.
-Ahora estoy escondido organizando la situación e intentando analizar las características de ese monstruo a mi manera.
-En cuanto a la persona que fue atrapada, no pudo soportar el miedo, entró en pánico, corrió e hizo mucho ruido.
-Esa fue probablemente la razón por la que el monstruo la descubrió.
-Además, una vez encendí mi linterna por accidente cerca del monstruo, pero como no pareció detectar la luz deslumbrante, mi ubicación no quedó al descubierto.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Canto-Pranto, o Errante</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Gostaria de dizer o meu nome... mas, como ele foi destruído, não consigo mais me lembrar.
-Você, que está lendo este bilhete, provavelmente está na mesma situação.
-Vou anotar aqui o que aconteceu neste labirinto.
-Havia outras pessoas explorando o labirinto além de mim, mas uma delas foi pega por um monstro alto, de terno e pele vermelha.
-Fui o primeiro a fugir, então não sei o que aconteceu com ela depois disso.
-Agora estou escondido tentando organizar a situação e analisando as características daquele monstro à minha maneira.
-Em relação à pessoa que foi pega, ela não aguentou o medo, entrou em pânico, saiu correndo e fez muito barulho.
-Essa provavelmente foi a razão pela qual o monstro a encontrou.
-Além disso, uma vez acendi minha lanterna sem querer perto dele, mas, talvez por ele não conseguir detectar a luz forte, minha localização não foi descoberta.</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1683,12 +1611,45 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せないんだ。
-このメモを読んでいる君と同じ状況だろう。この迷宮で起こった出来事をここにメモする。
-俺の他に何人か迷宮を探索している人がいたが、そのうちの1人が長身でスーツ姿の肌が赤い化け物に捕まっちまった。
-俺はいち早く逃げたが、そいつがその後どうなったかは分からない。
-今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
-まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。化け物に見つかった原因は恐らくそれだろう。また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
+    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せない。そのため、この迷宮で起こった出来事をここにメモする。
+何人かで迷宮を探索していたが、そのうちの1人がスーツ姿の肌が赤い化け物に捕まってしまった。俺はいち早く逃げたが、そいつがその後どうなったかは分からない。今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
+まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。見つかった原因は恐らくそれだろう。また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I'd like to say "My name is...", but I discarded my name and can no longer remember it. So, I will record the events that happened in this labyrinth here.
+I was exploring the labyrinth with a few others, but one of us was caught by a red-skinned monster in a suit. I fled immediately, so I don't know what became of them. As I organize the situation while hiding, I'll try to analyze the characteristics of that monster in my own way.
+First, regarding the person who was caught, they couldn't endure the terror, panicked, ran around, and made loud noises. That was likely why they were spotted. Also, I once accidentally turned on my light near the monster, but because it couldn't detect the blinding light, my position wasn't exposed.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想说“我的名字叫……”，但因为抛弃了名字，我已经想不起来了。因此，我在此记录下在这个迷宫里发生的事情。
+我之前和几个人一起在迷宫里探索，但其中一个人被一个穿西装、红皮肤的怪物抓住了。我第一时间逃跑了，所以不知道那个人后来怎么样了。现在我边躲藏边整理情况，顺便按照我自己的理解分析一下那个怪物的特征。
+首先是关于那个被抓住的人，他因为无法忍受恐惧而陷入恐慌，到处乱跑并发出很大的声音。这恐怕就是被发现的原因。另外，我曾经有一次在怪物附近不小心点亮了手电筒，但也许是因为它无法察觉眩目的光线，我的位置并没有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想說「我的名字叫……」，但因為拋棄了名字，我已经想不起來了。因此，我在此記錄下在這個迷宮裡發生的事情。
+我之前和幾個人一起在迷宮裡探索，但其中一個人被一個穿西裝、紅皮膚的怪物抓住了。我第一時間逃跑了，所以不知道那個人後來怎麼樣了。現在我邊躲藏邊整理情況，順便按照我自己的理解分析一下那個怪物的特徵。
+首先是關於那個被抓住的人，他因為無法忍受恐懼而陷入恐慌，到處亂跑並發出很大的聲音。這恐怕就是被發現的原因。另外，我曾經有一次在怪物附近不小心點亮了手電筒，但也許是因為它無法察覺眩目的光線，我的位置並沒有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Me gustaría decir "Mi nombre es...", pero como deseché mi nombre, ya no puedo recordarlo. Por lo tanto, dejaré anotados aquí los acontecimientos que ocurrieron en este laberinto.
+Estaba explorando el laberinto con varias personas, pero una de ellas fue atrapada por un monstruo de piel roja en traje. Huí de inmediato, así que no sé qué fue de esa persona. Mientras me escondo y pongo en orden la situación, intentaré analizar las características de ese monstruo a mi manera.
+En primer lugar, sobre la persona atrapada: no pudo soportar el terror, entró en pánico, corrió e hizo ruidos fuertes. Probablemente esa fue la razón por la que la descubrieron. Además, una vez encendí mi linterna por accidente cerca del monstruo, pero como no pudo detectar la luz deslumbrante, no descubrió mi ubicación.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eu gostaria de dizer "Meu nome é...", mas como descartei meu nome, já não consigo me lembrar dele. Por isso, deixarei anotados aqui os acontecimentos que ocorreram neste labirinto.
+Eu estava explorando o labirinto com algumas pessoas, mas uma delas foi pega por um monstro de pele vermelha vestindo terno. Eu fugi imediatamente, então não sei o que aconteceu com ela. Enquanto me escondo e organizo a situação, tentarei analisar as características daquele monstro do meu jeito.
+Primeiro, em relação à pessoa que foi pega: ela não aguentou o terror, entrou em pânico, correu e fez barulhos altos. Essa provavelmente foi a razão de ter sido descoberta. Além disso, uma vez acendi minha lanterna por acidente perto do monstro, mas como ele não conseguiu detectar a luz cegante, meu paradeiro não foi revelado.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
+俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
+姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4854,7 +4815,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="409.6">
+    <row r="29" spans="1:36" ht="409.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4886,10 +4847,10 @@
         <v>16</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="M29" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N29" s="1">
         <v>1</v>
@@ -4898,70 +4859,70 @@
         <v>0</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q29" s="1">
         <v>16</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="S29" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="U29" s="1">
         <v>16</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="W29" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Y29" s="1">
         <v>16</v>
       </c>
       <c r="Z29" s="8" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="AA29" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AC29" s="1">
         <v>16</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="AE29" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG29" s="1">
         <v>16</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="AI29" s="1">
         <v>10</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36" ht="409.6">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -4993,10 +4954,10 @@
         <v>16</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M30" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N30" s="1">
         <v>1</v>
@@ -5005,67 +4966,67 @@
         <v>0</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q30" s="1">
         <v>16</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="S30" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="U30" s="1">
         <v>16</v>
       </c>
       <c r="V30" s="8" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="W30" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Y30" s="1">
         <v>16</v>
       </c>
       <c r="Z30" s="8" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="AA30" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AC30" s="1">
         <v>16</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="AE30" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG30" s="1">
         <v>16</v>
       </c>
       <c r="AH30" s="1" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="AI30" s="1">
         <v>10</v>
       </c>
       <c r="AJ30" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:36" ht="409.5">
@@ -5094,7 +5055,7 @@
         <v>2</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="K31" s="1">
         <v>16</v>
@@ -5112,67 +5073,67 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="Q31" s="1">
         <v>16</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="S31" s="1">
         <v>10</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="U31" s="1">
         <v>16</v>
       </c>
       <c r="V31" s="8" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="W31" s="1">
         <v>10</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="Y31" s="1">
         <v>16</v>
       </c>
       <c r="Z31" s="9" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="AA31" s="1">
         <v>10</v>
       </c>
       <c r="AB31" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AC31" s="1">
         <v>16</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="AE31" s="1">
         <v>10</v>
       </c>
       <c r="AF31" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AG31" s="1">
         <v>16</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AI31" s="1">
         <v>10</v>
       </c>
       <c r="AJ31" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="32" spans="1:36" ht="375">
@@ -5201,13 +5162,13 @@
         <v>3</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K32" s="1">
         <v>16</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="M32" s="1">
         <v>10</v>
@@ -5219,67 +5180,67 @@
         <v>0</v>
       </c>
       <c r="P32" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="Q32" s="1">
         <v>16</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="S32" s="1">
         <v>10</v>
       </c>
       <c r="T32" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="U32" s="1">
         <v>16</v>
       </c>
       <c r="V32" s="8" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="W32" s="1">
         <v>10</v>
       </c>
       <c r="X32" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="Y32" s="1">
         <v>16</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AA32" s="1">
         <v>10</v>
       </c>
       <c r="AB32" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AC32" s="1">
         <v>16</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AE32" s="1">
         <v>10</v>
       </c>
       <c r="AF32" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG32" s="1">
         <v>16</v>
       </c>
       <c r="AH32" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AI32" s="1">
         <v>10</v>
       </c>
       <c r="AJ32" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04296982-097B-4F91-AEDD-F126B9B57688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7521F8-42A7-4059-9CDE-0D9D3706DD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5064,7 +5064,7 @@
         <v>387</v>
       </c>
       <c r="M31" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N31" s="1">
         <v>1</v>
@@ -5082,7 +5082,7 @@
         <v>369</v>
       </c>
       <c r="S31" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>359</v>
@@ -5094,7 +5094,7 @@
         <v>370</v>
       </c>
       <c r="W31" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="X31" s="5" t="s">
         <v>360</v>
@@ -5106,7 +5106,7 @@
         <v>371</v>
       </c>
       <c r="AA31" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB31" t="s">
         <v>361</v>
@@ -5118,7 +5118,7 @@
         <v>372</v>
       </c>
       <c r="AE31" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="s">
         <v>362</v>
@@ -5130,7 +5130,7 @@
         <v>373</v>
       </c>
       <c r="AI31" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ31" s="1" t="s">
         <v>363</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7521F8-42A7-4059-9CDE-0D9D3706DD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCFCDBF-507D-42BE-9E25-FA4F2D5A1F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="389">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1650,6 +1650,10 @@
     <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
 俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
 姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>demoStatus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2028,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ1002"/>
+  <dimension ref="A1:AK1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2038,36 +2042,36 @@
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="14.875" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="27.625" customWidth="1"/>
-    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.375" customWidth="1"/>
-    <col min="12" max="12" width="22.375" customWidth="1"/>
-    <col min="13" max="13" width="26.25" customWidth="1"/>
-    <col min="14" max="14" width="9.625" customWidth="1"/>
-    <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="16" max="16" width="31.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.375" customWidth="1"/>
-    <col min="18" max="18" width="20.625" customWidth="1"/>
-    <col min="19" max="19" width="23.875" customWidth="1"/>
-    <col min="20" max="20" width="24.75" customWidth="1"/>
-    <col min="21" max="21" width="24.875" customWidth="1"/>
-    <col min="22" max="22" width="26.375" customWidth="1"/>
-    <col min="23" max="23" width="32" customWidth="1"/>
-    <col min="24" max="24" width="19" customWidth="1"/>
-    <col min="25" max="25" width="22.5" customWidth="1"/>
-    <col min="26" max="26" width="23.625" customWidth="1"/>
-    <col min="27" max="27" width="28.375" customWidth="1"/>
-    <col min="28" max="28" width="21" customWidth="1"/>
-    <col min="29" max="29" width="23.125" customWidth="1"/>
-    <col min="30" max="30" width="24.875" customWidth="1"/>
-    <col min="31" max="31" width="26" customWidth="1"/>
-    <col min="32" max="32" width="31.875" customWidth="1"/>
-    <col min="33" max="33" width="28.5" customWidth="1"/>
-    <col min="34" max="34" width="28.25" customWidth="1"/>
-    <col min="35" max="35" width="31.375" customWidth="1"/>
+    <col min="9" max="10" width="27.625" customWidth="1"/>
+    <col min="11" max="11" width="26.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.375" customWidth="1"/>
+    <col min="13" max="13" width="22.375" customWidth="1"/>
+    <col min="14" max="14" width="26.25" customWidth="1"/>
+    <col min="15" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="14.875" customWidth="1"/>
+    <col min="17" max="17" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
+    <col min="19" max="19" width="20.625" customWidth="1"/>
+    <col min="20" max="20" width="23.875" customWidth="1"/>
+    <col min="21" max="21" width="24.75" customWidth="1"/>
+    <col min="22" max="22" width="24.875" customWidth="1"/>
+    <col min="23" max="23" width="26.375" customWidth="1"/>
+    <col min="24" max="24" width="32" customWidth="1"/>
+    <col min="25" max="25" width="19" customWidth="1"/>
+    <col min="26" max="26" width="22.5" customWidth="1"/>
+    <col min="27" max="27" width="23.625" customWidth="1"/>
+    <col min="28" max="28" width="28.375" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="30" width="23.125" customWidth="1"/>
+    <col min="31" max="31" width="24.875" customWidth="1"/>
+    <col min="32" max="32" width="26" customWidth="1"/>
+    <col min="33" max="33" width="31.875" customWidth="1"/>
+    <col min="34" max="34" width="28.5" customWidth="1"/>
+    <col min="35" max="35" width="28.25" customWidth="1"/>
+    <col min="36" max="36" width="31.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2095,95 +2099,98 @@
       <c r="I1" t="s">
         <v>349</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
+        <v>388</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
       <c r="Q1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>154</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>155</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>156</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>157</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>189</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>190</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>191</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>192</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>193</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>194</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>195</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>196</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>234</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>235</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>236</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>237</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:36" ht="409.5">
+    <row r="3" spans="1:37" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2208,89 +2215,92 @@
       <c r="I3">
         <v>99999</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>13</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>12</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>11</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="U3" s="4">
-        <v>14</v>
-      </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="4">
+        <v>14</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="W3" s="4">
+      <c r="X3" s="4">
         <v>13</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="Y3" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="5" t="s">
+      <c r="Z3" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA3" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AB3" s="6">
         <v>13</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>12</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>11</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>12</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AI3" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AI3">
+      <c r="AJ3">
         <v>11</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AK3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="228" customHeight="1">
+    <row r="4" spans="1:37" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2315,89 +2325,92 @@
       <c r="I4">
         <v>99999</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K4">
-        <v>14</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="M4">
-        <v>14</v>
-      </c>
       <c r="N4">
+        <v>14</v>
+      </c>
+      <c r="O4">
         <v>1</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
         <v>20</v>
       </c>
-      <c r="Q4">
-        <v>14</v>
-      </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4">
+        <v>14</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S4">
-        <v>14</v>
-      </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4">
+        <v>14</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="U4" s="4">
-        <v>14</v>
-      </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="4">
+        <v>14</v>
+      </c>
+      <c r="W4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="W4" s="4">
-        <v>14</v>
-      </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="Y4" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="AA4" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AB4" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC4" t="s">
         <v>198</v>
       </c>
-      <c r="AC4">
-        <v>14</v>
-      </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AD4">
+        <v>14</v>
+      </c>
+      <c r="AE4" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AE4">
-        <v>14</v>
-      </c>
-      <c r="AF4" t="s">
+      <c r="AF4">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="s">
         <v>239</v>
       </c>
-      <c r="AG4">
-        <v>14</v>
-      </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4">
+        <v>14</v>
+      </c>
+      <c r="AI4" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AI4">
-        <v>14</v>
-      </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4">
+        <v>14</v>
+      </c>
+      <c r="AK4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="92.25" customHeight="1">
+    <row r="5" spans="1:37" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2422,89 +2435,92 @@
       <c r="I5">
         <v>99999</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K5">
-        <v>14</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5">
+        <v>14</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M5">
-        <v>14</v>
-      </c>
       <c r="N5">
+        <v>14</v>
+      </c>
+      <c r="O5">
         <v>1</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
         <v>24</v>
       </c>
-      <c r="Q5">
-        <v>14</v>
-      </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5">
+        <v>14</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S5">
-        <v>14</v>
-      </c>
-      <c r="T5" s="3" t="s">
+      <c r="T5">
+        <v>14</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="U5" s="4">
-        <v>14</v>
-      </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="4">
+        <v>14</v>
+      </c>
+      <c r="W5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="W5" s="4">
-        <v>14</v>
-      </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="Y5" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z5" s="5" t="s">
+      <c r="Z5" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="AA5" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AB5" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC5" t="s">
         <v>200</v>
       </c>
-      <c r="AC5">
-        <v>14</v>
-      </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="AE5">
-        <v>14</v>
-      </c>
-      <c r="AF5" t="s">
+      <c r="AF5">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="s">
         <v>241</v>
       </c>
-      <c r="AG5">
-        <v>14</v>
-      </c>
-      <c r="AH5" s="1" t="s">
+      <c r="AH5">
+        <v>14</v>
+      </c>
+      <c r="AI5" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AI5">
-        <v>14</v>
-      </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5">
+        <v>14</v>
+      </c>
+      <c r="AK5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="37.5">
+    <row r="6" spans="1:37" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2529,94 +2545,97 @@
       <c r="I6">
         <v>99999</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K6">
-        <v>14</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M6">
-        <v>14</v>
-      </c>
       <c r="N6">
+        <v>14</v>
+      </c>
+      <c r="O6">
         <v>1</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
         <v>27</v>
       </c>
-      <c r="Q6">
-        <v>14</v>
-      </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6">
+        <v>14</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S6">
-        <v>14</v>
-      </c>
-      <c r="T6" s="3" t="s">
+      <c r="T6">
+        <v>14</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="U6" s="4">
-        <v>14</v>
-      </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="4">
+        <v>14</v>
+      </c>
+      <c r="W6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="W6" s="4">
-        <v>14</v>
-      </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="Y6" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z6" s="5" t="s">
+      <c r="Z6" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="AA6" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB6" t="s">
+      <c r="AB6" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC6" t="s">
         <v>202</v>
       </c>
-      <c r="AC6">
-        <v>14</v>
-      </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AD6">
+        <v>14</v>
+      </c>
+      <c r="AE6" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AE6">
-        <v>14</v>
-      </c>
-      <c r="AF6" t="s">
+      <c r="AF6">
+        <v>14</v>
+      </c>
+      <c r="AG6" t="s">
         <v>243</v>
       </c>
-      <c r="AG6">
-        <v>14</v>
-      </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AH6">
+        <v>14</v>
+      </c>
+      <c r="AI6" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AI6">
-        <v>14</v>
-      </c>
-      <c r="AJ6" t="s">
+      <c r="AJ6">
+        <v>14</v>
+      </c>
+      <c r="AK6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="56.25">
+    <row r="8" spans="1:37" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2641,89 +2660,92 @@
       <c r="I8">
         <v>99999</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K8">
-        <v>14</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8">
+        <v>14</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
       <c r="N8">
+        <v>14</v>
+      </c>
+      <c r="O8">
         <v>1</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
         <v>30</v>
       </c>
-      <c r="Q8">
-        <v>14</v>
-      </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8">
+        <v>14</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S8">
-        <v>14</v>
-      </c>
-      <c r="T8" s="3" t="s">
+      <c r="T8">
+        <v>14</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="U8" s="4">
-        <v>14</v>
-      </c>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="4">
+        <v>14</v>
+      </c>
+      <c r="W8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="W8" s="4">
-        <v>14</v>
-      </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="Y8" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z8" s="5" t="s">
+      <c r="Z8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA8" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="AA8" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AB8" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="s">
         <v>204</v>
       </c>
-      <c r="AC8">
-        <v>14</v>
-      </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AD8">
+        <v>14</v>
+      </c>
+      <c r="AE8" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AE8">
-        <v>14</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="s">
         <v>245</v>
       </c>
-      <c r="AG8">
-        <v>14</v>
-      </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AH8">
+        <v>14</v>
+      </c>
+      <c r="AI8" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AI8">
-        <v>14</v>
-      </c>
-      <c r="AJ8" t="s">
+      <c r="AJ8">
+        <v>14</v>
+      </c>
+      <c r="AK8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="297.75" customHeight="1">
+    <row r="9" spans="1:37" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2748,89 +2770,92 @@
       <c r="I9">
         <v>99999</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K9">
-        <v>14</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9">
+        <v>14</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M9">
-        <v>14</v>
-      </c>
       <c r="N9">
+        <v>14</v>
+      </c>
+      <c r="O9">
         <v>1</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q9">
-        <v>14</v>
-      </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9">
+        <v>14</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S9">
-        <v>14</v>
-      </c>
-      <c r="T9" s="3" t="s">
+      <c r="T9">
+        <v>14</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="U9" s="4">
-        <v>14</v>
-      </c>
-      <c r="V9" s="3" t="s">
+      <c r="V9" s="4">
+        <v>14</v>
+      </c>
+      <c r="W9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="W9" s="4">
-        <v>14</v>
-      </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="Y9" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z9" s="5" t="s">
+      <c r="Z9" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA9" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="AA9" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB9" s="1" t="s">
+      <c r="AB9" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AC9">
-        <v>14</v>
-      </c>
-      <c r="AD9" s="1" t="s">
+      <c r="AD9">
+        <v>14</v>
+      </c>
+      <c r="AE9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="AE9">
-        <v>14</v>
-      </c>
-      <c r="AF9" s="1" t="s">
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9" s="1" t="s">
+      <c r="AH9">
+        <v>14</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AI9">
-        <v>14</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
+      <c r="AJ9">
+        <v>14</v>
+      </c>
+      <c r="AK9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="56.25">
+    <row r="10" spans="1:37" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2855,89 +2880,92 @@
       <c r="I10">
         <v>99999</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K10">
-        <v>14</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10">
+        <v>14</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="M10">
-        <v>14</v>
-      </c>
       <c r="N10">
+        <v>14</v>
+      </c>
+      <c r="O10">
         <v>1</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="s">
         <v>35</v>
       </c>
-      <c r="Q10">
-        <v>14</v>
-      </c>
-      <c r="R10" s="1" t="s">
+      <c r="R10">
+        <v>14</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S10">
-        <v>14</v>
-      </c>
-      <c r="T10" s="3" t="s">
+      <c r="T10">
+        <v>14</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="U10" s="4">
-        <v>14</v>
-      </c>
-      <c r="V10" s="3" t="s">
+      <c r="V10" s="4">
+        <v>14</v>
+      </c>
+      <c r="W10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="W10" s="4">
-        <v>14</v>
-      </c>
-      <c r="X10" s="5" t="s">
+      <c r="X10" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y10" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="Y10" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z10" s="5" t="s">
+      <c r="Z10" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA10" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="AA10" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB10" t="s">
+      <c r="AB10" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC10" t="s">
         <v>208</v>
       </c>
-      <c r="AC10">
-        <v>14</v>
-      </c>
-      <c r="AD10" s="1" t="s">
+      <c r="AD10">
+        <v>14</v>
+      </c>
+      <c r="AE10" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AE10">
-        <v>14</v>
-      </c>
-      <c r="AF10" t="s">
+      <c r="AF10">
+        <v>14</v>
+      </c>
+      <c r="AG10" t="s">
         <v>248</v>
       </c>
-      <c r="AG10">
-        <v>14</v>
-      </c>
-      <c r="AH10" s="1" t="s">
+      <c r="AH10">
+        <v>14</v>
+      </c>
+      <c r="AI10" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AI10">
-        <v>14</v>
-      </c>
-      <c r="AJ10" t="s">
+      <c r="AJ10">
+        <v>14</v>
+      </c>
+      <c r="AK10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="37.5">
+    <row r="11" spans="1:37" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2962,89 +2990,92 @@
       <c r="I11">
         <v>99999</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K11">
-        <v>14</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11">
+        <v>14</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M11">
-        <v>14</v>
-      </c>
       <c r="N11">
+        <v>14</v>
+      </c>
+      <c r="O11">
         <v>1</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="s">
         <v>27</v>
       </c>
-      <c r="Q11">
-        <v>14</v>
-      </c>
-      <c r="R11" s="1" t="s">
+      <c r="R11">
+        <v>14</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="S11">
-        <v>14</v>
-      </c>
-      <c r="T11" s="3" t="s">
+      <c r="T11">
+        <v>14</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="U11" s="4">
-        <v>14</v>
-      </c>
-      <c r="V11" s="3" t="s">
+      <c r="V11" s="4">
+        <v>14</v>
+      </c>
+      <c r="W11" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="W11" s="4">
-        <v>14</v>
-      </c>
-      <c r="X11" s="5" t="s">
+      <c r="X11" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y11" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="Y11" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z11" s="5" t="s">
+      <c r="Z11" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="AA11" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB11" t="s">
+      <c r="AB11" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC11" t="s">
         <v>202</v>
       </c>
-      <c r="AC11">
-        <v>14</v>
-      </c>
-      <c r="AD11" s="1" t="s">
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="AE11">
-        <v>14</v>
-      </c>
-      <c r="AF11" t="s">
+      <c r="AF11">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="s">
         <v>243</v>
       </c>
-      <c r="AG11">
-        <v>14</v>
-      </c>
-      <c r="AH11" s="1" t="s">
+      <c r="AH11">
+        <v>14</v>
+      </c>
+      <c r="AI11" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AI11">
-        <v>14</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
+      <c r="AJ11">
+        <v>14</v>
+      </c>
+      <c r="AK11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="56.25">
+    <row r="12" spans="1:37" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3070,89 +3101,92 @@
       <c r="I12">
         <v>99999</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K12">
-        <v>14</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12">
+        <v>14</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="M12">
-        <v>14</v>
-      </c>
       <c r="N12">
+        <v>14</v>
+      </c>
+      <c r="O12">
         <v>1</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="s">
         <v>30</v>
       </c>
-      <c r="Q12">
-        <v>14</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="R12">
+        <v>14</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S12">
-        <v>14</v>
-      </c>
-      <c r="T12" s="3" t="s">
+      <c r="T12">
+        <v>14</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="U12" s="4">
-        <v>14</v>
-      </c>
-      <c r="V12" s="3" t="s">
+      <c r="V12" s="4">
+        <v>14</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="W12" s="4">
-        <v>14</v>
-      </c>
-      <c r="X12" s="5" t="s">
+      <c r="X12" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y12" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="Y12" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z12" s="5" t="s">
+      <c r="Z12" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA12" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="AA12" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB12" t="s">
+      <c r="AB12" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="s">
         <v>204</v>
       </c>
-      <c r="AC12">
-        <v>14</v>
-      </c>
-      <c r="AD12" s="1" t="s">
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="AE12">
-        <v>14</v>
-      </c>
-      <c r="AF12" t="s">
+      <c r="AF12">
+        <v>14</v>
+      </c>
+      <c r="AG12" t="s">
         <v>245</v>
       </c>
-      <c r="AG12">
-        <v>14</v>
-      </c>
-      <c r="AH12" s="1" t="s">
+      <c r="AH12">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AI12">
-        <v>14</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
+      <c r="AJ12">
+        <v>14</v>
+      </c>
+      <c r="AK12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="225" customHeight="1">
+    <row r="13" spans="1:37" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3180,89 +3214,92 @@
       <c r="I13">
         <v>99999</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K13">
-        <v>14</v>
-      </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13">
+        <v>14</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>12</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>1</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>60</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>38</v>
       </c>
-      <c r="Q13">
-        <v>14</v>
-      </c>
-      <c r="R13" s="1" t="s">
+      <c r="R13">
+        <v>14</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>10</v>
       </c>
-      <c r="T13" s="3" t="s">
+      <c r="U13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="U13" s="4">
-        <v>14</v>
-      </c>
-      <c r="V13" s="3" t="s">
+      <c r="V13" s="4">
+        <v>14</v>
+      </c>
+      <c r="W13" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="W13" s="4">
+      <c r="X13" s="4">
         <v>12</v>
       </c>
-      <c r="X13" s="5" t="s">
+      <c r="Y13" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="Y13" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z13" s="5" t="s">
+      <c r="Z13" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA13" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AA13" s="6">
+      <c r="AB13" s="6">
         <v>12</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>210</v>
       </c>
-      <c r="AC13">
-        <v>14</v>
-      </c>
-      <c r="AD13" s="1" t="s">
+      <c r="AD13">
+        <v>14</v>
+      </c>
+      <c r="AE13" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>10</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AG13" t="s">
         <v>250</v>
       </c>
-      <c r="AG13">
-        <v>14</v>
-      </c>
-      <c r="AH13" s="1" t="s">
+      <c r="AH13">
+        <v>14</v>
+      </c>
+      <c r="AI13" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <v>10</v>
       </c>
-      <c r="AJ13" s="1" t="s">
+      <c r="AK13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="252" customHeight="1">
+    <row r="14" spans="1:37" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3288,89 +3325,92 @@
       <c r="I14">
         <v>99999</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="1">
-        <v>14</v>
-      </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="1">
+        <v>14</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1">
         <v>12</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>1</v>
       </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="s">
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q14" s="1">
-        <v>14</v>
-      </c>
-      <c r="R14" s="1" t="s">
+      <c r="R14" s="1">
+        <v>14</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <v>12</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="U14" s="4">
-        <v>14</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="V14" s="4">
+        <v>14</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="W14" s="4">
+      <c r="X14" s="4">
         <v>12</v>
       </c>
-      <c r="X14" s="5" t="s">
+      <c r="Y14" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="Y14" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z14" s="5" t="s">
+      <c r="Z14" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA14" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AB14" s="6">
         <v>12</v>
       </c>
-      <c r="AB14" s="1" t="s">
+      <c r="AC14" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="AC14">
-        <v>14</v>
-      </c>
-      <c r="AD14" s="1" t="s">
+      <c r="AD14">
+        <v>14</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>12</v>
       </c>
-      <c r="AF14" s="1" t="s">
+      <c r="AG14" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AG14">
-        <v>14</v>
-      </c>
-      <c r="AH14" s="1" t="s">
+      <c r="AH14">
+        <v>14</v>
+      </c>
+      <c r="AI14" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>12</v>
       </c>
-      <c r="AJ14" s="1" t="s">
+      <c r="AK14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="56.25">
+    <row r="15" spans="1:37" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3396,29 +3436,32 @@
       <c r="I15">
         <v>99999</v>
       </c>
-      <c r="K15" s="1">
-        <v>14</v>
-      </c>
-      <c r="M15" s="1">
-        <v>14</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>14</v>
-      </c>
-      <c r="S15" s="1">
-        <v>14</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>14</v>
+      </c>
+      <c r="N15" s="1">
+        <v>14</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>14</v>
+      </c>
+      <c r="T15" s="1">
+        <v>14</v>
+      </c>
+      <c r="AK15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="56.25">
+    <row r="16" spans="1:37" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3444,89 +3487,92 @@
       <c r="I16">
         <v>99999</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K16" s="1">
-        <v>14</v>
-      </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="1">
+        <v>14</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M16" s="1">
-        <v>14</v>
-      </c>
-      <c r="N16">
+      <c r="N16" s="1">
+        <v>14</v>
+      </c>
+      <c r="O16">
         <v>1</v>
       </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="s">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Q16" s="1">
-        <v>14</v>
-      </c>
-      <c r="R16" s="1" t="s">
+      <c r="R16" s="1">
+        <v>14</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S16" s="1">
-        <v>14</v>
-      </c>
-      <c r="T16" s="3" t="s">
+      <c r="T16" s="1">
+        <v>14</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="U16" s="4">
-        <v>14</v>
-      </c>
-      <c r="V16" s="3" t="s">
+      <c r="V16" s="4">
+        <v>14</v>
+      </c>
+      <c r="W16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="W16" s="4">
-        <v>14</v>
-      </c>
-      <c r="X16" s="5" t="s">
+      <c r="X16" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="Y16" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z16" s="5" t="s">
+      <c r="Z16" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA16" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="AA16" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AB16" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AC16">
-        <v>14</v>
-      </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AE16">
-        <v>14</v>
-      </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AF16">
+        <v>14</v>
+      </c>
+      <c r="AG16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="AG16">
-        <v>14</v>
-      </c>
-      <c r="AH16" s="1" t="s">
+      <c r="AH16">
+        <v>14</v>
+      </c>
+      <c r="AI16" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AI16">
-        <v>14</v>
-      </c>
-      <c r="AJ16" t="s">
+      <c r="AJ16">
+        <v>14</v>
+      </c>
+      <c r="AK16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="56.25">
+    <row r="17" spans="1:37" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3552,89 +3598,92 @@
       <c r="I17">
         <v>99999</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="1">
-        <v>14</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="1">
+        <v>14</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="M17" s="1">
-        <v>14</v>
-      </c>
-      <c r="N17">
+      <c r="N17" s="1">
+        <v>14</v>
+      </c>
+      <c r="O17">
         <v>1</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1" t="s">
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Q17" s="1">
-        <v>14</v>
-      </c>
-      <c r="R17" s="1" t="s">
+      <c r="R17" s="1">
+        <v>14</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="S17" s="1">
-        <v>14</v>
-      </c>
-      <c r="T17" s="3" t="s">
+      <c r="T17" s="1">
+        <v>14</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="U17" s="4">
-        <v>14</v>
-      </c>
-      <c r="V17" s="3" t="s">
+      <c r="V17" s="4">
+        <v>14</v>
+      </c>
+      <c r="W17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="W17" s="4">
-        <v>14</v>
-      </c>
-      <c r="X17" s="5" t="s">
+      <c r="X17" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="Y17" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z17" s="5" t="s">
+      <c r="Z17" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="AA17" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB17" s="1" t="s">
+      <c r="AB17" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AC17">
-        <v>14</v>
-      </c>
-      <c r="AD17" s="1" t="s">
+      <c r="AD17">
+        <v>14</v>
+      </c>
+      <c r="AE17" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AE17">
-        <v>14</v>
-      </c>
-      <c r="AF17" s="1" t="s">
+      <c r="AF17">
+        <v>14</v>
+      </c>
+      <c r="AG17" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AG17">
-        <v>14</v>
-      </c>
-      <c r="AH17" s="1" t="s">
+      <c r="AH17">
+        <v>14</v>
+      </c>
+      <c r="AI17" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AI17">
-        <v>14</v>
-      </c>
-      <c r="AJ17" t="s">
+      <c r="AJ17">
+        <v>14</v>
+      </c>
+      <c r="AK17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="56.25">
+    <row r="18" spans="1:37" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3659,89 +3708,92 @@
       <c r="I18">
         <v>99999</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="K18" s="1">
-        <v>14</v>
-      </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" s="1">
+        <v>14</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="M18" s="1">
-        <v>14</v>
-      </c>
-      <c r="N18">
+      <c r="N18" s="1">
+        <v>14</v>
+      </c>
+      <c r="O18">
         <v>1</v>
       </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1" t="s">
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="R18" s="1">
         <v>12</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="S18" s="1">
-        <v>14</v>
-      </c>
-      <c r="T18" s="3" t="s">
+      <c r="T18" s="1">
+        <v>14</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="U18" s="4">
-        <v>14</v>
-      </c>
-      <c r="V18" s="3" t="s">
+      <c r="V18" s="4">
+        <v>14</v>
+      </c>
+      <c r="W18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W18" s="4">
-        <v>14</v>
-      </c>
-      <c r="X18" s="5" t="s">
+      <c r="X18" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y18" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="Y18" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z18" s="5" t="s">
+      <c r="Z18" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA18" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="AA18" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="1" t="s">
+      <c r="AB18" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC18" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>12</v>
       </c>
-      <c r="AD18" s="1" t="s">
+      <c r="AE18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="AE18">
-        <v>14</v>
-      </c>
-      <c r="AF18" s="1" t="s">
+      <c r="AF18">
+        <v>14</v>
+      </c>
+      <c r="AG18" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>12</v>
       </c>
-      <c r="AH18" s="1" t="s">
+      <c r="AI18" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AI18">
-        <v>14</v>
-      </c>
-      <c r="AJ18" t="s">
+      <c r="AJ18">
+        <v>14</v>
+      </c>
+      <c r="AK18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="56.25">
+    <row r="19" spans="1:37" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3767,89 +3819,92 @@
       <c r="I19">
         <v>99999</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="1">
-        <v>14</v>
-      </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" s="1">
+        <v>14</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M19" s="1">
-        <v>14</v>
-      </c>
-      <c r="N19">
+      <c r="N19" s="1">
+        <v>14</v>
+      </c>
+      <c r="O19">
         <v>1</v>
       </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="1" t="s">
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Q19" s="1">
-        <v>14</v>
-      </c>
-      <c r="R19" s="1" t="s">
+      <c r="R19" s="1">
+        <v>14</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="S19" s="1">
-        <v>14</v>
-      </c>
-      <c r="T19" s="3" t="s">
+      <c r="T19" s="1">
+        <v>14</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="U19" s="4">
-        <v>14</v>
-      </c>
-      <c r="V19" s="3" t="s">
+      <c r="V19" s="4">
+        <v>14</v>
+      </c>
+      <c r="W19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="W19" s="4">
-        <v>14</v>
-      </c>
-      <c r="X19" s="5" t="s">
+      <c r="X19" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y19" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="Y19" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z19" s="5" t="s">
+      <c r="Z19" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA19" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="AA19" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB19" s="1" t="s">
+      <c r="AB19" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC19" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AC19">
-        <v>14</v>
-      </c>
-      <c r="AD19" s="1" t="s">
+      <c r="AD19">
+        <v>14</v>
+      </c>
+      <c r="AE19" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AE19">
-        <v>14</v>
-      </c>
-      <c r="AF19" s="1" t="s">
+      <c r="AF19">
+        <v>14</v>
+      </c>
+      <c r="AG19" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AG19">
-        <v>14</v>
-      </c>
-      <c r="AH19" s="1" t="s">
+      <c r="AH19">
+        <v>14</v>
+      </c>
+      <c r="AI19" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="AI19">
-        <v>14</v>
-      </c>
-      <c r="AJ19" t="s">
+      <c r="AJ19">
+        <v>14</v>
+      </c>
+      <c r="AK19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="56.25">
+    <row r="20" spans="1:37" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3874,89 +3929,92 @@
       <c r="I20">
         <v>99999</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="1">
-        <v>14</v>
-      </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="1">
+        <v>14</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="M20" s="1">
-        <v>14</v>
-      </c>
-      <c r="N20">
+      <c r="N20" s="1">
+        <v>14</v>
+      </c>
+      <c r="O20">
         <v>1</v>
       </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>12</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="S20" s="1">
-        <v>14</v>
-      </c>
-      <c r="T20" s="3" t="s">
+      <c r="T20" s="1">
+        <v>14</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="U20" s="4">
-        <v>14</v>
-      </c>
-      <c r="V20" s="3" t="s">
+      <c r="V20" s="4">
+        <v>14</v>
+      </c>
+      <c r="W20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="W20" s="4">
-        <v>14</v>
-      </c>
-      <c r="X20" s="5" t="s">
+      <c r="X20" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="Y20" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z20" s="5" t="s">
+      <c r="Z20" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="AA20" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB20" s="1" t="s">
+      <c r="AB20" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC20" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>12</v>
       </c>
-      <c r="AD20" s="1" t="s">
+      <c r="AE20" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AE20">
-        <v>14</v>
-      </c>
-      <c r="AF20" s="1" t="s">
+      <c r="AF20">
+        <v>14</v>
+      </c>
+      <c r="AG20" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>12</v>
       </c>
-      <c r="AH20" s="1" t="s">
+      <c r="AI20" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AI20">
-        <v>14</v>
-      </c>
-      <c r="AJ20" t="s">
+      <c r="AJ20">
+        <v>14</v>
+      </c>
+      <c r="AK20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="257.25" customHeight="1">
+    <row r="21" spans="1:37" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3984,89 +4042,92 @@
       <c r="I21">
         <v>99999</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K21" s="1">
-        <v>14</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="1">
+        <v>14</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M21" s="1">
+      <c r="N21" s="1">
         <v>12</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>1</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <v>1</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="Q21" s="1">
-        <v>14</v>
-      </c>
-      <c r="R21" s="1" t="s">
+      <c r="R21" s="1">
+        <v>14</v>
+      </c>
+      <c r="S21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <v>10</v>
       </c>
-      <c r="T21" s="3" t="s">
+      <c r="U21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="U21" s="4">
-        <v>14</v>
-      </c>
-      <c r="V21" s="3" t="s">
+      <c r="V21" s="4">
+        <v>14</v>
+      </c>
+      <c r="W21" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="W21" s="4">
+      <c r="X21" s="4">
         <v>12</v>
       </c>
-      <c r="X21" s="5" t="s">
+      <c r="Y21" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="Y21" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z21" s="5" t="s">
+      <c r="Z21" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA21" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="AA21" s="6">
+      <c r="AB21" s="6">
         <v>12</v>
       </c>
-      <c r="AB21" s="1" t="s">
+      <c r="AC21" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AC21">
-        <v>14</v>
-      </c>
-      <c r="AD21" s="1" t="s">
+      <c r="AD21">
+        <v>14</v>
+      </c>
+      <c r="AE21" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>10</v>
       </c>
-      <c r="AF21" s="1" t="s">
+      <c r="AG21" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="AG21">
-        <v>14</v>
-      </c>
-      <c r="AH21" s="1" t="s">
+      <c r="AH21">
+        <v>14</v>
+      </c>
+      <c r="AI21" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>10</v>
       </c>
-      <c r="AJ21" s="1" t="s">
+      <c r="AK21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="409.5">
+    <row r="22" spans="1:37" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4091,89 +4152,92 @@
       <c r="I22">
         <v>99999</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>12</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M22">
-        <v>14</v>
-      </c>
       <c r="N22">
+        <v>14</v>
+      </c>
+      <c r="O22">
         <v>1</v>
       </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1" t="s">
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>12</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>12</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="U22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U22" s="4">
+      <c r="V22" s="4">
         <v>12</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="W22" s="4">
-        <v>14</v>
-      </c>
-      <c r="X22" s="5" t="s">
+      <c r="X22" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y22" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="Y22" s="6">
+      <c r="Z22" s="6">
         <v>12</v>
       </c>
-      <c r="Z22" s="5" t="s">
+      <c r="AA22" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="AA22" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB22" s="1" t="s">
+      <c r="AB22" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC22" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>12</v>
       </c>
-      <c r="AD22" s="1" t="s">
+      <c r="AE22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>12</v>
       </c>
-      <c r="AF22" s="1" t="s">
+      <c r="AG22" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>12</v>
       </c>
-      <c r="AH22" s="1" t="s">
+      <c r="AI22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>12</v>
       </c>
-      <c r="AJ22" s="1" t="s">
+      <c r="AK22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="409.5">
+    <row r="23" spans="1:37" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4198,89 +4262,92 @@
       <c r="I23">
         <v>99999</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>12</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="M23" s="4">
+      <c r="N23" s="4">
         <v>12</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>1</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1" t="s">
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <v>12</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>12</v>
       </c>
-      <c r="T23" s="7" t="s">
+      <c r="U23" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="U23" s="4">
+      <c r="V23" s="4">
         <v>12</v>
       </c>
-      <c r="V23" s="8" t="s">
+      <c r="W23" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="W23" s="4">
+      <c r="X23" s="4">
         <v>12</v>
       </c>
-      <c r="X23" s="5" t="s">
+      <c r="Y23" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="Y23" s="4">
+      <c r="Z23" s="4">
         <v>12</v>
       </c>
-      <c r="Z23" s="1" t="s">
+      <c r="AA23" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AA23" s="4">
+      <c r="AB23" s="4">
         <v>12</v>
       </c>
-      <c r="AB23" s="1" t="s">
+      <c r="AC23" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>12</v>
       </c>
-      <c r="AD23" s="1" t="s">
+      <c r="AE23" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>10</v>
       </c>
-      <c r="AF23" s="1" t="s">
+      <c r="AG23" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>12</v>
       </c>
-      <c r="AH23" s="1" t="s">
+      <c r="AI23" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>10</v>
       </c>
-      <c r="AJ23" s="1" t="s">
+      <c r="AK23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="56.25">
+    <row r="24" spans="1:37" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4305,89 +4372,92 @@
       <c r="I24">
         <v>99999</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="K24" s="1">
-        <v>14</v>
-      </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="1">
+        <v>14</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="M24">
-        <v>14</v>
-      </c>
       <c r="N24">
+        <v>14</v>
+      </c>
+      <c r="O24">
         <v>1</v>
       </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1" t="s">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="Q24" s="1">
-        <v>14</v>
-      </c>
-      <c r="R24" s="1" t="s">
+      <c r="R24" s="1">
+        <v>14</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="S24" s="1">
-        <v>14</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="T24" s="1">
+        <v>14</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="U24" s="1">
-        <v>14</v>
-      </c>
-      <c r="V24" s="7" t="s">
+      <c r="V24" s="1">
+        <v>14</v>
+      </c>
+      <c r="W24" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="W24" s="1">
-        <v>14</v>
-      </c>
-      <c r="X24" s="5" t="s">
+      <c r="X24" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y24" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="Y24" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z24" s="5" t="s">
+      <c r="Z24" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA24" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="AA24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB24" s="1" t="s">
+      <c r="AB24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC24" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>12</v>
       </c>
-      <c r="AD24" s="1" t="s">
+      <c r="AE24" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="AE24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AF24" s="1" t="s">
+      <c r="AF24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AG24" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>12</v>
       </c>
-      <c r="AH24" s="1" t="s">
+      <c r="AI24" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AI24" s="6">
-        <v>14</v>
-      </c>
-      <c r="AJ24" s="1" t="s">
+      <c r="AJ24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AK24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="56.25">
+    <row r="25" spans="1:37" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4412,89 +4482,92 @@
       <c r="I25">
         <v>99999</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K25" s="1">
-        <v>14</v>
-      </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="1">
+        <v>14</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="M25">
-        <v>14</v>
-      </c>
       <c r="N25">
+        <v>14</v>
+      </c>
+      <c r="O25">
         <v>1</v>
       </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="Q25" s="1">
-        <v>14</v>
-      </c>
-      <c r="R25" s="1" t="s">
+      <c r="R25" s="1">
+        <v>14</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="S25" s="1">
-        <v>14</v>
-      </c>
-      <c r="T25" s="7" t="s">
+      <c r="T25" s="1">
+        <v>14</v>
+      </c>
+      <c r="U25" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="U25" s="1">
-        <v>14</v>
-      </c>
-      <c r="V25" s="3" t="s">
+      <c r="V25" s="1">
+        <v>14</v>
+      </c>
+      <c r="W25" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="W25" s="1">
-        <v>14</v>
-      </c>
-      <c r="X25" s="5" t="s">
+      <c r="X25" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y25" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="Y25" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z25" t="s">
+      <c r="Z25" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA25" t="s">
         <v>307</v>
       </c>
-      <c r="AA25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB25" t="s">
+      <c r="AB25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC25" t="s">
         <v>308</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>12</v>
       </c>
-      <c r="AD25" s="1" t="s">
+      <c r="AE25" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="AE25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AF25" s="1" t="s">
+      <c r="AF25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AG25" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>12</v>
       </c>
-      <c r="AH25" s="1" t="s">
+      <c r="AI25" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AI25" s="6">
-        <v>14</v>
-      </c>
-      <c r="AJ25" s="1" t="s">
+      <c r="AJ25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AK25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="75">
+    <row r="26" spans="1:37" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4519,89 +4592,92 @@
       <c r="I26">
         <v>99999</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="K26" s="1">
-        <v>14</v>
-      </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="1">
+        <v>14</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="M26">
-        <v>14</v>
-      </c>
       <c r="N26">
+        <v>14</v>
+      </c>
+      <c r="O26">
         <v>1</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26" s="1" t="s">
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="Q26" s="1">
-        <v>14</v>
-      </c>
-      <c r="R26" s="1" t="s">
+      <c r="R26" s="1">
+        <v>14</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="S26" s="1">
-        <v>14</v>
-      </c>
-      <c r="T26" s="7" t="s">
+      <c r="T26" s="1">
+        <v>14</v>
+      </c>
+      <c r="U26" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="U26" s="1">
-        <v>14</v>
-      </c>
-      <c r="V26" s="8" t="s">
+      <c r="V26" s="1">
+        <v>14</v>
+      </c>
+      <c r="W26" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="W26" s="1">
-        <v>14</v>
-      </c>
-      <c r="X26" s="5" t="s">
+      <c r="X26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y26" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="Y26" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z26" s="5" t="s">
+      <c r="Z26" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA26" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="AA26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB26" s="1" t="s">
+      <c r="AB26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>12</v>
       </c>
-      <c r="AD26" s="1" t="s">
+      <c r="AE26" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AE26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AF26" s="1" t="s">
+      <c r="AF26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AG26" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>12</v>
       </c>
-      <c r="AH26" s="1" t="s">
+      <c r="AI26" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="AI26" s="6">
-        <v>14</v>
-      </c>
-      <c r="AJ26" s="1" t="s">
+      <c r="AJ26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AK26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="56.25">
+    <row r="27" spans="1:37" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4626,89 +4702,92 @@
       <c r="I27">
         <v>99999</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K27" s="1">
-        <v>14</v>
-      </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="1">
+        <v>14</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="M27">
-        <v>14</v>
-      </c>
       <c r="N27">
+        <v>14</v>
+      </c>
+      <c r="O27">
         <v>1</v>
       </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27" s="1" t="s">
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="Q27" s="1">
-        <v>14</v>
-      </c>
-      <c r="R27" s="1" t="s">
+      <c r="R27" s="1">
+        <v>14</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="S27" s="1">
-        <v>14</v>
-      </c>
-      <c r="T27" s="7" t="s">
+      <c r="T27" s="1">
+        <v>14</v>
+      </c>
+      <c r="U27" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="U27" s="1">
-        <v>14</v>
-      </c>
-      <c r="V27" s="8" t="s">
+      <c r="V27" s="1">
+        <v>14</v>
+      </c>
+      <c r="W27" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="W27" s="1">
-        <v>14</v>
-      </c>
-      <c r="X27" s="5" t="s">
+      <c r="X27" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y27" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="Y27" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z27" s="5" t="s">
+      <c r="Z27" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA27" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="AA27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB27" s="1" t="s">
+      <c r="AB27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>12</v>
       </c>
-      <c r="AD27" s="1" t="s">
+      <c r="AE27" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="AE27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AF27" s="1" t="s">
+      <c r="AF27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AG27" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>12</v>
       </c>
-      <c r="AH27" s="1" t="s">
+      <c r="AI27" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="AI27" s="6">
-        <v>14</v>
-      </c>
-      <c r="AJ27" s="1" t="s">
+      <c r="AJ27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AK27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="75">
+    <row r="28" spans="1:37" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4733,89 +4812,92 @@
       <c r="I28">
         <v>99999</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K28" s="1">
-        <v>14</v>
-      </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="1">
+        <v>14</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="M28">
-        <v>14</v>
-      </c>
       <c r="N28">
+        <v>14</v>
+      </c>
+      <c r="O28">
         <v>1</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1" t="s">
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="Q28" s="1">
-        <v>14</v>
-      </c>
-      <c r="R28" s="1" t="s">
+      <c r="R28" s="1">
+        <v>14</v>
+      </c>
+      <c r="S28" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="S28" s="1">
-        <v>14</v>
-      </c>
-      <c r="T28" s="7" t="s">
+      <c r="T28" s="1">
+        <v>14</v>
+      </c>
+      <c r="U28" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="U28" s="1">
-        <v>14</v>
-      </c>
-      <c r="V28" s="8" t="s">
+      <c r="V28" s="1">
+        <v>14</v>
+      </c>
+      <c r="W28" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="W28" s="1">
-        <v>14</v>
-      </c>
-      <c r="X28" s="5" t="s">
+      <c r="X28" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y28" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="Y28" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z28" s="5" t="s">
+      <c r="Z28" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA28" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="AA28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB28" s="1" t="s">
+      <c r="AB28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC28" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>12</v>
       </c>
-      <c r="AD28" s="1" t="s">
+      <c r="AE28" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="AE28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AF28" s="1" t="s">
+      <c r="AF28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AG28" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>12</v>
       </c>
-      <c r="AH28" s="1" t="s">
+      <c r="AI28" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="AI28" s="6">
-        <v>14</v>
-      </c>
-      <c r="AJ28" s="1" t="s">
+      <c r="AJ28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AK28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="409.5">
+    <row r="29" spans="1:37" ht="409.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4840,89 +4922,92 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>16</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="M29" s="1">
+      <c r="N29" s="1">
         <v>12</v>
       </c>
-      <c r="N29" s="1">
+      <c r="O29" s="1">
         <v>1</v>
       </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="R29" s="1">
         <v>16</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="S29" s="1">
+      <c r="T29" s="1">
         <v>12</v>
       </c>
-      <c r="T29" s="7" t="s">
+      <c r="U29" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="U29" s="1">
+      <c r="V29" s="1">
         <v>16</v>
       </c>
-      <c r="V29" s="8" t="s">
+      <c r="W29" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="W29" s="1">
+      <c r="X29" s="1">
         <v>12</v>
       </c>
-      <c r="X29" s="5" t="s">
+      <c r="Y29" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Z29" s="1">
         <v>16</v>
       </c>
-      <c r="Z29" s="8" t="s">
+      <c r="AA29" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="AA29" s="1">
+      <c r="AB29" s="1">
         <v>12</v>
       </c>
-      <c r="AB29" s="1" t="s">
+      <c r="AC29" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="AC29" s="1">
+      <c r="AD29" s="1">
         <v>16</v>
       </c>
-      <c r="AD29" s="1" t="s">
+      <c r="AE29" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="AE29" s="1">
+      <c r="AF29" s="1">
         <v>12</v>
       </c>
-      <c r="AF29" s="1" t="s">
+      <c r="AG29" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AG29" s="1">
+      <c r="AH29" s="1">
         <v>16</v>
       </c>
-      <c r="AH29" s="1" t="s">
+      <c r="AI29" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="AI29" s="1">
+      <c r="AJ29" s="1">
         <v>10</v>
       </c>
-      <c r="AJ29" s="1" t="s">
+      <c r="AK29" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="409.5">
+    <row r="30" spans="1:37" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -4947,89 +5032,92 @@
       <c r="I30">
         <v>1</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>16</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="M30" s="1">
+      <c r="N30" s="1">
         <v>12</v>
       </c>
-      <c r="N30" s="1">
+      <c r="O30" s="1">
         <v>1</v>
       </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="1" t="s">
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="R30" s="1">
         <v>16</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="S30" s="1">
+      <c r="T30" s="1">
         <v>12</v>
       </c>
-      <c r="T30" s="7" t="s">
+      <c r="U30" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="U30" s="1">
+      <c r="V30" s="1">
         <v>16</v>
       </c>
-      <c r="V30" s="8" t="s">
+      <c r="W30" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="W30" s="1">
+      <c r="X30" s="1">
         <v>12</v>
       </c>
-      <c r="X30" s="5" t="s">
+      <c r="Y30" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="Z30" s="1">
         <v>16</v>
       </c>
-      <c r="Z30" s="8" t="s">
+      <c r="AA30" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="AA30" s="1">
+      <c r="AB30" s="1">
         <v>12</v>
       </c>
-      <c r="AB30" s="1" t="s">
+      <c r="AC30" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="AC30" s="1">
+      <c r="AD30" s="1">
         <v>16</v>
       </c>
-      <c r="AD30" s="1" t="s">
+      <c r="AE30" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="AE30" s="1">
+      <c r="AF30" s="1">
         <v>12</v>
       </c>
-      <c r="AF30" s="1" t="s">
+      <c r="AG30" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AG30" s="1">
+      <c r="AH30" s="1">
         <v>16</v>
       </c>
-      <c r="AH30" s="1" t="s">
+      <c r="AI30" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="AI30" s="1">
+      <c r="AJ30" s="1">
         <v>10</v>
       </c>
-      <c r="AJ30" s="1" t="s">
+      <c r="AK30" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="409.5">
+    <row r="31" spans="1:37" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5054,89 +5142,92 @@
       <c r="I31">
         <v>2</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>16</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="M31" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="M31" s="1">
-        <v>14</v>
-      </c>
       <c r="N31" s="1">
+        <v>14</v>
+      </c>
+      <c r="O31" s="1">
         <v>1</v>
       </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="P31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="s">
         <v>380</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="R31" s="1">
         <v>16</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="S31" s="1">
+      <c r="T31" s="1">
         <v>12</v>
       </c>
-      <c r="T31" s="3" t="s">
+      <c r="U31" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="U31" s="1">
+      <c r="V31" s="1">
         <v>16</v>
       </c>
-      <c r="V31" s="8" t="s">
+      <c r="W31" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="W31" s="1">
-        <v>14</v>
-      </c>
-      <c r="X31" s="5" t="s">
+      <c r="X31" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y31" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="Y31" s="1">
+      <c r="Z31" s="1">
         <v>16</v>
       </c>
-      <c r="Z31" s="9" t="s">
+      <c r="AA31" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="AA31" s="1">
-        <v>14</v>
-      </c>
-      <c r="AB31" t="s">
+      <c r="AB31" s="1">
+        <v>14</v>
+      </c>
+      <c r="AC31" t="s">
         <v>361</v>
       </c>
-      <c r="AC31" s="1">
+      <c r="AD31" s="1">
         <v>16</v>
       </c>
-      <c r="AD31" s="1" t="s">
+      <c r="AE31" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="AE31" s="1">
+      <c r="AF31" s="1">
         <v>12</v>
       </c>
-      <c r="AF31" t="s">
+      <c r="AG31" t="s">
         <v>362</v>
       </c>
-      <c r="AG31" s="1">
+      <c r="AH31" s="1">
         <v>16</v>
       </c>
-      <c r="AH31" s="1" t="s">
+      <c r="AI31" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AI31" s="1">
+      <c r="AJ31" s="1">
         <v>12</v>
       </c>
-      <c r="AJ31" s="1" t="s">
+      <c r="AK31" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="375">
+    <row r="32" spans="1:37" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5161,85 +5252,88 @@
       <c r="I32">
         <v>3</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>16</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="M32" s="1">
+      <c r="N32" s="1">
         <v>10</v>
       </c>
-      <c r="N32" s="1">
+      <c r="O32" s="1">
         <v>1</v>
       </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
         <v>365</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="R32" s="1">
         <v>16</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="S32" s="1">
+      <c r="T32" s="1">
         <v>10</v>
       </c>
-      <c r="T32" t="s">
+      <c r="U32" t="s">
         <v>366</v>
       </c>
-      <c r="U32" s="1">
+      <c r="V32" s="1">
         <v>16</v>
       </c>
-      <c r="V32" s="8" t="s">
+      <c r="W32" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="W32" s="1">
+      <c r="X32" s="1">
         <v>10</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Y32" t="s">
         <v>366</v>
       </c>
-      <c r="Y32" s="1">
+      <c r="Z32" s="1">
         <v>16</v>
       </c>
-      <c r="Z32" s="1" t="s">
+      <c r="AA32" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="AA32" s="1">
+      <c r="AB32" s="1">
         <v>10</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>367</v>
       </c>
-      <c r="AC32" s="1">
+      <c r="AD32" s="1">
         <v>16</v>
       </c>
-      <c r="AD32" s="1" t="s">
+      <c r="AE32" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="AE32" s="1">
+      <c r="AF32" s="1">
         <v>10</v>
       </c>
-      <c r="AF32" t="s">
+      <c r="AG32" t="s">
         <v>355</v>
       </c>
-      <c r="AG32" s="1">
+      <c r="AH32" s="1">
         <v>16</v>
       </c>
-      <c r="AH32" s="1" t="s">
+      <c r="AI32" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="AI32" s="1">
+      <c r="AJ32" s="1">
         <v>10</v>
       </c>
-      <c r="AJ32" s="1" t="s">
+      <c r="AK32" s="1" t="s">
         <v>368</v>
       </c>
     </row>
@@ -10043,22 +10137,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:36">
+    <row r="993" spans="1:37">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:36">
+    <row r="994" spans="1:37">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:36">
+    <row r="995" spans="1:37">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:36">
+    <row r="996" spans="1:37">
       <c r="A996">
         <v>994</v>
       </c>
@@ -10080,89 +10174,89 @@
       <c r="H996">
         <v>0</v>
       </c>
-      <c r="J996" s="1" t="s">
+      <c r="K996" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K996">
-        <v>14</v>
-      </c>
-      <c r="L996" t="s">
+      <c r="L996">
+        <v>14</v>
+      </c>
+      <c r="M996" t="s">
         <v>44</v>
       </c>
-      <c r="M996">
-        <v>14</v>
-      </c>
       <c r="N996">
+        <v>14</v>
+      </c>
+      <c r="O996">
         <v>1</v>
       </c>
-      <c r="O996">
-        <v>0</v>
-      </c>
-      <c r="P996" t="s">
+      <c r="P996">
+        <v>0</v>
+      </c>
+      <c r="Q996" t="s">
         <v>43</v>
       </c>
-      <c r="Q996">
-        <v>14</v>
-      </c>
-      <c r="R996" t="s">
+      <c r="R996">
+        <v>14</v>
+      </c>
+      <c r="S996" t="s">
         <v>44</v>
       </c>
-      <c r="S996">
-        <v>14</v>
-      </c>
-      <c r="T996" s="3" t="s">
+      <c r="T996">
+        <v>14</v>
+      </c>
+      <c r="U996" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="U996" s="4">
-        <v>14</v>
-      </c>
-      <c r="V996" s="4" t="s">
+      <c r="V996" s="4">
+        <v>14</v>
+      </c>
+      <c r="W996" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="W996" s="4">
-        <v>14</v>
-      </c>
-      <c r="X996" s="5" t="s">
+      <c r="X996" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y996" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="Y996" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z996" s="6" t="s">
+      <c r="Z996" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA996" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="AA996" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB996" t="s">
+      <c r="AB996" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC996" t="s">
         <v>141</v>
       </c>
-      <c r="AC996">
-        <v>14</v>
-      </c>
-      <c r="AD996" t="s">
+      <c r="AD996">
+        <v>14</v>
+      </c>
+      <c r="AE996" t="s">
         <v>228</v>
       </c>
-      <c r="AE996">
-        <v>14</v>
-      </c>
-      <c r="AF996" t="s">
+      <c r="AF996">
+        <v>14</v>
+      </c>
+      <c r="AG996" t="s">
         <v>141</v>
       </c>
-      <c r="AG996">
-        <v>14</v>
-      </c>
-      <c r="AH996" t="s">
+      <c r="AH996">
+        <v>14</v>
+      </c>
+      <c r="AI996" t="s">
         <v>266</v>
       </c>
-      <c r="AI996">
-        <v>14</v>
-      </c>
-      <c r="AJ996" t="s">
+      <c r="AJ996">
+        <v>14</v>
+      </c>
+      <c r="AK996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:36" ht="93.75">
+    <row r="997" spans="1:37" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -10187,89 +10281,89 @@
       <c r="H997">
         <v>0</v>
       </c>
-      <c r="J997" s="1" t="s">
+      <c r="K997" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K997">
-        <v>14</v>
-      </c>
-      <c r="L997" t="s">
+      <c r="L997">
+        <v>14</v>
+      </c>
+      <c r="M997" t="s">
         <v>47</v>
       </c>
-      <c r="M997">
-        <v>14</v>
-      </c>
       <c r="N997">
+        <v>14</v>
+      </c>
+      <c r="O997">
         <v>1</v>
       </c>
-      <c r="O997">
-        <v>0</v>
-      </c>
-      <c r="P997" t="s">
+      <c r="P997">
+        <v>0</v>
+      </c>
+      <c r="Q997" t="s">
         <v>48</v>
       </c>
-      <c r="Q997">
-        <v>14</v>
-      </c>
-      <c r="R997" t="s">
+      <c r="R997">
+        <v>14</v>
+      </c>
+      <c r="S997" t="s">
         <v>47</v>
       </c>
-      <c r="S997">
-        <v>14</v>
-      </c>
-      <c r="T997" s="3" t="s">
+      <c r="T997">
+        <v>14</v>
+      </c>
+      <c r="U997" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="U997" s="4">
-        <v>14</v>
-      </c>
-      <c r="V997" s="4" t="s">
+      <c r="V997" s="4">
+        <v>14</v>
+      </c>
+      <c r="W997" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="W997" s="4">
-        <v>14</v>
-      </c>
-      <c r="X997" s="5" t="s">
+      <c r="X997" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y997" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="Y997" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z997" s="6" t="s">
+      <c r="Z997" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA997" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="AA997" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB997" t="s">
+      <c r="AB997" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC997" t="s">
         <v>143</v>
       </c>
-      <c r="AC997">
-        <v>14</v>
-      </c>
-      <c r="AD997" t="s">
+      <c r="AD997">
+        <v>14</v>
+      </c>
+      <c r="AE997" t="s">
         <v>229</v>
       </c>
-      <c r="AE997">
-        <v>14</v>
-      </c>
-      <c r="AF997" t="s">
+      <c r="AF997">
+        <v>14</v>
+      </c>
+      <c r="AG997" t="s">
         <v>143</v>
       </c>
-      <c r="AG997">
-        <v>14</v>
-      </c>
-      <c r="AH997" t="s">
+      <c r="AH997">
+        <v>14</v>
+      </c>
+      <c r="AI997" t="s">
         <v>267</v>
       </c>
-      <c r="AI997">
-        <v>14</v>
-      </c>
-      <c r="AJ997" s="1" t="s">
+      <c r="AJ997">
+        <v>14</v>
+      </c>
+      <c r="AK997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:36" ht="75">
+    <row r="998" spans="1:37" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -10291,89 +10385,89 @@
       <c r="H998">
         <v>0</v>
       </c>
-      <c r="J998" s="1" t="s">
+      <c r="K998" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K998">
-        <v>14</v>
-      </c>
-      <c r="L998" s="1" t="s">
+      <c r="L998">
+        <v>14</v>
+      </c>
+      <c r="M998" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M998">
-        <v>14</v>
-      </c>
       <c r="N998">
+        <v>14</v>
+      </c>
+      <c r="O998">
         <v>1</v>
       </c>
-      <c r="O998">
-        <v>0</v>
-      </c>
-      <c r="P998" t="s">
+      <c r="P998">
+        <v>0</v>
+      </c>
+      <c r="Q998" t="s">
         <v>51</v>
       </c>
-      <c r="Q998">
-        <v>14</v>
-      </c>
-      <c r="R998" s="1" t="s">
+      <c r="R998">
+        <v>14</v>
+      </c>
+      <c r="S998" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S998">
-        <v>14</v>
-      </c>
-      <c r="T998" s="3" t="s">
+      <c r="T998">
+        <v>14</v>
+      </c>
+      <c r="U998" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="U998" s="4">
-        <v>14</v>
-      </c>
-      <c r="V998" s="3" t="s">
+      <c r="V998" s="4">
+        <v>14</v>
+      </c>
+      <c r="W998" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="W998" s="4">
-        <v>14</v>
-      </c>
-      <c r="X998" s="5" t="s">
+      <c r="X998" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y998" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="Y998" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z998" s="5" t="s">
+      <c r="Z998" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA998" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="AA998" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB998" t="s">
+      <c r="AB998" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC998" t="s">
         <v>145</v>
       </c>
-      <c r="AC998">
-        <v>14</v>
-      </c>
-      <c r="AD998" s="1" t="s">
+      <c r="AD998">
+        <v>14</v>
+      </c>
+      <c r="AE998" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AE998">
-        <v>14</v>
-      </c>
-      <c r="AF998" t="s">
+      <c r="AF998">
+        <v>14</v>
+      </c>
+      <c r="AG998" t="s">
         <v>145</v>
       </c>
-      <c r="AG998">
-        <v>14</v>
-      </c>
-      <c r="AH998" s="1" t="s">
+      <c r="AH998">
+        <v>14</v>
+      </c>
+      <c r="AI998" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="AI998">
-        <v>14</v>
-      </c>
-      <c r="AJ998" s="1" t="s">
+      <c r="AJ998">
+        <v>14</v>
+      </c>
+      <c r="AK998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:36" ht="75">
+    <row r="999" spans="1:37" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -10395,89 +10489,89 @@
       <c r="H999">
         <v>0</v>
       </c>
-      <c r="J999" s="1" t="s">
+      <c r="K999" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K999">
-        <v>14</v>
-      </c>
-      <c r="L999" s="1" t="s">
+      <c r="L999">
+        <v>14</v>
+      </c>
+      <c r="M999" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M999">
-        <v>14</v>
-      </c>
       <c r="N999">
+        <v>14</v>
+      </c>
+      <c r="O999">
         <v>1</v>
       </c>
-      <c r="O999">
-        <v>0</v>
-      </c>
-      <c r="P999" t="s">
+      <c r="P999">
+        <v>0</v>
+      </c>
+      <c r="Q999" t="s">
         <v>54</v>
       </c>
-      <c r="Q999">
-        <v>14</v>
-      </c>
-      <c r="R999" s="1" t="s">
+      <c r="R999">
+        <v>14</v>
+      </c>
+      <c r="S999" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="S999">
-        <v>14</v>
-      </c>
-      <c r="T999" s="3" t="s">
+      <c r="T999">
+        <v>14</v>
+      </c>
+      <c r="U999" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="U999" s="4">
-        <v>14</v>
-      </c>
-      <c r="V999" s="3" t="s">
+      <c r="V999" s="4">
+        <v>14</v>
+      </c>
+      <c r="W999" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="W999" s="4">
-        <v>14</v>
-      </c>
-      <c r="X999" s="5" t="s">
+      <c r="X999" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y999" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="Y999" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z999" s="5" t="s">
+      <c r="Z999" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA999" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="AA999" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB999" t="s">
+      <c r="AB999" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC999" t="s">
         <v>147</v>
       </c>
-      <c r="AC999">
-        <v>14</v>
-      </c>
-      <c r="AD999" s="1" t="s">
+      <c r="AD999">
+        <v>14</v>
+      </c>
+      <c r="AE999" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AE999">
-        <v>14</v>
-      </c>
-      <c r="AF999" t="s">
+      <c r="AF999">
+        <v>14</v>
+      </c>
+      <c r="AG999" t="s">
         <v>147</v>
       </c>
-      <c r="AG999">
-        <v>14</v>
-      </c>
-      <c r="AH999" s="1" t="s">
+      <c r="AH999">
+        <v>14</v>
+      </c>
+      <c r="AI999" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="AI999">
-        <v>14</v>
-      </c>
-      <c r="AJ999" s="1" t="s">
+      <c r="AJ999">
+        <v>14</v>
+      </c>
+      <c r="AK999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:36" ht="75">
+    <row r="1000" spans="1:37" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -10499,89 +10593,89 @@
       <c r="H1000">
         <v>0</v>
       </c>
-      <c r="J1000" s="1" t="s">
+      <c r="K1000" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K1000">
-        <v>14</v>
-      </c>
-      <c r="L1000" s="1" t="s">
+      <c r="L1000">
+        <v>14</v>
+      </c>
+      <c r="M1000" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M1000">
-        <v>14</v>
-      </c>
       <c r="N1000">
+        <v>14</v>
+      </c>
+      <c r="O1000">
         <v>1</v>
       </c>
-      <c r="O1000">
-        <v>0</v>
-      </c>
-      <c r="P1000" s="1" t="s">
+      <c r="P1000">
+        <v>0</v>
+      </c>
+      <c r="Q1000" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Q1000">
-        <v>14</v>
-      </c>
-      <c r="R1000" s="1" t="s">
+      <c r="R1000">
+        <v>14</v>
+      </c>
+      <c r="S1000" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="S1000">
-        <v>14</v>
-      </c>
-      <c r="T1000" s="3" t="s">
+      <c r="T1000">
+        <v>14</v>
+      </c>
+      <c r="U1000" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="U1000" s="4">
-        <v>14</v>
-      </c>
-      <c r="V1000" s="3" t="s">
+      <c r="V1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="W1000" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="W1000" s="4">
-        <v>14</v>
-      </c>
-      <c r="X1000" s="5" t="s">
+      <c r="X1000" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y1000" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="Y1000" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z1000" s="5" t="s">
+      <c r="Z1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA1000" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="AA1000" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB1000" s="1" t="s">
+      <c r="AB1000" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC1000" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AC1000">
-        <v>14</v>
-      </c>
-      <c r="AD1000" s="1" t="s">
+      <c r="AD1000">
+        <v>14</v>
+      </c>
+      <c r="AE1000" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AE1000">
-        <v>14</v>
-      </c>
-      <c r="AF1000" s="1" t="s">
+      <c r="AF1000">
+        <v>14</v>
+      </c>
+      <c r="AG1000" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AG1000">
-        <v>14</v>
-      </c>
-      <c r="AH1000" s="1" t="s">
+      <c r="AH1000">
+        <v>14</v>
+      </c>
+      <c r="AI1000" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="AI1000">
-        <v>14</v>
-      </c>
-      <c r="AJ1000" s="1" t="s">
+      <c r="AJ1000">
+        <v>14</v>
+      </c>
+      <c r="AK1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:36">
+    <row r="1001" spans="1:37">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -10603,89 +10697,89 @@
       <c r="H1001">
         <v>0</v>
       </c>
-      <c r="J1001" s="1" t="s">
+      <c r="K1001" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K1001">
-        <v>14</v>
-      </c>
-      <c r="L1001" t="s">
+      <c r="L1001">
+        <v>14</v>
+      </c>
+      <c r="M1001" t="s">
         <v>57</v>
       </c>
-      <c r="M1001">
-        <v>14</v>
-      </c>
       <c r="N1001">
+        <v>14</v>
+      </c>
+      <c r="O1001">
         <v>1</v>
       </c>
-      <c r="O1001">
-        <v>0</v>
-      </c>
-      <c r="P1001" t="s">
+      <c r="P1001">
+        <v>0</v>
+      </c>
+      <c r="Q1001" t="s">
         <v>56</v>
       </c>
-      <c r="Q1001">
-        <v>14</v>
-      </c>
-      <c r="R1001" t="s">
+      <c r="R1001">
+        <v>14</v>
+      </c>
+      <c r="S1001" t="s">
         <v>57</v>
       </c>
-      <c r="S1001">
-        <v>14</v>
-      </c>
-      <c r="T1001" s="3" t="s">
+      <c r="T1001">
+        <v>14</v>
+      </c>
+      <c r="U1001" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="U1001" s="4">
-        <v>14</v>
-      </c>
-      <c r="V1001" s="4" t="s">
+      <c r="V1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="W1001" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="W1001" s="4">
-        <v>14</v>
-      </c>
-      <c r="X1001" s="5" t="s">
+      <c r="X1001" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y1001" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="Y1001" s="6">
-        <v>14</v>
-      </c>
-      <c r="Z1001" s="6" t="s">
+      <c r="Z1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA1001" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="AA1001" s="6">
-        <v>14</v>
-      </c>
-      <c r="AB1001" t="s">
+      <c r="AB1001" s="6">
+        <v>14</v>
+      </c>
+      <c r="AC1001" t="s">
         <v>151</v>
       </c>
-      <c r="AC1001">
-        <v>14</v>
-      </c>
-      <c r="AD1001" t="s">
+      <c r="AD1001">
+        <v>14</v>
+      </c>
+      <c r="AE1001" t="s">
         <v>233</v>
       </c>
-      <c r="AE1001">
-        <v>14</v>
-      </c>
-      <c r="AF1001" t="s">
+      <c r="AF1001">
+        <v>14</v>
+      </c>
+      <c r="AG1001" t="s">
         <v>151</v>
       </c>
-      <c r="AG1001">
-        <v>14</v>
-      </c>
-      <c r="AH1001" t="s">
+      <c r="AH1001">
+        <v>14</v>
+      </c>
+      <c r="AI1001" t="s">
         <v>271</v>
       </c>
-      <c r="AI1001">
-        <v>14</v>
-      </c>
-      <c r="AJ1001" t="s">
+      <c r="AJ1001">
+        <v>14</v>
+      </c>
+      <c r="AK1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:36">
+    <row r="1002" spans="1:37">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -10707,73 +10801,73 @@
       <c r="H1002">
         <v>0</v>
       </c>
-      <c r="J1002" s="1" t="s">
+      <c r="K1002" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1002">
-        <v>0</v>
-      </c>
-      <c r="L1002" s="1" t="s">
+      <c r="L1002">
+        <v>0</v>
+      </c>
+      <c r="M1002" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M1002">
-        <v>0</v>
-      </c>
       <c r="N1002">
         <v>0</v>
       </c>
       <c r="O1002">
         <v>0</v>
       </c>
-      <c r="P1002" t="s">
+      <c r="P1002">
+        <v>0</v>
+      </c>
+      <c r="Q1002" t="s">
         <v>62</v>
       </c>
-      <c r="Q1002">
-        <v>0</v>
-      </c>
-      <c r="R1002" t="s">
+      <c r="R1002">
+        <v>0</v>
+      </c>
+      <c r="S1002" t="s">
         <v>62</v>
       </c>
-      <c r="T1002" s="3" t="s">
+      <c r="U1002" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U1002" s="4">
-        <v>0</v>
-      </c>
-      <c r="V1002" s="3" t="s">
+      <c r="V1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="W1002" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="W1002" s="4">
-        <v>0</v>
-      </c>
-      <c r="X1002" s="5" t="s">
+      <c r="X1002" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y1002" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="Y1002" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z1002" s="5" t="s">
+      <c r="Z1002" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA1002" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="AA1002" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB1002" t="s">
+      <c r="AB1002" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC1002" t="s">
         <v>62</v>
       </c>
-      <c r="AC1002">
-        <v>0</v>
-      </c>
-      <c r="AD1002" t="s">
+      <c r="AD1002">
+        <v>0</v>
+      </c>
+      <c r="AE1002" t="s">
         <v>153</v>
       </c>
-      <c r="AF1002" t="s">
+      <c r="AG1002" t="s">
         <v>62</v>
       </c>
-      <c r="AG1002">
-        <v>0</v>
-      </c>
-      <c r="AH1002" t="s">
+      <c r="AH1002">
+        <v>0</v>
+      </c>
+      <c r="AI1002" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCFCDBF-507D-42BE-9E25-FA4F2D5A1F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92E4FA9-0CEE-4AD8-B23F-508175262209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5265,7 +5265,7 @@
         <v>374</v>
       </c>
       <c r="N32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O32" s="1">
         <v>1</v>
@@ -5283,7 +5283,7 @@
         <v>375</v>
       </c>
       <c r="T32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U32" t="s">
         <v>366</v>
@@ -5295,7 +5295,7 @@
         <v>376</v>
       </c>
       <c r="X32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="s">
         <v>366</v>
@@ -5307,7 +5307,7 @@
         <v>377</v>
       </c>
       <c r="AB32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AC32" t="s">
         <v>367</v>
@@ -5319,7 +5319,7 @@
         <v>378</v>
       </c>
       <c r="AF32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="s">
         <v>355</v>
@@ -5331,7 +5331,7 @@
         <v>379</v>
       </c>
       <c r="AJ32" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AK32" s="1" t="s">
         <v>368</v>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92E4FA9-0CEE-4AD8-B23F-508175262209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE9C50-451B-493A-B169-A494894A67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="390">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1488,7 +1488,181 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>デモ版用静声に熱する彷徨う者の情報</t>
+    <t>&lt;r="びび"&gt;微美&lt;/r&gt;しき&lt;r="びぼう"&gt;魅忘&lt;/r&gt;の&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>娇美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>嬌美惑忘之徘徊者</t>
+  </si>
+  <si>
+    <t>Errante Bello del Olvido</t>
+  </si>
+  <si>
+    <t>Errante Belo do Esquecimento</t>
+  </si>
+  <si>
+    <t>微美しき魅忘の彷徨う者の情報</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="うた"&gt;唄&lt;/r&gt;&lt;r="うた"&gt;歌&lt;/r&gt;う&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sing-Song Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>咏永的彷徨者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canto-Llanto, el Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唄歌う彷徨う者の情報</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>It happened the moment I heard a woman's voice from somewhere and peered out from cover to check what was going on. The moment the earless, brown-haired woman noticed me, she screamed and lunged at me with wild ferocity.
+I got lucky and dove into cover to escape her, but someone nearby ended up being targeted instead. The fact that it ran off into the distance with that thing is the only reason I survived — but there's a good chance that person only got attacked because of me.
+Getting seen isn't the only trigger — if it's exposed to light, it loses itself entirely and charges. Bottom line: never use a light source around it, no matter what.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不知从哪里传来了女人的声音，我正想从暗处窥探情况，就在那一瞬间，一个没有耳朵、留着棕色头发的女人注意到了我，尖叫着朝我猛扑过来。
+我运气好滚进了暗处才逃过一劫，但附近的一个人却因此被盯上了。多亏它带着那家伙一起跑远了，我才捡回一条命——但那人很可能是因为我才被袭击的。
+不仅仅是被看到会引发攻击，只要被灯光照到，它就会彻底失控冲过来。总之，对付它绝对不能用灯光。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不知從哪裡傳來了女人的聲音，我正想從暗處窺探情況，就在那一瞬間，一個沒有耳朵、留著棕色頭髮的女人注意到了我，尖叫著朝我猛撲過來。
+我運氣好滾進了暗處才逃過一劫，但附近的一個人卻因此被盯上了。多虧牠帶著那傢伙一起跑遠了，我才撿回一條命——但那人很可能是因為我才被襲擊的。
+不僅僅是被看到會引發攻擊，只要被燈光照到，牠就會徹底失控衝過來。總之，對付牠絕對不能用燈光。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fue en el instante en que oí la voz de una mujer surgir de algún lugar y me asomé desde donde me escondía para ver qué pasaba. En cuanto esa mujer sin orejas y de cabello castaño me notó, se lanzó hacia mí gritando con una ferocidad desquiciada.
+Tuve la suerte de arrojarme a un escondite y escapar, pero alguien que estaba cerca terminó siendo el blanco. El hecho de que esa cosa se alejara corriendo junto con esa persona es la única razón por la que sobreviví, pero es muy probable que a esa persona la atacaran por mi culpa.
+No basta con que la vean para que ataque: si la ilumina una luz, pierde completamente el control y embiste. En resumen, bajo ninguna circunstancia hay que usar luz cerca de ella.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Foi no instante em que ouvi a voz de uma mulher vindo de algum lugar e espiei do meu esconderijo para ver o que estava acontecendo. Assim que aquela mulher sem orelhas e de cabelo castanho me percebeu, ela avançou gritando com uma fúria descontrolada.
+Tive a sorte de me jogar num esconderijo e escapar, mas alguém que estava por perto acabou sendo o alvo. O fato de aquela coisa ter corrido para longe junto com essa pessoa foi a única razão pela qual sobrevivi — mas é bem provável que essa pessoa só tenha sido atacada por minha causa.
+Não é só ser vista que desencadeia o ataque: se for exposta à luz, ela perde completamente o controle e avança. Resumindo, nunca se deve usar luz perto dela, de jeito nenhum.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠くから子供の鼻歌が聞こえてきたが、歌が全て終わった瞬間、いきなりこちらに向かって走り始めてきた。
+何度も奴を足止めしながら逃げ切ったつもりだが、常に俺を追跡してくる。なんで俺の居場所が常にバレているんだ…。
+他の化け物の時は運よく逃げ切れたが、今度こそ俺は終わりかもしれない…。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I heard a child humming a tune from somewhere far off, and the instant the humming finished, it suddenly started running straight at me.
+I've been stalling it over and over and thought I'd gotten away clean, but it keeps tracking me no matter what. Why does it always know exactly where I am...
+I got lucky and escaped the other monsters, but this time... this might really be it for me.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>远处传来了孩子哼歌的声音，可就在那首歌唱完的瞬间，它突然朝我猛冲了过来。
+我一次又一次地拖住它、试图甩掉它，本以为已经逃脱了，可它却始终紧追不舍。为什么我的位置总是被它发现……
+之前遇到别的怪物时运气好逃过了一劫，可这一次……我可能真的要完了……</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠處傳來了孩子哼歌的聲音，可就在那首歌唱完的瞬間，牠突然朝我猛衝了過來。
+我一次又一次地拖住牠、試圖甩掉牠，本以為已經逃脫了，可牠卻始終緊追不捨。為什麼我的位置總是被牠發現……
+之前遇到其他怪物時運氣好逃過了一劫，可這一次……我可能真的要完了……</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Oí a lo lejos el tarareo de un niño, y en el instante mismo en que la melodía terminó, se lanzó a correr directo hacia mí.
+Lo he ido frenando una y otra vez y pensé que había logrado escapar limpiamente, pero no importa lo que haga, siempre me sigue el rastro. ¿Por qué siempre sabe exactamente dónde estoy...?
+Con los otros monstruos tuve la suerte de escapar, pero esta vez... puede que de verdad sea mi fin.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ouvi ao longe um zumbido de criança, uma cantarolada, e no exato instante em que a melodia terminou, aquilo saiu correndo direto na minha direção.
+Fiquei atrasando-o várias vezes e achei que tinha conseguido escapar de vez, mas não importa o que eu faça, ele sempre me rastreia. Por que ele sempre sabe exatamente onde eu estou...
+Com os outros monstros tive a sorte de escapar, mas dessa vez... pode ser que esse seja realmente o meu fim.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Beauteous-Bewilder Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せない。そのため、この迷宮で起こった出来事をここにメモする。
+何人かで迷宮を探索していたが、そのうちの1人がスーツ姿の肌が赤い化け物に捕まってしまった。俺はいち早く逃げたが、そいつがその後どうなったかは分からない。今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
+まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。見つかった原因は恐らくそれだろう。また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I'd like to say "My name is...", but I discarded my name and can no longer remember it. So, I will record the events that happened in this labyrinth here.
+I was exploring the labyrinth with a few others, but one of us was caught by a red-skinned monster in a suit. I fled immediately, so I don't know what became of them. As I organize the situation while hiding, I'll try to analyze the characteristics of that monster in my own way.
+First, regarding the person who was caught, they couldn't endure the terror, panicked, ran around, and made loud noises. That was likely why they were spotted. Also, I once accidentally turned on my light near the monster, but because it couldn't detect the blinding light, my position wasn't exposed.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想说“我的名字叫……”，但因为抛弃了名字，我已经想不起来了。因此，我在此记录下在这个迷宫里发生的事情。
+我之前和几个人一起在迷宫里探索，但其中一个人被一个穿西装、红皮肤的怪物抓住了。我第一时间逃跑了，所以不知道那个人后来怎么样了。现在我边躲藏边整理情况，顺便按照我自己的理解分析一下那个怪物的特征。
+首先是关于那个被抓住的人，他因为无法忍受恐惧而陷入恐慌，到处乱跑并发出很大的声音。这恐怕就是被发现的原因。另外，我曾经有一次在怪物附近不小心点亮了手电筒，但也许是因为它无法察觉眩目的光线，我的位置并没有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我想說「我的名字叫……」，但因為拋棄了名字，我已经想不起來了。因此，我在此記錄下在這個迷宮裡發生的事情。
+我之前和幾個人一起在迷宮裡探索，但其中一個人被一個穿西裝、紅皮膚的怪物抓住了。我第一時間逃跑了，所以不知道那個人後來怎麼樣了。現在我邊躲藏邊整理情況，順便按照我自己的理解分析一下那個怪物的特徵。
+首先是關於那個被抓住的人，他因為無法忍受恐懼而陷入恐慌，到處亂跑並發出很大的聲音。這恐怕就是被發現的原因。另外，我曾經有一次在怪物附近不小心點亮了手電筒，但也許是因為它無法察覺眩目的光線，我的位置並沒有暴露。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Me gustaría decir "Mi nombre es...", pero como deseché mi nombre, ya no puedo recordarlo. Por lo tanto, dejaré anotados aquí los acontecimientos que ocurrieron en este laberinto.
+Estaba explorando el laberinto con varias personas, pero una de ellas fue atrapada por un monstruo de piel roja en traje. Huí de inmediato, así que no sé qué fue de esa persona. Mientras me escondo y pongo en orden la situación, intentaré analizar las características de ese monstruo a mi manera.
+En primer lugar, sobre la persona atrapada: no pudo soportar el terror, entró en pánico, corrió e hizo ruidos fuertes. Probablemente esa fue la razón por la que la descubrieron. Además, una vez encendí mi linterna por accidente cerca del monstruo, pero como no pudo detectar la luz deslumbrante, no descubrió mi ubicación.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eu gostaria de dizer "Meu nome é...", mas como descartei meu nome, já não consigo me lembrar dele. Por isso, deixarei anotados aqui os acontecimentos que ocorreram neste labirinto.
+Eu estava explorando o labirinto com algumas pessoas, mas uma delas foi pega por um monstro de pele vermelha vestindo terno. Eu fugi imediatamente, então não sei o que aconteceu com ela. Enquanto me escondo e organizo a situação, tentarei analisar as características daquele monstro do meu jeito.
+Primeiro, em relação à pessoa que foi pega: ela não aguentou o terror, entrou em pânico, correu e fez barulhos altos. Essa provavelmente foi a razão de ter sido descoberta. Além disso, uma vez acendi minha lanterna por acidente perto do monstro, mas como ele não conseguiu detectar a luz cegante, meu paradeiro não foi revelado.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
+俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
+姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>demoStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="せいせい"&gt;静声&lt;/r&gt;に&lt;r="ねっ"&gt;熱&lt;/r&gt;する&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;Demo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>デモ版用静声に熱する彷徨う者の情報。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用していない。</t>
+    </r>
     <rPh sb="2" eb="3">
       <t>バン</t>
     </rPh>
@@ -1498,162 +1672,9 @@
     <rPh sb="15" eb="17">
       <t>ジョウホウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="びび"&gt;微美&lt;/r&gt;しき&lt;r="びぼう"&gt;魅忘&lt;/r&gt;の&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>娇美惑忘之徘徊者</t>
-  </si>
-  <si>
-    <t>嬌美惑忘之徘徊者</t>
-  </si>
-  <si>
-    <t>Errante Bello del Olvido</t>
-  </si>
-  <si>
-    <t>Errante Belo do Esquecimento</t>
-  </si>
-  <si>
-    <t>微美しき魅忘の彷徨う者の情報</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;r="うた"&gt;唄&lt;/r&gt;&lt;r="うた"&gt;歌&lt;/r&gt;う&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Sing-Song Wanderer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>咏永的彷徨者</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Canto-Llanto, el Errante</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>唄歌う彷徨う者の情報</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>It happened the moment I heard a woman's voice from somewhere and peered out from cover to check what was going on. The moment the earless, brown-haired woman noticed me, she screamed and lunged at me with wild ferocity.
-I got lucky and dove into cover to escape her, but someone nearby ended up being targeted instead. The fact that it ran off into the distance with that thing is the only reason I survived — but there's a good chance that person only got attacked because of me.
-Getting seen isn't the only trigger — if it's exposed to light, it loses itself entirely and charges. Bottom line: never use a light source around it, no matter what.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>不知从哪里传来了女人的声音，我正想从暗处窥探情况，就在那一瞬间，一个没有耳朵、留着棕色头发的女人注意到了我，尖叫着朝我猛扑过来。
-我运气好滚进了暗处才逃过一劫，但附近的一个人却因此被盯上了。多亏它带着那家伙一起跑远了，我才捡回一条命——但那人很可能是因为我才被袭击的。
-不仅仅是被看到会引发攻击，只要被灯光照到，它就会彻底失控冲过来。总之，对付它绝对不能用灯光。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>不知從哪裡傳來了女人的聲音，我正想從暗處窺探情況，就在那一瞬間，一個沒有耳朵、留著棕色頭髮的女人注意到了我，尖叫著朝我猛撲過來。
-我運氣好滾進了暗處才逃過一劫，但附近的一個人卻因此被盯上了。多虧牠帶著那傢伙一起跑遠了，我才撿回一條命——但那人很可能是因為我才被襲擊的。
-不僅僅是被看到會引發攻擊，只要被燈光照到，牠就會徹底失控衝過來。總之，對付牠絕對不能用燈光。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Fue en el instante en que oí la voz de una mujer surgir de algún lugar y me asomé desde donde me escondía para ver qué pasaba. En cuanto esa mujer sin orejas y de cabello castaño me notó, se lanzó hacia mí gritando con una ferocidad desquiciada.
-Tuve la suerte de arrojarme a un escondite y escapar, pero alguien que estaba cerca terminó siendo el blanco. El hecho de que esa cosa se alejara corriendo junto con esa persona es la única razón por la que sobreviví, pero es muy probable que a esa persona la atacaran por mi culpa.
-No basta con que la vean para que ataque: si la ilumina una luz, pierde completamente el control y embiste. En resumen, bajo ninguna circunstancia hay que usar luz cerca de ella.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Foi no instante em que ouvi a voz de uma mulher vindo de algum lugar e espiei do meu esconderijo para ver o que estava acontecendo. Assim que aquela mulher sem orelhas e de cabelo castanho me percebeu, ela avançou gritando com uma fúria descontrolada.
-Tive a sorte de me jogar num esconderijo e escapar, mas alguém que estava por perto acabou sendo o alvo. O fato de aquela coisa ter corrido para longe junto com essa pessoa foi a única razão pela qual sobrevivi — mas é bem provável que essa pessoa só tenha sido atacada por minha causa.
-Não é só ser vista que desencadeia o ataque: se for exposta à luz, ela perde completamente o controle e avança. Resumindo, nunca se deve usar luz perto dela, de jeito nenhum.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>遠くから子供の鼻歌が聞こえてきたが、歌が全て終わった瞬間、いきなりこちらに向かって走り始めてきた。
-何度も奴を足止めしながら逃げ切ったつもりだが、常に俺を追跡してくる。なんで俺の居場所が常にバレているんだ…。
-他の化け物の時は運よく逃げ切れたが、今度こそ俺は終わりかもしれない…。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>I heard a child humming a tune from somewhere far off, and the instant the humming finished, it suddenly started running straight at me.
-I've been stalling it over and over and thought I'd gotten away clean, but it keeps tracking me no matter what. Why does it always know exactly where I am...
-I got lucky and escaped the other monsters, but this time... this might really be it for me.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>远处传来了孩子哼歌的声音，可就在那首歌唱完的瞬间，它突然朝我猛冲了过来。
-我一次又一次地拖住它、试图甩掉它，本以为已经逃脱了，可它却始终紧追不舍。为什么我的位置总是被它发现……
-之前遇到别的怪物时运气好逃过了一劫，可这一次……我可能真的要完了……</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>遠處傳來了孩子哼歌的聲音，可就在那首歌唱完的瞬間，牠突然朝我猛衝了過來。
-我一次又一次地拖住牠、試圖甩掉牠，本以為已經逃脫了，可牠卻始終緊追不捨。為什麼我的位置總是被牠發現……
-之前遇到其他怪物時運氣好逃過了一劫，可這一次……我可能真的要完了……</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Oí a lo lejos el tarareo de un niño, y en el instante mismo en que la melodía terminó, se lanzó a correr directo hacia mí.
-Lo he ido frenando una y otra vez y pensé que había logrado escapar limpiamente, pero no importa lo que haga, siempre me sigue el rastro. ¿Por qué siempre sabe exactamente dónde estoy...?
-Con los otros monstruos tuve la suerte de escapar, pero esta vez... puede que de verdad sea mi fin.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Ouvi ao longe um zumbido de criança, uma cantarolada, e no exato instante em que a melodia terminou, aquilo saiu correndo direto na minha direção.
-Fiquei atrasando-o várias vezes e achei que tinha conseguido escapar de vez, mas não importa o que eu faça, ele sempre me rastreia. Por que ele sempre sabe exatamente onde eu estou...
-Com os outros monstros tive a sorte de escapar, mas dessa vez... pode ser que esse seja realmente o meu fim.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Beauteous-Bewilder Wanderer</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>俺の名は…と言いたいところだが、名前を破棄されたせいで思い出せない。そのため、この迷宮で起こった出来事をここにメモする。
-何人かで迷宮を探索していたが、そのうちの1人がスーツ姿の肌が赤い化け物に捕まってしまった。俺はいち早く逃げたが、そいつがその後どうなったかは分からない。今隠れながらこの状況を整理しているが、あの化け物の特徴を俺なりに分析してみる。
-まず化け物に捕まった者についてだが、恐怖に耐えきれずパニックになって走ったり大きな音を立てていた。見つかった原因は恐らくそれだろう。また、一度だけ化け物の近くで俺はうっかりライトを点けてしまったが、眩しい光を検知できていないからか居場所がバレなかった。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>I'd like to say "My name is...", but I discarded my name and can no longer remember it. So, I will record the events that happened in this labyrinth here.
-I was exploring the labyrinth with a few others, but one of us was caught by a red-skinned monster in a suit. I fled immediately, so I don't know what became of them. As I organize the situation while hiding, I'll try to analyze the characteristics of that monster in my own way.
-First, regarding the person who was caught, they couldn't endure the terror, panicked, ran around, and made loud noises. That was likely why they were spotted. Also, I once accidentally turned on my light near the monster, but because it couldn't detect the blinding light, my position wasn't exposed.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>我想说“我的名字叫……”，但因为抛弃了名字，我已经想不起来了。因此，我在此记录下在这个迷宫里发生的事情。
-我之前和几个人一起在迷宫里探索，但其中一个人被一个穿西装、红皮肤的怪物抓住了。我第一时间逃跑了，所以不知道那个人后来怎么样了。现在我边躲藏边整理情况，顺便按照我自己的理解分析一下那个怪物的特征。
-首先是关于那个被抓住的人，他因为无法忍受恐惧而陷入恐慌，到处乱跑并发出很大的声音。这恐怕就是被发现的原因。另外，我曾经有一次在怪物附近不小心点亮了手电筒，但也许是因为它无法察觉眩目的光线，我的位置并没有暴露。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>我想說「我的名字叫……」，但因為拋棄了名字，我已经想不起來了。因此，我在此記錄下在這個迷宮裡發生的事情。
-我之前和幾個人一起在迷宮裡探索，但其中一個人被一個穿西裝、紅皮膚的怪物抓住了。我第一時間逃跑了，所以不知道那個人後來怎麼樣了。現在我邊躲藏邊整理情況，順便按照我自己的理解分析一下那個怪物的特徵。
-首先是關於那個被抓住的人，他因為無法忍受恐懼而陷入恐慌，到處亂跑並發出很大的聲音。這恐怕就是被發現的原因。另外，我曾經有一次在怪物附近不小心點亮了手電筒，但也許是因為它無法察覺眩目的光線，我的位置並沒有暴露。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Me gustaría decir "Mi nombre es...", pero como deseché mi nombre, ya no puedo recordarlo. Por lo tanto, dejaré anotados aquí los acontecimientos que ocurrieron en este laberinto.
-Estaba explorando el laberinto con varias personas, pero una de ellas fue atrapada por un monstruo de piel roja en traje. Huí de inmediato, así que no sé qué fue de esa persona. Mientras me escondo y pongo en orden la situación, intentaré analizar las características de ese monstruo a mi manera.
-En primer lugar, sobre la persona atrapada: no pudo soportar el terror, entró en pánico, corrió e hizo ruidos fuertes. Probablemente esa fue la razón por la que la descubrieron. Además, una vez encendí mi linterna por accidente cerca del monstruo, pero como no pudo detectar la luz deslumbrante, no descubrió mi ubicación.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Eu gostaria de dizer "Meu nome é...", mas como descartei meu nome, já não consigo me lembrar dele. Por isso, deixarei anotados aqui os acontecimentos que ocorreram neste labirinto.
-Eu estava explorando o labirinto com algumas pessoas, mas uma delas foi pega por um monstro de pele vermelha vestindo terno. Eu fugi imediatamente, então não sei o que aconteceu com ela. Enquanto me escondo e organizo a situação, tentarei analisar as características daquele monstro do meu jeito.
-Primeiro, em relação à pessoa que foi pega: ela não aguentou o terror, entrou em pânico, correu e fez barulhos altos. Essa provavelmente foi a razão de ter sido descoberta. Além disso, uma vez acendi minha lanterna por acidente perto do monstro, mas como ele não conseguiu detectar a luz cegante, meu paradeiro não foi revelado.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>どこからか女の声が聞こえて、様子を探ろうと物陰から覗いた瞬間だった。耳のない茶髪の女がこちらに気づくなり、叫びながら猛然と襲いかかってきた。
-俺は運良く物陰に転がり込んで難を逃れたが、近くにいた1人が狙われてしまった。化け物と一緒に遠くへ走っていったおかげで俺は助かったが、狙われたそいつは俺のせいで襲われた可能性が高い。
-姿を見られただけでなく、灯りを当てられると我を失って突進してきたので、とにかく奴に対して灯りは絶対に使うべきではない。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>demoStatus</t>
+    <rPh sb="18" eb="20">
+      <t>シヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1661,7 +1682,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1707,6 +1728,15 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2100,7 +2130,7 @@
         <v>349</v>
       </c>
       <c r="J1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -4926,13 +4956,13 @@
         <v>1</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="L29" s="1">
         <v>16</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N29" s="1">
         <v>12</v>
@@ -4950,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T29" s="1">
         <v>12</v>
@@ -4962,7 +4992,7 @@
         <v>16</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="X29" s="1">
         <v>12</v>
@@ -4974,7 +5004,7 @@
         <v>16</v>
       </c>
       <c r="AA29" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AB29" s="1">
         <v>12</v>
@@ -4986,7 +5016,7 @@
         <v>16</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AF29" s="1">
         <v>12</v>
@@ -4998,13 +5028,13 @@
         <v>16</v>
       </c>
       <c r="AI29" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AJ29" s="1">
         <v>10</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" spans="1:37" ht="409.5">
@@ -5042,7 +5072,7 @@
         <v>16</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N30" s="1">
         <v>12</v>
@@ -5060,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T30" s="1">
         <v>12</v>
@@ -5072,7 +5102,7 @@
         <v>16</v>
       </c>
       <c r="W30" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="X30" s="1">
         <v>12</v>
@@ -5084,7 +5114,7 @@
         <v>16</v>
       </c>
       <c r="AA30" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AB30" s="1">
         <v>12</v>
@@ -5096,7 +5126,7 @@
         <v>16</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AF30" s="1">
         <v>12</v>
@@ -5108,7 +5138,7 @@
         <v>16</v>
       </c>
       <c r="AI30" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AJ30" s="1">
         <v>10</v>
@@ -5146,13 +5176,13 @@
         <v>0</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L31" s="1">
         <v>16</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N31" s="1">
         <v>14</v>
@@ -5164,67 +5194,67 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R31" s="1">
         <v>16</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="T31" s="1">
         <v>12</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V31" s="1">
         <v>16</v>
       </c>
       <c r="W31" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="X31" s="1">
         <v>14</v>
       </c>
       <c r="Y31" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z31" s="1">
         <v>16</v>
       </c>
       <c r="AA31" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AB31" s="1">
         <v>14</v>
       </c>
       <c r="AC31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AD31" s="1">
         <v>16</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF31" s="1">
         <v>12</v>
       </c>
       <c r="AG31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AH31" s="1">
         <v>16</v>
       </c>
       <c r="AI31" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AJ31" s="1">
         <v>12</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:37" ht="375">
@@ -5256,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L32" s="1">
         <v>16</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N32" s="1">
         <v>14</v>
@@ -5274,49 +5304,49 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R32" s="1">
         <v>16</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T32" s="1">
         <v>14</v>
       </c>
       <c r="U32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="V32" s="1">
         <v>16</v>
       </c>
       <c r="W32" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="X32" s="1">
         <v>14</v>
       </c>
       <c r="Y32" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Z32" s="1">
         <v>16</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AB32" s="1">
         <v>14</v>
       </c>
       <c r="AC32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD32" s="1">
         <v>16</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AF32" s="1">
         <v>14</v>
@@ -5328,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="AI32" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ32" s="1">
         <v>14</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE9C50-451B-493A-B169-A494894A67C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90D24D7-FD69-4F51-AB69-EE290177A8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="388">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1643,46 +1643,12 @@
     <t>demoStatus</t>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>&lt;r="せいせい"&gt;静声&lt;/r&gt;に&lt;r="ねっ"&gt;熱&lt;/r&gt;する&lt;r="さまよ"&gt;彷徨&lt;/r&gt;う&lt;r="もの"&gt;者&lt;/r&gt;Demo</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>デモ版用静声に熱する彷徨う者の情報。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>使用していない。</t>
-    </r>
-    <rPh sb="2" eb="3">
-      <t>バン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1728,15 +1694,6 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4927,115 +4884,36 @@
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="409.5">
+    <row r="29" spans="1:37">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="L29" s="1">
-        <v>16</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="N29" s="1">
-        <v>12</v>
-      </c>
-      <c r="O29" s="1">
-        <v>1</v>
-      </c>
-      <c r="P29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R29" s="1">
-        <v>16</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="T29" s="1">
-        <v>12</v>
-      </c>
-      <c r="U29" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="V29" s="1">
-        <v>16</v>
-      </c>
-      <c r="W29" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="X29" s="1">
-        <v>12</v>
-      </c>
-      <c r="Y29" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z29" s="1">
-        <v>16</v>
-      </c>
-      <c r="AA29" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="AB29" s="1">
-        <v>12</v>
-      </c>
-      <c r="AC29" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>16</v>
-      </c>
-      <c r="AE29" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="AF29" s="1">
-        <v>12</v>
-      </c>
-      <c r="AG29" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="AH29" s="1">
-        <v>16</v>
-      </c>
-      <c r="AI29" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="AJ29" s="1">
-        <v>10</v>
-      </c>
-      <c r="AK29" s="1" t="s">
-        <v>389</v>
-      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
     </row>
     <row r="30" spans="1:37" ht="409.5">
       <c r="A30">

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90D24D7-FD69-4F51-AB69-EE290177A8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168B685D-2E2F-436B-9B6C-9847A500F405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="442">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1642,6 +1642,193 @@
   <si>
     <t>demoStatus</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemNameRussian</t>
+  </si>
+  <si>
+    <t>itemNameSizeRussian</t>
+  </si>
+  <si>
+    <t>itemDescriptionRussian</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizeRussian</t>
+  </si>
+  <si>
+    <t>Тело мальчика в парке</t>
+  </si>
+  <si>
+    <t>Срочно! В парке найдено тело мальчика! Каким было орудие убийства?
+Ранним утром ×-го числа ●-го месяца неподалёку от парка △△ в черте города было обнаружено тело мальчика (предположительно 12–14 лет). Место находки — прогулочная аллея, любимая местными жителями; тело заметил прохожий во время утренней прогулки.
+Видимых повреждений на теле нет, и, как сообщается, «наличие состава преступления не установлено». Кроме того, по словам следователей, орудия убийства рядом с местом происшествия, по всей видимости, не нашли.
+Личность мальчика до сих пор не установлена; полиция опрашивает местных жителей.
+Расследование идёт с трудом. Следите за новостями.</t>
+  </si>
+  <si>
+    <t>Снотворное</t>
+  </si>
+  <si>
+    <t>Сильное снотворное: если принять его за 1–2 часа до сна, оно избавит от недосыпа.</t>
+  </si>
+  <si>
+    <t>Нож</t>
+  </si>
+  <si>
+    <t>Старый нож с острым лезвием.</t>
+  </si>
+  <si>
+    <t>Молоток</t>
+  </si>
+  <si>
+    <t>Тяжёлый железный молоток.</t>
+  </si>
+  <si>
+    <t>Верёвка</t>
+  </si>
+  <si>
+    <t>Толстая прочная верёвка с растрёпанными концами.</t>
+  </si>
+  <si>
+    <t>Обучение</t>
+  </si>
+  <si>
+    <t>Мужчина был убит у себя дома. На голове следы сильных ударов; полиция начала расследование, полагая, что преступление совершено тупым предметом.</t>
+  </si>
+  <si>
+    <t>Топор</t>
+  </si>
+  <si>
+    <t>Тяжёлый топор: лезвие иззубрено сильнее, чем кажется на первый взгляд.</t>
+  </si>
+  <si>
+    <t>Усилитель выносливости</t>
+  </si>
+  <si>
+    <t>При использовании: на время снижает расход выносливости и ускоряет её восстановление.</t>
+  </si>
+  <si>
+    <t>Загадочный компас</t>
+  </si>
+  <si>
+    <t>В стрелку вставлен осколок синей сферы, поэтому она всегда указывает туда, где находится Синяя сфера Правосудия.</t>
+  </si>
+  <si>
+    <t>Макет больничной койки</t>
+  </si>
+  <si>
+    <t>На обороте макета написано: «Болезнь».</t>
+  </si>
+  <si>
+    <t>Макет железнодорожного переезда</t>
+  </si>
+  <si>
+    <t>На обороте макета написано: «Наезд».</t>
+  </si>
+  <si>
+    <t>Макет разрушенного здания</t>
+  </si>
+  <si>
+    <t>На обороте макета написано: «Раздавливание».</t>
+  </si>
+  <si>
+    <t>Макет камина</t>
+  </si>
+  <si>
+    <t>На обороте макета написано: «Сожжение».</t>
+  </si>
+  <si>
+    <t>Макет бассейна</t>
+  </si>
+  <si>
+    <t>На обороте макета написано: «Утопление».</t>
+  </si>
+  <si>
+    <t>Хлопушка</t>
+  </si>
+  <si>
+    <t>Если применить её против Скитальца рядом прямо перед вами, он на время растеряется и не сможет действовать. Но при этом раздастся громкий хлопок.</t>
+  </si>
+  <si>
+    <t>История об одном лучшем друге</t>
+  </si>
+  <si>
+    <t>Моему бывшему лучшему другу
+Помнишь, как в детстве мы всегда играли вместе в парке △△ неподалёку?
+«Мы всегда будем вместе».
+Эти слова, что ты сказал мне в тот день на скамейке в парке, я и сейчас помню до мельчайших подробностей.
+Но с каждым новым сезоном ты приходил в парк всё реже и реже……
+Когда мы виделись в последний раз, ты лежал холодный и даже не шелохнулся, и больше не позвал меня по имени своим ласковым голосом…
+Я терпел все эти дни без тебя, но мне слишком больно, и больше я не могу.
+Поэтому я тоже иду к тебе.</t>
+  </si>
+  <si>
+    <t>Продолжение! Тело мальчика в парке</t>
+  </si>
+  <si>
+    <t>Полиция продолжает опрашивать жителей в связи с телом мальчика, найденным в парке △△.
+Были опрошены семь учеников, общавшихся с мальчиком в школе. Расспросив их о его школьных вещах, полиция подозревает, что некоторые из них, возможно, лгут.
+A: На уроке труда он чуть-чуть побрызгал на дерево из нового баллончика с краской.
+B: За долгие годы его учебник совсем истрепался и разваливается.
+C: Я видел, как кто-то клал иголки в его сменную обувь.
+D: Согласен с A.
+E: Тетрадь новая, ею почти не пользовались.
+F: Согласен с B. C лжёт.
+G: Согласен с C. A лжёт.</t>
+  </si>
+  <si>
+    <t>Сменная обувь</t>
+  </si>
+  <si>
+    <t>Если присмотреться, внутри спрятаны иголки.</t>
+  </si>
+  <si>
+    <t>Учебник</t>
+  </si>
+  <si>
+    <t>Истрёпан так сильно, что это никак не может быть естественным износом.</t>
+  </si>
+  <si>
+    <t>Грязная туфля</t>
+  </si>
+  <si>
+    <t>Закрашена краской из баллончика и сильно испачкана.</t>
+  </si>
+  <si>
+    <t>Баллончик краски</t>
+  </si>
+  <si>
+    <t>Аэрозольная краска. Внутри почти ничего не осталось.</t>
+  </si>
+  <si>
+    <t>Новая тетрадь</t>
+  </si>
+  <si>
+    <t>Если присмотреться, некоторые страницы склеены между собой.</t>
+  </si>
+  <si>
+    <t>Скиталец, вскипающий от тишины</t>
+  </si>
+  <si>
+    <t>Я бы сказал: «Меня зовут…», — но моё имя уничтожили, и я не могу его вспомнить. Поэтому записываю здесь всё, что произошло в этом лабиринте.
+Мы обследовали лабиринт вместе с несколькими людьми, но одного из нас схватило краснокожее чудовище в костюме. Я сразу же сбежал, так что не знаю, что с ним стало потом. Сейчас я прячусь и пытаюсь осмыслить происходящее — попробую по-своему разобрать повадки этого чудовища.
+Во-первых, тот, кого схватили, не выдержал страха, запаниковал — бегал и сильно шумел. Скорее всего, его заметили именно поэтому. А ещё однажды я по неосторожности включил фонарь рядом с чудовищем, но меня не обнаружили — видимо, оно не замечает яркого света.</t>
+  </si>
+  <si>
+    <t>Пленительная Скиталица забвения</t>
+  </si>
+  <si>
+    <t>Откуда-то донёсся женский голос, и я выглянул из укрытия, чтобы посмотреть, что происходит. В тот же миг безухая женщина с каштановыми волосами заметила меня и с криком яростно бросилась в атаку.
+Мне повезло — я успел закатиться в укрытие и спастись, но вместо меня она набросилась на того, кто был рядом. Я выжил лишь потому, что они вместе с чудовищем умчались вдаль, но, скорее всего, на того беднягу напали из-за меня.
+Она бросается не только когда тебя увидит: стоит посветить на неё — и она теряет рассудок и кидается вперёд. Поэтому ни в коем случае не используй против неё свет.</t>
+  </si>
+  <si>
+    <t>Поющий Скиталец</t>
+  </si>
+  <si>
+    <t>Издалека донеслось, как ребёнок что-то напевает, а как только песенка закончилась, он вдруг бросился бежать прямо ко мне.
+Я много раз задерживал его и думал, что оторвался, но он всё равно меня выслеживает. Почему он всегда знает, где я…
+От других чудовищ мне повезло уйти, но на этот раз, похоже, мне конец…</t>
   </si>
 </sst>
 </file>
@@ -2019,7 +2206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK1002"/>
+  <dimension ref="A1:AO1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2056,9 +2243,13 @@
     <col min="34" max="34" width="28.5" customWidth="1"/>
     <col min="35" max="35" width="28.25" customWidth="1"/>
     <col min="36" max="36" width="31.375" customWidth="1"/>
+    <col min="37" max="37" width="62" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="70.625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="28.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2168,16 +2359,28 @@
         <v>237</v>
       </c>
       <c r="AK1" t="s">
+        <v>388</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>389</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>390</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>391</v>
+      </c>
+      <c r="AO1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:41">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:37" ht="409.5">
+    <row r="3" spans="1:41" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2284,10 +2487,22 @@
         <v>11</v>
       </c>
       <c r="AK3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="AL3">
+        <v>12</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="AN3">
+        <v>11</v>
+      </c>
+      <c r="AO3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="228" customHeight="1">
+    <row r="4" spans="1:41" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2394,10 +2609,22 @@
         <v>14</v>
       </c>
       <c r="AK4" t="s">
+        <v>394</v>
+      </c>
+      <c r="AL4">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="AN4">
+        <v>14</v>
+      </c>
+      <c r="AO4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="92.25" customHeight="1">
+    <row r="5" spans="1:41" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2504,10 +2731,22 @@
         <v>14</v>
       </c>
       <c r="AK5" t="s">
+        <v>396</v>
+      </c>
+      <c r="AL5">
+        <v>14</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AN5">
+        <v>14</v>
+      </c>
+      <c r="AO5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="37.5">
+    <row r="6" spans="1:41" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2614,15 +2853,27 @@
         <v>14</v>
       </c>
       <c r="AK6" t="s">
+        <v>398</v>
+      </c>
+      <c r="AL6">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AN6">
+        <v>14</v>
+      </c>
+      <c r="AO6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:41">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="56.25">
+    <row r="8" spans="1:41" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2729,10 +2980,22 @@
         <v>14</v>
       </c>
       <c r="AK8" t="s">
+        <v>400</v>
+      </c>
+      <c r="AL8">
+        <v>14</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN8">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="297.75" customHeight="1">
+    <row r="9" spans="1:41" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2839,10 +3102,22 @@
         <v>14</v>
       </c>
       <c r="AK9" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="AL9">
+        <v>13</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="AN9">
+        <v>14</v>
+      </c>
+      <c r="AO9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="56.25">
+    <row r="10" spans="1:41" ht="93.75">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2949,10 +3224,22 @@
         <v>14</v>
       </c>
       <c r="AK10" t="s">
+        <v>404</v>
+      </c>
+      <c r="AL10">
+        <v>14</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="AN10">
+        <v>12</v>
+      </c>
+      <c r="AO10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="37.5">
+    <row r="11" spans="1:41" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3058,11 +3345,23 @@
       <c r="AJ11">
         <v>14</v>
       </c>
-      <c r="AK11" s="1" t="s">
+      <c r="AK11" t="s">
+        <v>398</v>
+      </c>
+      <c r="AL11">
+        <v>14</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AN11">
+        <v>14</v>
+      </c>
+      <c r="AO11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="56.25">
+    <row r="12" spans="1:41" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3169,11 +3468,23 @@
       <c r="AJ12">
         <v>14</v>
       </c>
-      <c r="AK12" s="1" t="s">
+      <c r="AK12" t="s">
+        <v>400</v>
+      </c>
+      <c r="AL12">
+        <v>14</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AN12">
+        <v>14</v>
+      </c>
+      <c r="AO12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="225" customHeight="1">
+    <row r="13" spans="1:41" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3282,11 +3593,23 @@
       <c r="AJ13">
         <v>10</v>
       </c>
-      <c r="AK13" s="1" t="s">
+      <c r="AK13" t="s">
+        <v>406</v>
+      </c>
+      <c r="AL13">
+        <v>14</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="AN13">
+        <v>10</v>
+      </c>
+      <c r="AO13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="252" customHeight="1">
+    <row r="14" spans="1:41" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3394,10 +3717,22 @@
         <v>12</v>
       </c>
       <c r="AK14" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AL14">
+        <v>13</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AN14">
+        <v>12</v>
+      </c>
+      <c r="AO14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="56.25">
+    <row r="15" spans="1:41" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3444,11 +3779,11 @@
       <c r="T15" s="1">
         <v>14</v>
       </c>
-      <c r="AK15" s="1" t="s">
+      <c r="AO15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="56.25">
+    <row r="16" spans="1:41" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3555,11 +3890,23 @@
       <c r="AJ16">
         <v>14</v>
       </c>
-      <c r="AK16" t="s">
+      <c r="AK16" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="AL16">
+        <v>14</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AN16">
+        <v>14</v>
+      </c>
+      <c r="AO16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="56.25">
+    <row r="17" spans="1:41" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3666,11 +4013,23 @@
       <c r="AJ17">
         <v>14</v>
       </c>
-      <c r="AK17" t="s">
+      <c r="AK17" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="AL17">
+        <v>12</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="AN17">
+        <v>14</v>
+      </c>
+      <c r="AO17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="56.25">
+    <row r="18" spans="1:41" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3776,11 +4135,23 @@
       <c r="AJ18">
         <v>14</v>
       </c>
-      <c r="AK18" t="s">
+      <c r="AK18" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="AL18">
+        <v>12</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="AN18">
+        <v>14</v>
+      </c>
+      <c r="AO18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="56.25">
+    <row r="19" spans="1:41" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3887,11 +4258,23 @@
       <c r="AJ19">
         <v>14</v>
       </c>
-      <c r="AK19" t="s">
+      <c r="AK19" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AL19">
+        <v>14</v>
+      </c>
+      <c r="AM19" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AN19">
+        <v>14</v>
+      </c>
+      <c r="AO19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="56.25">
+    <row r="20" spans="1:41" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3997,11 +4380,23 @@
       <c r="AJ20">
         <v>14</v>
       </c>
-      <c r="AK20" t="s">
+      <c r="AK20" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="AL20">
+        <v>12</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AN20">
+        <v>14</v>
+      </c>
+      <c r="AO20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="257.25" customHeight="1">
+    <row r="21" spans="1:41" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4111,10 +4506,22 @@
         <v>10</v>
       </c>
       <c r="AK21" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="AL21">
+        <v>13</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="AN21">
+        <v>10</v>
+      </c>
+      <c r="AO21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="409.5">
+    <row r="22" spans="1:41" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4221,10 +4628,22 @@
         <v>12</v>
       </c>
       <c r="AK22" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="AL22">
+        <v>12</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="AN22">
+        <v>12</v>
+      </c>
+      <c r="AO22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="409.5">
+    <row r="23" spans="1:41" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4331,10 +4750,22 @@
         <v>10</v>
       </c>
       <c r="AK23" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AL23">
+        <v>12</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN23">
+        <v>10</v>
+      </c>
+      <c r="AO23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="56.25">
+    <row r="24" spans="1:41" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4441,10 +4872,22 @@
         <v>14</v>
       </c>
       <c r="AK24" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="AL24">
+        <v>12</v>
+      </c>
+      <c r="AM24" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="AN24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AO24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="56.25">
+    <row r="25" spans="1:41" ht="93.75">
       <c r="A25">
         <v>23</v>
       </c>
@@ -4551,10 +4994,22 @@
         <v>14</v>
       </c>
       <c r="AK25" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="AL25">
+        <v>12</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN25" s="6">
+        <v>13</v>
+      </c>
+      <c r="AO25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="75">
+    <row r="26" spans="1:41" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -4661,10 +5116,22 @@
         <v>14</v>
       </c>
       <c r="AK26" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="AL26">
+        <v>12</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AN26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AO26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="56.25">
+    <row r="27" spans="1:41" ht="75">
       <c r="A27">
         <v>25</v>
       </c>
@@ -4771,10 +5238,22 @@
         <v>14</v>
       </c>
       <c r="AK27" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="AL27">
+        <v>10</v>
+      </c>
+      <c r="AM27" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN27" s="6">
+        <v>13</v>
+      </c>
+      <c r="AO27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="75">
+    <row r="28" spans="1:41" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4881,10 +5360,22 @@
         <v>14</v>
       </c>
       <c r="AK28" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="AL28">
+        <v>12</v>
+      </c>
+      <c r="AM28" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="AN28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AO28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:41">
       <c r="A29">
         <v>27</v>
       </c>
@@ -4914,8 +5405,12 @@
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
-    </row>
-    <row r="30" spans="1:37" ht="409.5">
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
+    </row>
+    <row r="30" spans="1:41" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5022,10 +5517,22 @@
         <v>10</v>
       </c>
       <c r="AK30" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="AL30" s="1">
+        <v>14</v>
+      </c>
+      <c r="AM30" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AN30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AO30" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="409.5">
+    <row r="31" spans="1:41" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5131,11 +5638,23 @@
       <c r="AJ31" s="1">
         <v>12</v>
       </c>
-      <c r="AK31" s="1" t="s">
+      <c r="AK31" t="s">
+        <v>438</v>
+      </c>
+      <c r="AL31" s="1">
+        <v>13</v>
+      </c>
+      <c r="AM31" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="AN31" s="1">
+        <v>12</v>
+      </c>
+      <c r="AO31" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="375">
+    <row r="32" spans="1:41" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5241,7 +5760,19 @@
       <c r="AJ32" s="1">
         <v>14</v>
       </c>
-      <c r="AK32" s="1" t="s">
+      <c r="AK32" t="s">
+        <v>440</v>
+      </c>
+      <c r="AL32" s="1">
+        <v>16</v>
+      </c>
+      <c r="AM32" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="AN32" s="1">
+        <v>14</v>
+      </c>
+      <c r="AO32" s="1" t="s">
         <v>367</v>
       </c>
     </row>
@@ -10045,22 +10576,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:37">
+    <row r="993" spans="1:41">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:37">
+    <row r="994" spans="1:41">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:37">
+    <row r="995" spans="1:41">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:37">
+    <row r="996" spans="1:41">
       <c r="A996">
         <v>994</v>
       </c>
@@ -10161,10 +10692,22 @@
         <v>14</v>
       </c>
       <c r="AK996" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL996">
+        <v>14</v>
+      </c>
+      <c r="AM996" t="s">
+        <v>266</v>
+      </c>
+      <c r="AN996">
+        <v>14</v>
+      </c>
+      <c r="AO996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:37" ht="93.75">
+    <row r="997" spans="1:41" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -10267,11 +10810,23 @@
       <c r="AJ997">
         <v>14</v>
       </c>
-      <c r="AK997" s="1" t="s">
+      <c r="AK997" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL997">
+        <v>14</v>
+      </c>
+      <c r="AM997" t="s">
+        <v>267</v>
+      </c>
+      <c r="AN997">
+        <v>14</v>
+      </c>
+      <c r="AO997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:37" ht="75">
+    <row r="998" spans="1:41" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -10371,11 +10926,23 @@
       <c r="AJ998">
         <v>14</v>
       </c>
-      <c r="AK998" s="1" t="s">
+      <c r="AK998" t="s">
+        <v>145</v>
+      </c>
+      <c r="AL998">
+        <v>14</v>
+      </c>
+      <c r="AM998" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AN998">
+        <v>14</v>
+      </c>
+      <c r="AO998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:37" ht="75">
+    <row r="999" spans="1:41" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -10475,11 +11042,23 @@
       <c r="AJ999">
         <v>14</v>
       </c>
-      <c r="AK999" s="1" t="s">
+      <c r="AK999" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL999">
+        <v>14</v>
+      </c>
+      <c r="AM999" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AN999">
+        <v>14</v>
+      </c>
+      <c r="AO999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:37" ht="75">
+    <row r="1000" spans="1:41" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -10580,10 +11159,22 @@
         <v>14</v>
       </c>
       <c r="AK1000" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL1000">
+        <v>14</v>
+      </c>
+      <c r="AM1000" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN1000">
+        <v>14</v>
+      </c>
+      <c r="AO1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:37">
+    <row r="1001" spans="1:41">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -10684,10 +11275,22 @@
         <v>14</v>
       </c>
       <c r="AK1001" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL1001">
+        <v>14</v>
+      </c>
+      <c r="AM1001" t="s">
+        <v>271</v>
+      </c>
+      <c r="AN1001">
+        <v>14</v>
+      </c>
+      <c r="AO1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:37">
+    <row r="1002" spans="1:41">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -10776,6 +11379,15 @@
         <v>0</v>
       </c>
       <c r="AI1002" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL1002">
+        <v>0</v>
+      </c>
+      <c r="AM1002" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168B685D-2E2F-436B-9B6C-9847A500F405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFCDD5B-EF8A-4DFC-932D-97FAA07B6654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="495">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -1829,6 +1829,190 @@
     <t>Издалека донеслось, как ребёнок что-то напевает, а как только песенка закончилась, он вдруг бросился бежать прямо ко мне.
 Я много раз задерживал его и думал, что оторвался, но он всё равно меня выслеживает. Почему он всегда знает, где я…
 От других чудовищ мне повезло уйти, но на этот раз, похоже, мне конец…</t>
+  </si>
+  <si>
+    <t>itemNameGerman</t>
+  </si>
+  <si>
+    <t>itemNameSizeGerman</t>
+  </si>
+  <si>
+    <t>itemDescriptionGerman</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizeGerman</t>
+  </si>
+  <si>
+    <t>Leiche eines Jungen im Park</t>
+  </si>
+  <si>
+    <t>Eilmeldung! Leiche eines Jungen im Park gefunden! Was war die Tatwaffe?
+In den frühen Morgenstunden des ×. ● wurde in der Nähe des △△-Parks in der Stadt die Leiche eines Jungen (geschätztes Alter 12–14 Jahre) gefunden. Der Fundort liegt an einem bei Anwohnern beliebten Spazierweg; ein Passant entdeckte die Leiche bei seinem Morgenspaziergang.
+Die Leiche wies keine sichtbaren äußeren Verletzungen auf, ein „Fremdverschulden ist unklar“. Zudem wurde laut Ermittlern in der Nähe des Fundorts offenbar keine Tatwaffe gefunden.
+Die Identität des Jungen ist noch nicht geklärt; die Polizei befragt die Anwohner.
+Die Ermittlungen gestalten sich schwierig – weitere Meldungen werden erwartet.</t>
+  </si>
+  <si>
+    <t>Schlaftabletten</t>
+  </si>
+  <si>
+    <t>Ein starkes Schlafmittel, das Schlafmangel behebt, wenn man es 1–2 Stunden vor dem Schlafengehen einnimmt.</t>
+  </si>
+  <si>
+    <t>Messer</t>
+  </si>
+  <si>
+    <t>Ein altes Messer mit scharfer Klinge.</t>
+  </si>
+  <si>
+    <t>Hammer</t>
+  </si>
+  <si>
+    <t>Ein schwerer Hammer aus Eisen.</t>
+  </si>
+  <si>
+    <t>Seil</t>
+  </si>
+  <si>
+    <t>Ein dickes, robustes Seil mit ausgefransten Enden.</t>
+  </si>
+  <si>
+    <t>Ein Mann wurde in seiner Wohnung ermordet aufgefunden. Am Kopf fanden sich Spuren heftiger Schläge; die Polizei ermittelt und geht von einem stumpfen Gegenstand als Tatwaffe aus.</t>
+  </si>
+  <si>
+    <t>Axt</t>
+  </si>
+  <si>
+    <t>Eine schwere Axt, deren Klinge schartiger ist, als es den Anschein hat.</t>
+  </si>
+  <si>
+    <t>Ausdauer-Booster</t>
+  </si>
+  <si>
+    <t>Bei Benutzung: Verringert für eine gewisse Zeit den Ausdauerverbrauch und erhöht die Ausdauerregeneration.</t>
+  </si>
+  <si>
+    <t>Seltsamer Kompass</t>
+  </si>
+  <si>
+    <t>In der Nadel steckt ein Splitter einer blauen Kugel, daher zeigt sie stets in die Richtung, in der sich eine Blaue Kugel des Urteils befindet.</t>
+  </si>
+  <si>
+    <t>Modell eines Krankenhausbetts</t>
+  </si>
+  <si>
+    <t>Auf der Rückseite des Modells steht „Krankheit“.</t>
+  </si>
+  <si>
+    <t>Modell eines Bahnübergangs</t>
+  </si>
+  <si>
+    <t>Auf der Rückseite des Modells steht „Überfahren“.</t>
+  </si>
+  <si>
+    <t>Modell eines eingestürzten Gebäudes</t>
+  </si>
+  <si>
+    <t>Auf der Rückseite des Modells steht „Zerquetscht“.</t>
+  </si>
+  <si>
+    <t>Modell eines Kamins</t>
+  </si>
+  <si>
+    <t>Auf der Rückseite des Modells steht „Verbrannt“.</t>
+  </si>
+  <si>
+    <t>Modell eines Schwimmbeckens</t>
+  </si>
+  <si>
+    <t>Auf der Rückseite des Modells steht „Ertrunken“.</t>
+  </si>
+  <si>
+    <t>Knallbonbon</t>
+  </si>
+  <si>
+    <t>Setzt man es gegen einen Umherirrenden direkt vor sich ein, erschrickt er und kann sich eine Weile nicht bewegen. Allerdings gibt es dabei einen lauten Knall.</t>
+  </si>
+  <si>
+    <t>Eine Geschichte über einen besten Freund</t>
+  </si>
+  <si>
+    <t>An meinen einstigen besten Freund
+Weißt du noch, wie wir als Kinder immer zusammen im △△-Park in der Nähe gespielt haben?
+„Wir bleiben für immer zusammen.“
+Diese Worte, die du an jenem Tag auf der Parkbank zu mir gesagt hast, habe ich bis heute deutlich in Erinnerung.
+Doch mit jeder Jahreszeit kamst du seltener in den Park …
+Als wir uns das letzte Mal sahen, lagst du kalt da und hast dich nicht mehr gerührt. Du hast meinen Namen nie wieder mit deiner sanften Stimme gerufen …
+Ich habe die Tage ohne dich ertragen, aber der Schmerz ist zu groß, ich kann nicht mehr.
+Deshalb komme ich jetzt zu dir.</t>
+  </si>
+  <si>
+    <t>Nachtrag! Leiche eines Jungen im Park</t>
+  </si>
+  <si>
+    <t>Zur Leiche des im △△-Park gefundenen Jungen setzt die Polizei ihre Befragungen in der Umgebung fort.
+Befragt wurden sieben Schüler, die an seiner Schule mit dem Jungen zu tun hatten. Nach den Aussagen über seine Schulsachen vermutet die Polizei, dass einige von ihnen lügen könnten.
+A: Im Werkunterricht hat er eine neue Sprühdose nur ganz kurz auf Holz benutzt.
+B: Sein Schulbuch ist nach jahrelangem Gebrauch völlig zerfleddert.
+C: Ich habe einmal gesehen, wie jemand Nadeln in seine Hausschuhe gesteckt hat.
+D: Ich stimme A zu.
+E: Sein Heft ist neu und kaum benutzt.
+F: Ich stimme B zu. C lügt.
+G: Ich stimme C zu. A lügt.</t>
+  </si>
+  <si>
+    <t>Hausschuhe</t>
+  </si>
+  <si>
+    <t>Bei genauerem Hinsehen sind Nadeln darin versteckt.</t>
+  </si>
+  <si>
+    <t>Schulbuch</t>
+  </si>
+  <si>
+    <t>So zerfleddert, dass es unmöglich natürlich sein kann.</t>
+  </si>
+  <si>
+    <t>Ein schmutziger Schuh</t>
+  </si>
+  <si>
+    <t>Mit Sprühfarbe übermalt und stark verschmutzt.</t>
+  </si>
+  <si>
+    <t>Sprühdose</t>
+  </si>
+  <si>
+    <t>Sprühfarbe. Sie ist fast leer.</t>
+  </si>
+  <si>
+    <t>Neues Heft</t>
+  </si>
+  <si>
+    <t>Bei genauerem Hinsehen sind einige Seiten zusammengeklebt.</t>
+  </si>
+  <si>
+    <t>Der in der Stille Entbrennende</t>
+  </si>
+  <si>
+    <t>Ich würde gern sagen: „Mein Name ist …“, aber mein Name wurde vernichtet, und ich kann mich nicht mehr erinnern. Deshalb halte ich hier fest, was in diesem Labyrinth geschehen ist.
+Wir haben das Labyrinth zu mehreren erkundet, aber einer von uns wurde von einem rothäutigen Ungeheuer im Anzug gepackt. Ich bin sofort geflohen und weiß nicht, was danach aus ihm wurde. Während ich mich verstecke und versuche, die Lage zu ordnen, will ich die Eigenschaften dieses Ungeheuers auf meine Weise analysieren.
+Zunächst zu dem, der gepackt wurde: Er hielt die Angst nicht aus, geriet in Panik, rannte herum und machte laute Geräusche. Vermutlich wurde er deshalb entdeckt. Außerdem habe ich einmal versehentlich in der Nähe des Ungeheuers meine Lampe eingeschaltet, doch mein Versteck wurde nicht verraten – wohl weil es grelles Licht nicht wahrnehmen kann.</t>
+  </si>
+  <si>
+    <t>Die Betörende des Vergessens</t>
+  </si>
+  <si>
+    <t>Irgendwoher hörte ich eine Frauenstimme, und als ich aus meiner Deckung spähte, um nachzusehen, geschah es: Eine braunhaarige Frau ohne Ohren bemerkte mich und stürzte sich schreiend und rasend auf mich.
+Ich hatte Glück und konnte mich in eine Deckung rollen, doch stattdessen nahm sie jemanden in der Nähe ins Visier. Ich habe nur überlebt, weil die beiden mit dem Ungeheuer in die Ferne davonliefen – aber wahrscheinlich wurde der andere meinetwegen angegriffen.
+Sie greift nicht nur an, wenn sie einen sieht: Wird sie angeleuchtet, verliert sie völlig die Beherrschung und stürmt los. Benutze ihr gegenüber also auf keinen Fall Licht.</t>
+  </si>
+  <si>
+    <t>Der singende Umherirrende</t>
+  </si>
+  <si>
+    <t>Aus der Ferne hörte ich ein Kind summen, und in dem Moment, als das Lied endete, rannte es plötzlich direkt auf mich zu.
+Ich habe es immer wieder aufgehalten und dachte, ich sei entkommen, aber es verfolgt mich ständig. Warum weiß es immer, wo ich bin …
+Den anderen Ungeheuern bin ich mit Glück entkommen, aber diesmal ist es vielleicht wirklich aus mit mir …</t>
   </si>
 </sst>
 </file>
@@ -2206,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO1002"/>
+  <dimension ref="A1:AS1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2247,9 +2431,13 @@
     <col min="38" max="38" width="22.75" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="70.625" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="50.125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="28.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2371,16 +2559,28 @@
         <v>391</v>
       </c>
       <c r="AO1" t="s">
+        <v>442</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>444</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>445</v>
+      </c>
+      <c r="AS1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:45">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:41" ht="409.5">
+    <row r="3" spans="1:45" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2499,10 +2699,22 @@
         <v>11</v>
       </c>
       <c r="AO3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="AP3">
+        <v>12</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="AR3">
+        <v>11</v>
+      </c>
+      <c r="AS3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="228" customHeight="1">
+    <row r="4" spans="1:45" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2621,10 +2833,22 @@
         <v>14</v>
       </c>
       <c r="AO4" t="s">
+        <v>448</v>
+      </c>
+      <c r="AP4">
+        <v>14</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="AR4">
+        <v>13</v>
+      </c>
+      <c r="AS4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="92.25" customHeight="1">
+    <row r="5" spans="1:45" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2743,10 +2967,22 @@
         <v>14</v>
       </c>
       <c r="AO5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AP5">
+        <v>14</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="AR5">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="37.5">
+    <row r="6" spans="1:45" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2865,15 +3101,27 @@
         <v>14</v>
       </c>
       <c r="AO6" t="s">
+        <v>452</v>
+      </c>
+      <c r="AP6">
+        <v>14</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="AR6">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:45">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="56.25">
+    <row r="8" spans="1:45" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2992,10 +3240,22 @@
         <v>14</v>
       </c>
       <c r="AO8" t="s">
+        <v>454</v>
+      </c>
+      <c r="AP8">
+        <v>14</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="AR8">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="297.75" customHeight="1">
+    <row r="9" spans="1:45" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3114,10 +3374,22 @@
         <v>14</v>
       </c>
       <c r="AO9" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AP9">
+        <v>14</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AR9">
+        <v>14</v>
+      </c>
+      <c r="AS9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="93.75">
+    <row r="10" spans="1:45" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3236,10 +3508,22 @@
         <v>12</v>
       </c>
       <c r="AO10" t="s">
+        <v>457</v>
+      </c>
+      <c r="AP10">
+        <v>14</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="AR10">
+        <v>12</v>
+      </c>
+      <c r="AS10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="37.5">
+    <row r="11" spans="1:45" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3357,11 +3641,23 @@
       <c r="AN11">
         <v>14</v>
       </c>
-      <c r="AO11" s="1" t="s">
+      <c r="AO11" t="s">
+        <v>452</v>
+      </c>
+      <c r="AP11">
+        <v>14</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="AR11">
+        <v>13</v>
+      </c>
+      <c r="AS11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="56.25">
+    <row r="12" spans="1:45" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3480,11 +3776,23 @@
       <c r="AN12">
         <v>14</v>
       </c>
-      <c r="AO12" s="1" t="s">
+      <c r="AO12" t="s">
+        <v>454</v>
+      </c>
+      <c r="AP12">
+        <v>14</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="AR12">
+        <v>14</v>
+      </c>
+      <c r="AS12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="225" customHeight="1">
+    <row r="13" spans="1:45" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3605,11 +3913,23 @@
       <c r="AN13">
         <v>10</v>
       </c>
-      <c r="AO13" s="1" t="s">
+      <c r="AO13" t="s">
+        <v>459</v>
+      </c>
+      <c r="AP13">
+        <v>14</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="AR13">
+        <v>10</v>
+      </c>
+      <c r="AS13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="252" customHeight="1">
+    <row r="14" spans="1:45" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3729,10 +4049,22 @@
         <v>12</v>
       </c>
       <c r="AO14" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="AP14">
+        <v>14</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="AR14">
+        <v>11</v>
+      </c>
+      <c r="AS14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="56.25">
+    <row r="15" spans="1:45" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3779,11 +4111,11 @@
       <c r="T15" s="1">
         <v>14</v>
       </c>
-      <c r="AO15" s="1" t="s">
+      <c r="AS15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="56.25">
+    <row r="16" spans="1:45" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3902,11 +4234,23 @@
       <c r="AN16">
         <v>14</v>
       </c>
-      <c r="AO16" t="s">
+      <c r="AO16" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="AP16">
+        <v>14</v>
+      </c>
+      <c r="AQ16" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="AR16">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="56.25">
+    <row r="17" spans="1:45" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4025,11 +4369,23 @@
       <c r="AN17">
         <v>14</v>
       </c>
-      <c r="AO17" t="s">
+      <c r="AO17" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="AP17">
+        <v>14</v>
+      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AR17">
+        <v>14</v>
+      </c>
+      <c r="AS17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="56.25">
+    <row r="18" spans="1:45" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4147,11 +4503,23 @@
       <c r="AN18">
         <v>14</v>
       </c>
-      <c r="AO18" t="s">
+      <c r="AO18" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="AP18">
+        <v>12</v>
+      </c>
+      <c r="AQ18" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="AR18">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="56.25">
+    <row r="19" spans="1:45" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4270,11 +4638,23 @@
       <c r="AN19">
         <v>14</v>
       </c>
-      <c r="AO19" t="s">
+      <c r="AO19" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="AP19">
+        <v>14</v>
+      </c>
+      <c r="AQ19" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="AR19">
+        <v>14</v>
+      </c>
+      <c r="AS19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="56.25">
+    <row r="20" spans="1:45" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4392,11 +4772,23 @@
       <c r="AN20">
         <v>14</v>
       </c>
-      <c r="AO20" t="s">
+      <c r="AO20" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="AP20">
+        <v>12</v>
+      </c>
+      <c r="AQ20" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="AR20">
+        <v>14</v>
+      </c>
+      <c r="AS20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="257.25" customHeight="1">
+    <row r="21" spans="1:45" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4518,10 +4910,22 @@
         <v>10</v>
       </c>
       <c r="AO21" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="AP21">
+        <v>14</v>
+      </c>
+      <c r="AQ21" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="AR21">
+        <v>10</v>
+      </c>
+      <c r="AS21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="409.5">
+    <row r="22" spans="1:45" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -4640,10 +5044,22 @@
         <v>12</v>
       </c>
       <c r="AO22" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="AP22">
+        <v>12</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="AR22">
+        <v>12</v>
+      </c>
+      <c r="AS22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="409.5">
+    <row r="23" spans="1:45" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -4762,10 +5178,22 @@
         <v>10</v>
       </c>
       <c r="AO23" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="AP23">
+        <v>12</v>
+      </c>
+      <c r="AQ23" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="AR23">
+        <v>10</v>
+      </c>
+      <c r="AS23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="56.25">
+    <row r="24" spans="1:45" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -4884,10 +5312,22 @@
         <v>14</v>
       </c>
       <c r="AO24" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AP24">
+        <v>12</v>
+      </c>
+      <c r="AQ24" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="AR24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AS24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="93.75">
+    <row r="25" spans="1:45" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5006,10 +5446,22 @@
         <v>13</v>
       </c>
       <c r="AO25" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="AP25">
+        <v>12</v>
+      </c>
+      <c r="AQ25" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="AR25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AS25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="75">
+    <row r="26" spans="1:45" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5128,10 +5580,22 @@
         <v>14</v>
       </c>
       <c r="AO26" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="AP26">
+        <v>12</v>
+      </c>
+      <c r="AQ26" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AR26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AS26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="75">
+    <row r="27" spans="1:45" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5250,10 +5714,22 @@
         <v>13</v>
       </c>
       <c r="AO27" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="AP27">
+        <v>12</v>
+      </c>
+      <c r="AQ27" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="AR27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AS27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="75">
+    <row r="28" spans="1:45" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5372,10 +5848,22 @@
         <v>14</v>
       </c>
       <c r="AO28" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="AP28">
+        <v>12</v>
+      </c>
+      <c r="AQ28" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="AR28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AS28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:41">
+    <row r="29" spans="1:45">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5409,8 +5897,12 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
-    </row>
-    <row r="30" spans="1:41" ht="409.5">
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="1"/>
+      <c r="AR29" s="1"/>
+      <c r="AS29" s="1"/>
+    </row>
+    <row r="30" spans="1:45" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -5529,10 +6021,22 @@
         <v>10</v>
       </c>
       <c r="AO30" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="AP30" s="1">
+        <v>16</v>
+      </c>
+      <c r="AQ30" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="AR30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AS30" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="1:41" ht="409.5">
+    <row r="31" spans="1:45" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -5650,11 +6154,23 @@
       <c r="AN31" s="1">
         <v>12</v>
       </c>
-      <c r="AO31" s="1" t="s">
+      <c r="AO31" t="s">
+        <v>491</v>
+      </c>
+      <c r="AP31" s="1">
+        <v>16</v>
+      </c>
+      <c r="AQ31" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="AR31" s="1">
+        <v>12</v>
+      </c>
+      <c r="AS31" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="32" spans="1:41" ht="375">
+    <row r="32" spans="1:45" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -5772,7 +6288,19 @@
       <c r="AN32" s="1">
         <v>14</v>
       </c>
-      <c r="AO32" s="1" t="s">
+      <c r="AO32" t="s">
+        <v>493</v>
+      </c>
+      <c r="AP32" s="1">
+        <v>16</v>
+      </c>
+      <c r="AQ32" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="AR32" s="1">
+        <v>14</v>
+      </c>
+      <c r="AS32" s="1" t="s">
         <v>367</v>
       </c>
     </row>
@@ -10576,22 +11104,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:41">
+    <row r="993" spans="1:45">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:41">
+    <row r="994" spans="1:45">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:41">
+    <row r="995" spans="1:45">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:41">
+    <row r="996" spans="1:45">
       <c r="A996">
         <v>994</v>
       </c>
@@ -10704,10 +11232,22 @@
         <v>14</v>
       </c>
       <c r="AO996" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP996">
+        <v>14</v>
+      </c>
+      <c r="AQ996" t="s">
+        <v>266</v>
+      </c>
+      <c r="AR996">
+        <v>14</v>
+      </c>
+      <c r="AS996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:41" ht="93.75">
+    <row r="997" spans="1:45" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -10822,11 +11362,23 @@
       <c r="AN997">
         <v>14</v>
       </c>
-      <c r="AO997" s="1" t="s">
+      <c r="AO997" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP997">
+        <v>14</v>
+      </c>
+      <c r="AQ997" t="s">
+        <v>267</v>
+      </c>
+      <c r="AR997">
+        <v>14</v>
+      </c>
+      <c r="AS997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:41" ht="75">
+    <row r="998" spans="1:45" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -10938,11 +11490,23 @@
       <c r="AN998">
         <v>14</v>
       </c>
-      <c r="AO998" s="1" t="s">
+      <c r="AO998" t="s">
+        <v>145</v>
+      </c>
+      <c r="AP998">
+        <v>14</v>
+      </c>
+      <c r="AQ998" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AR998">
+        <v>14</v>
+      </c>
+      <c r="AS998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:41" ht="75">
+    <row r="999" spans="1:45" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -11054,11 +11618,23 @@
       <c r="AN999">
         <v>14</v>
       </c>
-      <c r="AO999" s="1" t="s">
+      <c r="AO999" t="s">
+        <v>147</v>
+      </c>
+      <c r="AP999">
+        <v>14</v>
+      </c>
+      <c r="AQ999" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AR999">
+        <v>14</v>
+      </c>
+      <c r="AS999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:41" ht="75">
+    <row r="1000" spans="1:45" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -11171,10 +11747,22 @@
         <v>14</v>
       </c>
       <c r="AO1000" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AP1000">
+        <v>14</v>
+      </c>
+      <c r="AQ1000" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AR1000">
+        <v>14</v>
+      </c>
+      <c r="AS1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:41">
+    <row r="1001" spans="1:45">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -11287,10 +11875,22 @@
         <v>14</v>
       </c>
       <c r="AO1001" t="s">
+        <v>151</v>
+      </c>
+      <c r="AP1001">
+        <v>14</v>
+      </c>
+      <c r="AQ1001" t="s">
+        <v>271</v>
+      </c>
+      <c r="AR1001">
+        <v>14</v>
+      </c>
+      <c r="AS1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:41">
+    <row r="1002" spans="1:45">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -11388,6 +11988,15 @@
         <v>0</v>
       </c>
       <c r="AM1002" t="s">
+        <v>153</v>
+      </c>
+      <c r="AO1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP1002">
+        <v>0</v>
+      </c>
+      <c r="AQ1002" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFCDD5B-EF8A-4DFC-932D-97FAA07B6654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4C5E21-8FDC-437C-84C4-C6AED34B205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="549">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -2013,6 +2013,193 @@
     <t>Aus der Ferne hörte ich ein Kind summen, und in dem Moment, als das Lied endete, rannte es plötzlich direkt auf mich zu.
 Ich habe es immer wieder aufgehalten und dachte, ich sei entkommen, aber es verfolgt mich ständig. Warum weiß es immer, wo ich bin …
 Den anderen Ungeheuern bin ich mit Glück entkommen, aber diesmal ist es vielleicht wirklich aus mit mir …</t>
+  </si>
+  <si>
+    <t>itemNameFrench</t>
+  </si>
+  <si>
+    <t>itemNameSizeFrench</t>
+  </si>
+  <si>
+    <t>itemDescriptionFrench</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizeFrench</t>
+  </si>
+  <si>
+    <t>Corps d'un garçon dans un parc</t>
+  </si>
+  <si>
+    <t>Flash spécial ! Le corps d'un garçon retrouvé dans un parc ! Quelle était l'arme du crime ?
+Aux premières heures du × ●, le corps d'un garçon (âgé de 12 à 14 ans selon les estimations) a été découvert près du parc △△, en ville. Les lieux se situent le long d'une promenade appréciée des habitants, et le corps a été découvert par un passant lors de sa promenade matinale.
+Le corps ne présentait aucune blessure apparente, et « le caractère criminel reste indéterminé ». De plus, selon les enquêteurs, aucune arme n'aurait été retrouvée à proximité.
+L'identité du garçon n'a toujours pas été établie, et la police interroge les riverains.
+L'enquête piétine ; la suite est attendue.</t>
+  </si>
+  <si>
+    <t>Somnifères</t>
+  </si>
+  <si>
+    <t>Un somnifère puissant qui soulage le manque de sommeil s'il est pris 1 à 2 heures avant le coucher.</t>
+  </si>
+  <si>
+    <t>Couteau</t>
+  </si>
+  <si>
+    <t>Un vieux couteau à la lame acérée.</t>
+  </si>
+  <si>
+    <t>Marteau</t>
+  </si>
+  <si>
+    <t>Un lourd marteau en fer.</t>
+  </si>
+  <si>
+    <t>Corde</t>
+  </si>
+  <si>
+    <t>Une corde épaisse et solide, aux extrémités effilochées.</t>
+  </si>
+  <si>
+    <t>Tutoriel</t>
+  </si>
+  <si>
+    <t>Un homme a été retrouvé assassiné chez lui. Sa tête portait des traces de coups violents, et la police a ouvert une enquête, soupçonnant un objet contondant.</t>
+  </si>
+  <si>
+    <t>Hache</t>
+  </si>
+  <si>
+    <t>Une lourde hache, plus ébréchée qu'il n'y paraît.</t>
+  </si>
+  <si>
+    <t>Stimulant d'endurance</t>
+  </si>
+  <si>
+    <t>Utilisation : réduit la consommation d'endurance et augmente sa récupération pendant un certain temps.</t>
+  </si>
+  <si>
+    <t>Boussole étrange</t>
+  </si>
+  <si>
+    <t>Son aiguille contient un éclat d'orbe bleu ; elle indique toujours la direction d'un Orbe bleu du Jugement.</t>
+  </si>
+  <si>
+    <t>Maquette de lit d'hôpital</t>
+  </si>
+  <si>
+    <t>Au dos de la maquette est inscrit « Maladie ».</t>
+  </si>
+  <si>
+    <t>Maquette de passage à niveau</t>
+  </si>
+  <si>
+    <t>Au dos de la maquette est inscrit « Écrasé par un train ».</t>
+  </si>
+  <si>
+    <t>Maquette d'immeuble effondré</t>
+  </si>
+  <si>
+    <t>Au dos de la maquette est inscrit « Écrasement ».</t>
+  </si>
+  <si>
+    <t>Maquette de cheminée</t>
+  </si>
+  <si>
+    <t>Au dos de la maquette est inscrit « Brûlure ».</t>
+  </si>
+  <si>
+    <t>Maquette de piscine</t>
+  </si>
+  <si>
+    <t>Au dos de la maquette est inscrit « Noyade ».</t>
+  </si>
+  <si>
+    <t>Pétard</t>
+  </si>
+  <si>
+    <t>Utilisé contre un Errant proche, juste devant vous, il l'étourdit et l'empêche d'agir un moment. Mais il produit un bruit très fort.</t>
+  </si>
+  <si>
+    <t>Histoire d'un meilleur ami</t>
+  </si>
+  <si>
+    <t>À mon ancien meilleur ami
+Tu te souviens, quand on était petits, on jouait toujours ensemble au parc △△ tout près ?
+« On sera toujours ensemble. »
+Ces mots que tu m'as dits ce jour-là, sur le banc du parc, je m'en souviens encore parfaitement.
+Mais à chaque saison qui passait, tu venais de moins en moins souvent au parc…
+La dernière fois que je t'ai vu, tu étais allongé, froid, sans bouger d'un pouce, et tu ne m'as plus jamais appelé par mon nom de ta douce voix…
+J'ai supporté les jours sans toi, mais la douleur est trop forte, je n'en peux plus.
+Alors je viens te rejoindre.</t>
+  </si>
+  <si>
+    <t>Suite ! Corps d'un garçon dans un parc</t>
+  </si>
+  <si>
+    <t>Concernant le corps du garçon retrouvé au parc △△, la police poursuit son enquête de voisinage.
+Sept élèves ayant eu des liens avec le garçon à l'école ont été interrogés. D'après leurs déclarations sur ses affaires scolaires, la police soupçonne que plusieurs d'entre eux mentent.
+A : En cours de menuiserie, il a utilisé un tout petit peu d'une bombe de peinture neuve sur du bois.
+B : À force d'années d'usage, son manuel est complètement en lambeaux.
+C : J'ai vu quelqu'un mettre des aiguilles dans ses chaussons.
+D : Je suis d'accord avec A.
+E : Son cahier est neuf, il n'a presque pas servi.
+F : Je suis d'accord avec B. C ment.
+G : Je suis d'accord avec C. A ment.</t>
+  </si>
+  <si>
+    <t>Chaussons</t>
+  </si>
+  <si>
+    <t>En regardant bien, des aiguilles y sont dissimulées.</t>
+  </si>
+  <si>
+    <t>Manuel scolaire</t>
+  </si>
+  <si>
+    <t>Abîmé à un point qui ne peut pas être naturel.</t>
+  </si>
+  <si>
+    <t>Une chaussure sale</t>
+  </si>
+  <si>
+    <t>Recouverte de peinture en bombe et très salie.</t>
+  </si>
+  <si>
+    <t>Bombe de peinture</t>
+  </si>
+  <si>
+    <t>Une bombe de peinture. Elle est presque vide.</t>
+  </si>
+  <si>
+    <t>Cahier neuf</t>
+  </si>
+  <si>
+    <t>En regardant bien, certaines pages sont collées entre elles.</t>
+  </si>
+  <si>
+    <t>L'Errant qui s'embrase dans le silence</t>
+  </si>
+  <si>
+    <t>J'aimerais dire « Je m'appelle… », mais mon nom a été anéanti et je ne m'en souviens plus. Alors je note ici ce qui s'est passé dans ce labyrinthe.
+Nous explorions le labyrinthe à plusieurs, mais l'un de nous a été attrapé par un monstre à la peau rouge vêtu d'un costume. J'ai fui aussitôt, et je ne sais pas ce qu'il est devenu. Caché, j'essaie de faire le point et d'analyser à ma façon les caractéristiques de ce monstre.
+D'abord, celui qui a été attrapé n'a pas supporté la peur : il a paniqué, a couru et a fait beaucoup de bruit. C'est sans doute pour ça qu'il a été repéré. Et une fois, j'ai allumé ma lampe par mégarde près du monstre, mais ma position n'a pas été découverte, sans doute parce qu'il ne perçoit pas la lumière vive.</t>
+  </si>
+  <si>
+    <t>L'Envoûtante de l'oubli</t>
+  </si>
+  <si>
+    <t>J'ai entendu une voix de femme venant de quelque part, et c'est au moment où j'ai jeté un œil depuis ma cachette que c'est arrivé : une femme aux cheveux bruns, sans oreilles, m'a remarqué et s'est ruée sur moi en hurlant avec rage.
+J'ai eu de la chance et j'ai pu rouler à couvert, mais c'est quelqu'un d'autre, tout près, qui a été pris pour cible. Je n'ai survécu que parce qu'ils sont partis au loin avec le monstre, mais cette personne a sans doute été attaquée à cause de moi.
+Il ne suffit pas qu'elle te voie : si on l'éclaire, elle perd la raison et charge. Bref, n'utilise jamais de lumière contre elle.</t>
+  </si>
+  <si>
+    <t>L'Errant qui chante</t>
+  </si>
+  <si>
+    <t>J'ai entendu au loin un enfant fredonner, et dès que la chanson s'est terminée, il s'est soudain mis à courir droit sur moi.
+Je l'ai retardé maintes fois et je pensais l'avoir semé, mais il continue de me traquer. Pourquoi sait-il toujours où je suis…
+J'ai eu la chance d'échapper aux autres monstres, mais cette fois, c'est peut-être vraiment la fin pour moi…</t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS1002"/>
+  <dimension ref="A1:AW1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2435,9 +2622,13 @@
     <col min="42" max="42" width="22.75" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="50.125" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="46.5" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="27.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:49">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2571,16 +2762,28 @@
         <v>445</v>
       </c>
       <c r="AS1" t="s">
+        <v>495</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>496</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>498</v>
+      </c>
+      <c r="AW1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:45">
+    <row r="2" spans="1:49">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:45" ht="409.5">
+    <row r="3" spans="1:49" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2711,10 +2914,22 @@
         <v>11</v>
       </c>
       <c r="AS3" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="AT3">
+        <v>12</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:45" ht="228" customHeight="1">
+    <row r="4" spans="1:49" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2845,10 +3060,22 @@
         <v>13</v>
       </c>
       <c r="AS4" t="s">
+        <v>501</v>
+      </c>
+      <c r="AT4">
+        <v>14</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="AV4">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:45" ht="92.25" customHeight="1">
+    <row r="5" spans="1:49" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2979,10 +3206,22 @@
         <v>14</v>
       </c>
       <c r="AS5" t="s">
+        <v>503</v>
+      </c>
+      <c r="AT5">
+        <v>14</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="AV5">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="37.5">
+    <row r="6" spans="1:49" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3113,15 +3352,27 @@
         <v>13</v>
       </c>
       <c r="AS6" t="s">
+        <v>505</v>
+      </c>
+      <c r="AT6">
+        <v>14</v>
+      </c>
+      <c r="AU6" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="AV6">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:45">
+    <row r="7" spans="1:49">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:45" ht="56.25">
+    <row r="8" spans="1:49" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3252,10 +3503,22 @@
         <v>14</v>
       </c>
       <c r="AS8" t="s">
+        <v>507</v>
+      </c>
+      <c r="AT8">
+        <v>14</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="AV8">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="297.75" customHeight="1">
+    <row r="9" spans="1:49" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3386,10 +3649,22 @@
         <v>14</v>
       </c>
       <c r="AS9" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="AT9">
+        <v>14</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="AV9">
+        <v>14</v>
+      </c>
+      <c r="AW9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:45" ht="56.25">
+    <row r="10" spans="1:49" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3520,10 +3795,22 @@
         <v>12</v>
       </c>
       <c r="AS10" t="s">
+        <v>511</v>
+      </c>
+      <c r="AT10">
+        <v>14</v>
+      </c>
+      <c r="AU10" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="AV10">
+        <v>14</v>
+      </c>
+      <c r="AW10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:45" ht="37.5">
+    <row r="11" spans="1:49" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3653,11 +3940,23 @@
       <c r="AR11">
         <v>13</v>
       </c>
-      <c r="AS11" s="1" t="s">
+      <c r="AS11" t="s">
+        <v>505</v>
+      </c>
+      <c r="AT11">
+        <v>14</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="AV11">
+        <v>14</v>
+      </c>
+      <c r="AW11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="56.25">
+    <row r="12" spans="1:49" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3788,11 +4087,23 @@
       <c r="AR12">
         <v>14</v>
       </c>
-      <c r="AS12" s="1" t="s">
+      <c r="AS12" t="s">
+        <v>507</v>
+      </c>
+      <c r="AT12">
+        <v>14</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="AV12">
+        <v>14</v>
+      </c>
+      <c r="AW12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:45" ht="225" customHeight="1">
+    <row r="13" spans="1:49" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3925,11 +4236,23 @@
       <c r="AR13">
         <v>10</v>
       </c>
-      <c r="AS13" s="1" t="s">
+      <c r="AS13" t="s">
+        <v>513</v>
+      </c>
+      <c r="AT13">
+        <v>14</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="252" customHeight="1">
+    <row r="14" spans="1:49" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4061,10 +4384,22 @@
         <v>11</v>
       </c>
       <c r="AS14" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="AT14">
+        <v>14</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="AV14">
+        <v>12</v>
+      </c>
+      <c r="AW14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:45" ht="56.25">
+    <row r="15" spans="1:49" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4111,11 +4446,11 @@
       <c r="T15" s="1">
         <v>14</v>
       </c>
-      <c r="AS15" s="1" t="s">
+      <c r="AW15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:45" ht="56.25">
+    <row r="16" spans="1:49" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4246,11 +4581,23 @@
       <c r="AR16">
         <v>14</v>
       </c>
-      <c r="AS16" t="s">
+      <c r="AS16" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="AT16">
+        <v>14</v>
+      </c>
+      <c r="AU16" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="AV16">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="56.25">
+    <row r="17" spans="1:49" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4381,11 +4728,23 @@
       <c r="AR17">
         <v>14</v>
       </c>
-      <c r="AS17" t="s">
+      <c r="AS17" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="AT17">
+        <v>14</v>
+      </c>
+      <c r="AU17" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AV17">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="56.25">
+    <row r="18" spans="1:49" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4515,11 +4874,23 @@
       <c r="AR18">
         <v>14</v>
       </c>
-      <c r="AS18" t="s">
+      <c r="AS18" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="AT18">
+        <v>12</v>
+      </c>
+      <c r="AU18" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="AV18">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:45" ht="56.25">
+    <row r="19" spans="1:49" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -4650,11 +5021,23 @@
       <c r="AR19">
         <v>14</v>
       </c>
-      <c r="AS19" t="s">
+      <c r="AS19" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AT19">
+        <v>14</v>
+      </c>
+      <c r="AU19" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="AV19">
+        <v>14</v>
+      </c>
+      <c r="AW19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:45" ht="56.25">
+    <row r="20" spans="1:49" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -4784,11 +5167,23 @@
       <c r="AR20">
         <v>14</v>
       </c>
-      <c r="AS20" t="s">
+      <c r="AS20" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="AV20">
+        <v>14</v>
+      </c>
+      <c r="AW20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:45" ht="257.25" customHeight="1">
+    <row r="21" spans="1:49" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -4922,10 +5317,22 @@
         <v>10</v>
       </c>
       <c r="AS21" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="AT21">
+        <v>14</v>
+      </c>
+      <c r="AU21" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="AV21">
+        <v>10</v>
+      </c>
+      <c r="AW21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="409.5">
+    <row r="22" spans="1:49" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5056,10 +5463,22 @@
         <v>12</v>
       </c>
       <c r="AS22" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AT22">
+        <v>12</v>
+      </c>
+      <c r="AU22" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AV22">
+        <v>12</v>
+      </c>
+      <c r="AW22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:45" ht="409.5">
+    <row r="23" spans="1:49" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5190,10 +5609,22 @@
         <v>10</v>
       </c>
       <c r="AS23" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="AT23">
+        <v>12</v>
+      </c>
+      <c r="AU23" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="AV23">
+        <v>10</v>
+      </c>
+      <c r="AW23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:45" ht="56.25">
+    <row r="24" spans="1:49" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5324,10 +5755,22 @@
         <v>14</v>
       </c>
       <c r="AS24" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="AT24">
+        <v>12</v>
+      </c>
+      <c r="AU24" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AV24" s="6">
+        <v>14</v>
+      </c>
+      <c r="AW24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="56.25">
+    <row r="25" spans="1:49" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5458,10 +5901,22 @@
         <v>14</v>
       </c>
       <c r="AS25" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AT25">
+        <v>12</v>
+      </c>
+      <c r="AU25" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="AV25" s="6">
+        <v>14</v>
+      </c>
+      <c r="AW25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="75">
+    <row r="26" spans="1:49" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5592,10 +6047,22 @@
         <v>14</v>
       </c>
       <c r="AS26" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AT26">
+        <v>12</v>
+      </c>
+      <c r="AU26" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="AV26" s="6">
+        <v>14</v>
+      </c>
+      <c r="AW26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="56.25">
+    <row r="27" spans="1:49" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5726,10 +6193,22 @@
         <v>14</v>
       </c>
       <c r="AS27" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AT27">
+        <v>12</v>
+      </c>
+      <c r="AU27" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="AV27" s="6">
+        <v>14</v>
+      </c>
+      <c r="AW27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="75">
+    <row r="28" spans="1:49" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5860,10 +6339,22 @@
         <v>14</v>
       </c>
       <c r="AS28" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="AT28">
+        <v>12</v>
+      </c>
+      <c r="AU28" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="AV28" s="6">
+        <v>14</v>
+      </c>
+      <c r="AW28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:45">
+    <row r="29" spans="1:49">
       <c r="A29">
         <v>27</v>
       </c>
@@ -5901,8 +6392,12 @@
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
       <c r="AS29" s="1"/>
-    </row>
-    <row r="30" spans="1:45" ht="409.5">
+      <c r="AT29" s="1"/>
+      <c r="AU29" s="1"/>
+      <c r="AV29" s="1"/>
+      <c r="AW29" s="1"/>
+    </row>
+    <row r="30" spans="1:49" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6033,10 +6528,22 @@
         <v>10</v>
       </c>
       <c r="AS30" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="AT30" s="1">
+        <v>16</v>
+      </c>
+      <c r="AU30" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="AV30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AW30" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="1:45" ht="409.5">
+    <row r="31" spans="1:49" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6166,11 +6673,23 @@
       <c r="AR31" s="1">
         <v>12</v>
       </c>
-      <c r="AS31" s="1" t="s">
+      <c r="AS31" t="s">
+        <v>545</v>
+      </c>
+      <c r="AT31" s="1">
+        <v>16</v>
+      </c>
+      <c r="AU31" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="AV31" s="1">
+        <v>12</v>
+      </c>
+      <c r="AW31" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="375">
+    <row r="32" spans="1:49" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6300,7 +6819,19 @@
       <c r="AR32" s="1">
         <v>14</v>
       </c>
-      <c r="AS32" s="1" t="s">
+      <c r="AS32" t="s">
+        <v>547</v>
+      </c>
+      <c r="AT32" s="1">
+        <v>16</v>
+      </c>
+      <c r="AU32" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AV32" s="1">
+        <v>14</v>
+      </c>
+      <c r="AW32" s="1" t="s">
         <v>367</v>
       </c>
     </row>
@@ -11104,22 +11635,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:45">
+    <row r="993" spans="1:49">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:45">
+    <row r="994" spans="1:49">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:45">
+    <row r="995" spans="1:49">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:45">
+    <row r="996" spans="1:49">
       <c r="A996">
         <v>994</v>
       </c>
@@ -11244,10 +11775,22 @@
         <v>14</v>
       </c>
       <c r="AS996" t="s">
+        <v>141</v>
+      </c>
+      <c r="AT996">
+        <v>14</v>
+      </c>
+      <c r="AU996" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV996">
+        <v>14</v>
+      </c>
+      <c r="AW996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:45" ht="93.75">
+    <row r="997" spans="1:49" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -11374,11 +11917,23 @@
       <c r="AR997">
         <v>14</v>
       </c>
-      <c r="AS997" s="1" t="s">
+      <c r="AS997" t="s">
+        <v>143</v>
+      </c>
+      <c r="AT997">
+        <v>14</v>
+      </c>
+      <c r="AU997" t="s">
+        <v>267</v>
+      </c>
+      <c r="AV997">
+        <v>14</v>
+      </c>
+      <c r="AW997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:45" ht="75">
+    <row r="998" spans="1:49" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -11502,11 +12057,23 @@
       <c r="AR998">
         <v>14</v>
       </c>
-      <c r="AS998" s="1" t="s">
+      <c r="AS998" t="s">
+        <v>145</v>
+      </c>
+      <c r="AT998">
+        <v>14</v>
+      </c>
+      <c r="AU998" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AV998">
+        <v>14</v>
+      </c>
+      <c r="AW998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:45" ht="75">
+    <row r="999" spans="1:49" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -11630,11 +12197,23 @@
       <c r="AR999">
         <v>14</v>
       </c>
-      <c r="AS999" s="1" t="s">
+      <c r="AS999" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT999">
+        <v>14</v>
+      </c>
+      <c r="AU999" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AV999">
+        <v>14</v>
+      </c>
+      <c r="AW999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:45" ht="75">
+    <row r="1000" spans="1:49" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -11759,10 +12338,22 @@
         <v>14</v>
       </c>
       <c r="AS1000" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AT1000">
+        <v>14</v>
+      </c>
+      <c r="AU1000" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AV1000">
+        <v>14</v>
+      </c>
+      <c r="AW1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:45">
+    <row r="1001" spans="1:49">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -11887,10 +12478,22 @@
         <v>14</v>
       </c>
       <c r="AS1001" t="s">
+        <v>151</v>
+      </c>
+      <c r="AT1001">
+        <v>14</v>
+      </c>
+      <c r="AU1001" t="s">
+        <v>271</v>
+      </c>
+      <c r="AV1001">
+        <v>14</v>
+      </c>
+      <c r="AW1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:45">
+    <row r="1002" spans="1:49">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -11997,6 +12600,15 @@
         <v>0</v>
       </c>
       <c r="AQ1002" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT1002">
+        <v>0</v>
+      </c>
+      <c r="AU1002" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Item/ItemMessage.xlsx
+++ b/Assets/Originals/Excels/Item/ItemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4C5E21-8FDC-437C-84C4-C6AED34B205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B02094A-A851-4E09-A534-C1D2B7BA234F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="603">
   <si>
     <t>itemId</t>
     <phoneticPr fontId="1"/>
@@ -2200,6 +2200,193 @@
     <t>J'ai entendu au loin un enfant fredonner, et dès que la chanson s'est terminée, il s'est soudain mis à courir droit sur moi.
 Je l'ai retardé maintes fois et je pensais l'avoir semé, mais il continue de me traquer. Pourquoi sait-il toujours où je suis…
 J'ai eu la chance d'échapper aux autres monstres, mais cette fois, c'est peut-être vraiment la fin pour moi…</t>
+  </si>
+  <si>
+    <t>itemNameTurkish</t>
+  </si>
+  <si>
+    <t>itemNameSizeTurkish</t>
+  </si>
+  <si>
+    <t>itemDescriptionTurkish</t>
+  </si>
+  <si>
+    <t>itemDescriptionSizeTurkish</t>
+  </si>
+  <si>
+    <t>Parkta bir çocuğun cesedi</t>
+  </si>
+  <si>
+    <t>Son dakika! Parkta bir çocuğun cesedi bulundu! Cinayet silahı neydi?
+● ayının ×'inde sabaha karşı, şehirdeki △△ Parkı yakınlarında bir erkek çocuğun (tahminen 12-14 yaşında) cesedi bulundu. Olay yeri, yerel halkın sevdiği bir yürüyüş yolunun kenarında; ceset, sabah yürüyüşü yapan bir yoldan geçen tarafından fark edildi.
+Cesette gözle görülür bir yara yok ve “bir suç olup olmadığı belirsiz” deniyor. Ayrıca soruşturmacılara göre olay yerinin yakınında herhangi bir silah bulunamadı.
+Çocuğun kimliği henüz belirlenemedi; polis bölge sakinleriyle görüşmeye devam ediyor.
+Soruşturma zorlu ilerliyor; gelişmeler bekleniyor.</t>
+  </si>
+  <si>
+    <t>Uyku hapı</t>
+  </si>
+  <si>
+    <t>Yatmadan 1-2 saat önce alındığında uykusuzluğu gideren güçlü bir uyku hapı.</t>
+  </si>
+  <si>
+    <t>Bıçak</t>
+  </si>
+  <si>
+    <t>Keskin ağızlı eski bir bıçak.</t>
+  </si>
+  <si>
+    <t>Çekiç</t>
+  </si>
+  <si>
+    <t>Ağır, demir bir çekiç.</t>
+  </si>
+  <si>
+    <t>İp</t>
+  </si>
+  <si>
+    <t>Uçları yıpranmış, kalın ve sağlam bir ip.</t>
+  </si>
+  <si>
+    <t>Eğitim</t>
+  </si>
+  <si>
+    <t>Bir adam evinde öldürülmüş olarak bulundu. Başında şiddetli darbe izleri vardı; polis, olayın künt bir cisimle işlendiğini düşünerek soruşturma başlattı.</t>
+  </si>
+  <si>
+    <t>Balta</t>
+  </si>
+  <si>
+    <t>Ağzı göründüğünden daha fazla çentiklenmiş ağır bir balta.</t>
+  </si>
+  <si>
+    <t>Dayanıklılık Güçlendirici</t>
+  </si>
+  <si>
+    <t>Kullanınca: Belirli bir süre dayanıklılık tüketimini azaltır ve dayanıklılık yenilenmesini artırır.</t>
+  </si>
+  <si>
+    <t>Gizemli Pusula</t>
+  </si>
+  <si>
+    <t>İğnesinde mavi bir küre parçası kullanılmıştır; her zaman bir Yargının Mavi Küresi'nin bulunduğu yönü gösterir.</t>
+  </si>
+  <si>
+    <t>Hastane yatağı maketi</t>
+  </si>
+  <si>
+    <t>Maketin arkasında “Hastalık” yazıyor.</t>
+  </si>
+  <si>
+    <t>Hemzemin geçit maketi</t>
+  </si>
+  <si>
+    <t>Maketin arkasında “Ezilme (tren)” yazıyor.</t>
+  </si>
+  <si>
+    <t>Yıkılmış bina maketi</t>
+  </si>
+  <si>
+    <t>Maketin arkasında “Ezilme (enkaz)” yazıyor.</t>
+  </si>
+  <si>
+    <t>Şömine maketi</t>
+  </si>
+  <si>
+    <t>Maketin arkasında “Yanma” yazıyor.</t>
+  </si>
+  <si>
+    <t>Havuz maketi</t>
+  </si>
+  <si>
+    <t>Maketin arkasında “Boğulma” yazıyor.</t>
+  </si>
+  <si>
+    <t>Kraker</t>
+  </si>
+  <si>
+    <t>Hemen önündeki yakın bir Gezgine karşı kullanılırsa, onu bir süreliğine sersemletip hareketsiz bırakır. Ancak yüksek bir patlama sesi çıkarır.</t>
+  </si>
+  <si>
+    <t>Bir en yakın arkadaşın hikâyesi</t>
+  </si>
+  <si>
+    <t>Eski en yakın arkadaşıma
+Küçükken hep yakındaki △△ Parkı'nda birlikte oynadığımızı hatırlıyor musun?
+“Hep birlikte olacağız.”
+O gün parktaki bankta bana söylediğin bu sözleri hâlâ apaçık hatırlıyorum.
+Ama her mevsim geçtikçe parka gelebildiğin günler azaldı……
+Seni son gördüğümde soğuk bir hâlde yatıyordun, kılını bile kıpırdatmıyordun ve o her zamanki yumuşak sesinle adımı bir daha seslenmedin…
+Sensiz geçen günlere katlandım ama artık çok acı çekiyorum, dayanamıyorum.
+Bu yüzden ben de yanına geliyorum.</t>
+  </si>
+  <si>
+    <t>Gelişme! Parkta bir çocuğun cesedi</t>
+  </si>
+  <si>
+    <t>△△ Parkı'nda bulunan çocuğun cesediyle ilgili polis çevrede ifade almaya devam ediyor.
+Okulda çocukla ilişkisi olan yedi öğrenciyle görüşüldü. Çocuğun okul eşyaları hakkındaki ifadelere göre polis, bazılarının yalan söylüyor olabileceğini düşünüyor.
+A: Ahşap işleri dersinde yeni bir sprey boyayı tahtaya birazcık kullandı.
+B: Yıllarca kullanılınca ders kitabı sınırına ulaşmış, paramparça olmuş.
+C: Birinin onun okul terliklerine iğne koyduğunu gördüm.
+D: A'ya katılıyorum.
+E: Defteri yeni, neredeyse hiç kullanılmamış.
+F: B'ye katılıyorum. C yalan söylüyor.
+G: C'ye katılıyorum. A yalan söylüyor.</t>
+  </si>
+  <si>
+    <t>Okul terlikleri</t>
+  </si>
+  <si>
+    <t>Dikkatle bakınca içine iğneler yerleştirildiği görülüyor.</t>
+  </si>
+  <si>
+    <t>Ders kitabı</t>
+  </si>
+  <si>
+    <t>Asla doğal olamayacak kadar paramparça olmuş.</t>
+  </si>
+  <si>
+    <t>Kirli tek ayakkabı</t>
+  </si>
+  <si>
+    <t>Sprey boyayla boyanmış ve fena hâlde kirletilmiş.</t>
+  </si>
+  <si>
+    <t>Sprey boya kutusu</t>
+  </si>
+  <si>
+    <t>Boya spreyi. İçinde neredeyse hiç kalmamış.</t>
+  </si>
+  <si>
+    <t>Yeni defter</t>
+  </si>
+  <si>
+    <t>Dikkatle bakınca bazı sayfaların birbirine yapıştırıldığı görülüyor.</t>
+  </si>
+  <si>
+    <t>Sessizlikte Kızışan Gezgin</t>
+  </si>
+  <si>
+    <t>“Benim adım…” demek isterdim ama adım yok edildiği için hatırlayamıyorum. Bu yüzden bu labirentte olanları buraya not ediyorum.
+Birkaç kişiyle labirenti keşfediyorduk ama içimizden biri takım elbiseli, kırmızı tenli bir canavara yakalandı. Hemen kaçtım, o yüzden ona sonra ne olduğunu bilmiyorum. Şimdi saklanırken durumu toparlamaya çalışıyorum; o canavarın özelliklerini kendimce analiz edeyim.
+Önce yakalanan kişi hakkında: Korkuya dayanamayıp paniğe kapıldı, koştu ve çok ses çıkardı. Muhtemelen bu yüzden fark edildi. Ayrıca bir keresinde canavarın yakınında yanlışlıkla fenerimi yaktım ama yerim belli olmadı; galiba parlak ışığı algılayamıyor.</t>
+  </si>
+  <si>
+    <t>Unutuşun Büyüleyici Gezgini</t>
+  </si>
+  <si>
+    <t>Bir yerden bir kadın sesi duydum ve ne olduğunu anlamak için siperden baktığım an oldu: Kulakları olmayan kahverengi saçlı bir kadın beni fark eder etmez çığlık atarak bana saldırdı.
+Şansım yaver gitti, bir sipere yuvarlanıp kurtuldum ama bunun yerine yakındaki biri hedef alındı. Canavarla birlikte uzaklara koştukları için kurtuldum ama o kişi büyük ihtimalle benim yüzümden saldırıya uğradı.
+Sadece görülmek değil; üzerine ışık tutulursa kendini kaybedip saldırıyor. Yani ona karşı asla ışık kullanma.</t>
+  </si>
+  <si>
+    <t>Şarkı Söyleyen Gezgin</t>
+  </si>
+  <si>
+    <t>Uzaktan bir çocuğun mırıldandığını duydum; şarkı bittiği an birden doğruca bana doğru koşmaya başladı.
+Defalarca durdurup kaçtığımı sandım ama beni sürekli takip ediyor. Neden hep nerede olduğumu biliyor…
+Diğer canavarlardan şans eseri kaçtım ama bu sefer işim bitmiş olabilir…</t>
   </si>
 </sst>
 </file>
@@ -2577,7 +2764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW1002"/>
+  <dimension ref="A1:BA1002"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2626,9 +2813,13 @@
     <col min="46" max="46" width="21.875" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="46.5" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="38.875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="27.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49">
+    <row r="1" spans="1:53">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2774,16 +2965,28 @@
         <v>498</v>
       </c>
       <c r="AW1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>550</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>552</v>
+      </c>
+      <c r="BA1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:49">
+    <row r="2" spans="1:53">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:49" ht="409.5">
+    <row r="3" spans="1:53" ht="409.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2926,10 +3129,22 @@
         <v>11</v>
       </c>
       <c r="AW3" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="AZ3">
+        <v>11</v>
+      </c>
+      <c r="BA3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="228" customHeight="1">
+    <row r="4" spans="1:53" ht="228" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3072,10 +3287,22 @@
         <v>13</v>
       </c>
       <c r="AW4" t="s">
+        <v>555</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="AZ4">
+        <v>14</v>
+      </c>
+      <c r="BA4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="92.25" customHeight="1">
+    <row r="5" spans="1:53" ht="92.25" customHeight="1">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3218,10 +3445,22 @@
         <v>14</v>
       </c>
       <c r="AW5" t="s">
+        <v>557</v>
+      </c>
+      <c r="AX5">
+        <v>14</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="AZ5">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="37.5">
+    <row r="6" spans="1:53" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3364,15 +3603,27 @@
         <v>14</v>
       </c>
       <c r="AW6" t="s">
+        <v>559</v>
+      </c>
+      <c r="AX6">
+        <v>14</v>
+      </c>
+      <c r="AY6" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="AZ6">
+        <v>14</v>
+      </c>
+      <c r="BA6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:49">
+    <row r="7" spans="1:53">
       <c r="A7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="56.25">
+    <row r="8" spans="1:53" ht="56.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3515,10 +3766,22 @@
         <v>14</v>
       </c>
       <c r="AW8" t="s">
+        <v>561</v>
+      </c>
+      <c r="AX8">
+        <v>14</v>
+      </c>
+      <c r="AY8" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="AZ8">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="297.75" customHeight="1">
+    <row r="9" spans="1:53" ht="297.75" customHeight="1">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3661,10 +3924,22 @@
         <v>14</v>
       </c>
       <c r="AW9" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="AX9">
+        <v>14</v>
+      </c>
+      <c r="AY9" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="AZ9">
+        <v>14</v>
+      </c>
+      <c r="BA9" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="56.25">
+    <row r="10" spans="1:53" ht="56.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3807,10 +4082,22 @@
         <v>14</v>
       </c>
       <c r="AW10" t="s">
+        <v>565</v>
+      </c>
+      <c r="AX10">
+        <v>14</v>
+      </c>
+      <c r="AY10" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="37.5">
+    <row r="11" spans="1:53" ht="37.5">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3952,11 +4239,23 @@
       <c r="AV11">
         <v>14</v>
       </c>
-      <c r="AW11" s="1" t="s">
+      <c r="AW11" t="s">
+        <v>559</v>
+      </c>
+      <c r="AX11">
+        <v>14</v>
+      </c>
+      <c r="AY11" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="56.25">
+    <row r="12" spans="1:53" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4099,11 +4398,23 @@
       <c r="AV12">
         <v>14</v>
       </c>
-      <c r="AW12" s="1" t="s">
+      <c r="AW12" t="s">
+        <v>561</v>
+      </c>
+      <c r="AX12">
+        <v>14</v>
+      </c>
+      <c r="AY12" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="225" customHeight="1">
+    <row r="13" spans="1:53" ht="225" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4248,11 +4559,23 @@
       <c r="AV13">
         <v>10</v>
       </c>
-      <c r="AW13" s="1" t="s">
+      <c r="AW13" t="s">
+        <v>567</v>
+      </c>
+      <c r="AX13">
+        <v>14</v>
+      </c>
+      <c r="AY13" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="AZ13">
+        <v>10</v>
+      </c>
+      <c r="BA13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="252" customHeight="1">
+    <row r="14" spans="1:53" ht="252" customHeight="1">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4396,10 +4719,22 @@
         <v>12</v>
       </c>
       <c r="AW14" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="AX14">
+        <v>14</v>
+      </c>
+      <c r="AY14" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="56.25">
+    <row r="15" spans="1:53" ht="56.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4446,11 +4781,11 @@
       <c r="T15" s="1">
         <v>14</v>
       </c>
-      <c r="AW15" s="1" t="s">
+      <c r="BA15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="56.25">
+    <row r="16" spans="1:53" ht="56.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4593,11 +4928,23 @@
       <c r="AV16">
         <v>14</v>
       </c>
-      <c r="AW16" t="s">
+      <c r="AW16" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="AX16">
+        <v>14</v>
+      </c>
+      <c r="AY16" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="AZ16">
+        <v>14</v>
+      </c>
+      <c r="BA16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="56.25">
+    <row r="17" spans="1:53" ht="56.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4740,11 +5087,23 @@
       <c r="AV17">
         <v>14</v>
       </c>
-      <c r="AW17" t="s">
+      <c r="AW17" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="AX17">
+        <v>14</v>
+      </c>
+      <c r="AY17" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="56.25">
+    <row r="18" spans="1:53" ht="56.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4886,11 +5245,23 @@
       <c r="AV18">
         <v>14</v>
       </c>
-      <c r="AW18" t="s">
+      <c r="AW18" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="AX18">
+        <v>12</v>
+      </c>
+      <c r="AY18" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="AZ18">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="56.25">
+    <row r="19" spans="1:53" ht="56.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5033,11 +5404,23 @@
       <c r="AV19">
         <v>14</v>
       </c>
-      <c r="AW19" t="s">
+      <c r="AW19" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="AX19">
+        <v>14</v>
+      </c>
+      <c r="AY19" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="AZ19">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="56.25">
+    <row r="20" spans="1:53" ht="56.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5179,11 +5562,23 @@
       <c r="AV20">
         <v>14</v>
       </c>
-      <c r="AW20" t="s">
+      <c r="AW20" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="AX20">
+        <v>12</v>
+      </c>
+      <c r="AY20" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="AZ20">
+        <v>14</v>
+      </c>
+      <c r="BA20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="257.25" customHeight="1">
+    <row r="21" spans="1:53" ht="257.25" customHeight="1">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5329,10 +5724,22 @@
         <v>10</v>
       </c>
       <c r="AW21" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="AX21">
+        <v>14</v>
+      </c>
+      <c r="AY21" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="AZ21">
+        <v>10</v>
+      </c>
+      <c r="BA21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="409.5">
+    <row r="22" spans="1:53" ht="409.5">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5475,10 +5882,22 @@
         <v>12</v>
       </c>
       <c r="AW22" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="AX22">
+        <v>12</v>
+      </c>
+      <c r="AY22" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="AZ22">
+        <v>12</v>
+      </c>
+      <c r="BA22" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="409.5">
+    <row r="23" spans="1:53" ht="409.5">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5621,10 +6040,22 @@
         <v>10</v>
       </c>
       <c r="AW23" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AX23">
+        <v>12</v>
+      </c>
+      <c r="AY23" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="AZ23">
+        <v>10</v>
+      </c>
+      <c r="BA23" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="56.25">
+    <row r="24" spans="1:53" ht="56.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5767,10 +6198,22 @@
         <v>14</v>
       </c>
       <c r="AW24" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="AX24">
+        <v>12</v>
+      </c>
+      <c r="AY24" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="AZ24" s="6">
+        <v>14</v>
+      </c>
+      <c r="BA24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="56.25">
+    <row r="25" spans="1:53" ht="56.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5913,10 +6356,22 @@
         <v>14</v>
       </c>
       <c r="AW25" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AX25">
+        <v>12</v>
+      </c>
+      <c r="AY25" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="AZ25" s="6">
+        <v>14</v>
+      </c>
+      <c r="BA25" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="75">
+    <row r="26" spans="1:53" ht="75">
       <c r="A26">
         <v>24</v>
       </c>
@@ -6059,10 +6514,22 @@
         <v>14</v>
       </c>
       <c r="AW26" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AX26">
+        <v>12</v>
+      </c>
+      <c r="AY26" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AZ26" s="6">
+        <v>14</v>
+      </c>
+      <c r="BA26" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="56.25">
+    <row r="27" spans="1:53" ht="56.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -6205,10 +6672,22 @@
         <v>14</v>
       </c>
       <c r="AW27" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AZ27" s="6">
+        <v>14</v>
+      </c>
+      <c r="BA27" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="75">
+    <row r="28" spans="1:53" ht="75">
       <c r="A28">
         <v>26</v>
       </c>
@@ -6351,10 +6830,22 @@
         <v>14</v>
       </c>
       <c r="AW28" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="AX28">
+        <v>12</v>
+      </c>
+      <c r="AY28" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AZ28" s="6">
+        <v>14</v>
+      </c>
+      <c r="BA28" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:49">
+    <row r="29" spans="1:53">
       <c r="A29">
         <v>27</v>
       </c>
@@ -6396,8 +6887,12 @@
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
       <c r="AW29" s="1"/>
-    </row>
-    <row r="30" spans="1:49" ht="409.5">
+      <c r="AX29" s="1"/>
+      <c r="AY29" s="1"/>
+      <c r="AZ29" s="1"/>
+      <c r="BA29" s="1"/>
+    </row>
+    <row r="30" spans="1:53" ht="409.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6540,10 +7035,22 @@
         <v>10</v>
       </c>
       <c r="AW30" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AX30" s="1">
+        <v>16</v>
+      </c>
+      <c r="AY30" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AZ30" s="1">
+        <v>10</v>
+      </c>
+      <c r="BA30" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="409.5">
+    <row r="31" spans="1:53" ht="409.5">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6685,11 +7192,23 @@
       <c r="AV31" s="1">
         <v>12</v>
       </c>
-      <c r="AW31" s="1" t="s">
+      <c r="AW31" t="s">
+        <v>599</v>
+      </c>
+      <c r="AX31" s="1">
+        <v>16</v>
+      </c>
+      <c r="AY31" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="AZ31" s="1">
+        <v>12</v>
+      </c>
+      <c r="BA31" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="375">
+    <row r="32" spans="1:53" ht="375">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6831,7 +7350,19 @@
       <c r="AV32" s="1">
         <v>14</v>
       </c>
-      <c r="AW32" s="1" t="s">
+      <c r="AW32" t="s">
+        <v>601</v>
+      </c>
+      <c r="AX32" s="1">
+        <v>16</v>
+      </c>
+      <c r="AY32" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="AZ32" s="1">
+        <v>14</v>
+      </c>
+      <c r="BA32" s="1" t="s">
         <v>367</v>
       </c>
     </row>
@@ -11635,22 +12166,22 @@
         <v>990</v>
       </c>
     </row>
-    <row r="993" spans="1:49">
+    <row r="993" spans="1:53">
       <c r="A993">
         <v>991</v>
       </c>
     </row>
-    <row r="994" spans="1:49">
+    <row r="994" spans="1:53">
       <c r="A994">
         <v>992</v>
       </c>
     </row>
-    <row r="995" spans="1:49">
+    <row r="995" spans="1:53">
       <c r="A995">
         <v>993</v>
       </c>
     </row>
-    <row r="996" spans="1:49">
+    <row r="996" spans="1:53">
       <c r="A996">
         <v>994</v>
       </c>
@@ -11787,10 +12318,22 @@
         <v>14</v>
       </c>
       <c r="AW996" t="s">
+        <v>141</v>
+      </c>
+      <c r="AX996">
+        <v>14</v>
+      </c>
+      <c r="AY996" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ996">
+        <v>14</v>
+      </c>
+      <c r="BA996" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="997" spans="1:49" ht="93.75">
+    <row r="997" spans="1:53" ht="93.75">
       <c r="A997">
         <v>995</v>
       </c>
@@ -11929,11 +12472,23 @@
       <c r="AV997">
         <v>14</v>
       </c>
-      <c r="AW997" s="1" t="s">
+      <c r="AW997" t="s">
+        <v>143</v>
+      </c>
+      <c r="AX997">
+        <v>14</v>
+      </c>
+      <c r="AY997" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ997">
+        <v>14</v>
+      </c>
+      <c r="BA997" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="998" spans="1:49" ht="75">
+    <row r="998" spans="1:53" ht="75">
       <c r="A998">
         <v>996</v>
       </c>
@@ -12069,11 +12624,23 @@
       <c r="AV998">
         <v>14</v>
       </c>
-      <c r="AW998" s="1" t="s">
+      <c r="AW998" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX998">
+        <v>14</v>
+      </c>
+      <c r="AY998" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="AZ998">
+        <v>14</v>
+      </c>
+      <c r="BA998" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="999" spans="1:49" ht="75">
+    <row r="999" spans="1:53" ht="75">
       <c r="A999">
         <v>997</v>
       </c>
@@ -12209,11 +12776,23 @@
       <c r="AV999">
         <v>14</v>
       </c>
-      <c r="AW999" s="1" t="s">
+      <c r="AW999" t="s">
+        <v>147</v>
+      </c>
+      <c r="AX999">
+        <v>14</v>
+      </c>
+      <c r="AY999" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ999">
+        <v>14</v>
+      </c>
+      <c r="BA999" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="1000" spans="1:49" ht="75">
+    <row r="1000" spans="1:53" ht="75">
       <c r="A1000">
         <v>998</v>
       </c>
@@ -12350,10 +12929,22 @@
         <v>14</v>
       </c>
       <c r="AW1000" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX1000">
+        <v>14</v>
+      </c>
+      <c r="AY1000" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="AZ1000">
+        <v>14</v>
+      </c>
+      <c r="BA1000" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="1001" spans="1:49">
+    <row r="1001" spans="1:53">
       <c r="A1001">
         <v>999</v>
       </c>
@@ -12490,10 +13081,22 @@
         <v>14</v>
       </c>
       <c r="AW1001" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX1001">
+        <v>14</v>
+      </c>
+      <c r="AY1001" t="s">
+        <v>271</v>
+      </c>
+      <c r="AZ1001">
+        <v>14</v>
+      </c>
+      <c r="BA1001" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="1002" spans="1:49">
+    <row r="1002" spans="1:53">
       <c r="A1002">
         <v>1000</v>
       </c>
@@ -12609,6 +13212,15 @@
         <v>0</v>
       </c>
       <c r="AU1002" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="AX1002">
+        <v>0</v>
+      </c>
+      <c r="AY1002" t="s">
         <v>153</v>
       </c>
     </row>
